--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -816,7 +816,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122708958</v>
+        <v>122708596</v>
       </c>
       <c r="B3" t="n">
         <v>78660</v>
@@ -850,21 +850,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483506</v>
+        <v>483520</v>
       </c>
       <c r="R3" t="n">
-        <v>6991681</v>
+        <v>6991663</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -897,11 +892,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -953,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122708596</v>
+        <v>122708958</v>
       </c>
       <c r="B4" t="n">
         <v>78660</v>
@@ -987,16 +977,21 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483520</v>
+        <v>483506</v>
       </c>
       <c r="R4" t="n">
-        <v>6991663</v>
+        <v>6991681</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
@@ -1029,6 +1024,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122709756</v>
+        <v>122709081</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,36 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483522</v>
+        <v>483515</v>
       </c>
       <c r="R2" t="n">
-        <v>6991771</v>
+        <v>6991731</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +767,6 @@
           <t>2025-02-22</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -789,12 +793,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -812,10 +816,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122709081</v>
+        <v>122708546</v>
       </c>
       <c r="B3" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,51 +832,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483515</v>
+        <v>483452</v>
       </c>
       <c r="R3" t="n">
-        <v>6991731</v>
+        <v>6991602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -930,12 +920,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -956,7 +946,7 @@
         <v>122709111</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1083,7 +1073,7 @@
         <v>122708958</v>
       </c>
       <c r="B5" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1217,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708596</v>
+        <v>122709756</v>
       </c>
       <c r="B6" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1251,19 +1241,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483520</v>
+        <v>483522</v>
       </c>
       <c r="R6" t="n">
-        <v>6991663</v>
+        <v>6991771</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1293,6 +1288,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,10 +1344,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122708546</v>
+        <v>122708596</v>
       </c>
       <c r="B7" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483452</v>
+        <v>483520</v>
       </c>
       <c r="R7" t="n">
-        <v>6991602</v>
+        <v>6991663</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122709081</v>
+        <v>122709756</v>
       </c>
       <c r="B2" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,36 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>teleomorf</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483515</v>
+        <v>483522</v>
       </c>
       <c r="R2" t="n">
-        <v>6991731</v>
+        <v>6991771</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,6 +758,11 @@
           <t>2025-02-22</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -793,12 +789,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -816,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122708546</v>
+        <v>122708596</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -856,10 +852,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483452</v>
+        <v>483520</v>
       </c>
       <c r="R3" t="n">
-        <v>6991602</v>
+        <v>6991663</v>
       </c>
       <c r="S3" t="n">
         <v>8</v>
@@ -943,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709111</v>
+        <v>122709081</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -959,34 +955,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483508</v>
+        <v>483515</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1047,12 +1057,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,7 +1080,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122708958</v>
+        <v>122709111</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1104,24 +1114,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483506</v>
+        <v>483508</v>
       </c>
       <c r="R5" t="n">
-        <v>6991681</v>
+        <v>6991741</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1151,11 +1156,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122709756</v>
+        <v>122708958</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1243,7 +1243,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483522</v>
+        <v>483506</v>
       </c>
       <c r="R6" t="n">
-        <v>6991771</v>
+        <v>6991681</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,7 +1344,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122708596</v>
+        <v>122708546</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1384,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483520</v>
+        <v>483452</v>
       </c>
       <c r="R7" t="n">
-        <v>6991663</v>
+        <v>6991602</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122709756</v>
+        <v>122708546</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,24 +709,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483522</v>
+        <v>483452</v>
       </c>
       <c r="R2" t="n">
-        <v>6991771</v>
+        <v>6991602</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122708596</v>
+        <v>122709756</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -846,19 +836,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483520</v>
+        <v>483522</v>
       </c>
       <c r="R3" t="n">
-        <v>6991663</v>
+        <v>6991771</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,6 +883,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +939,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709081</v>
+        <v>122709111</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,48 +955,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483515</v>
+        <v>483508</v>
       </c>
       <c r="R4" t="n">
-        <v>6991731</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1057,12 +1043,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1080,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122709111</v>
+        <v>122709081</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1096,34 +1082,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483508</v>
+        <v>483515</v>
       </c>
       <c r="R5" t="n">
-        <v>6991741</v>
+        <v>6991731</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708958</v>
+        <v>122708596</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1241,21 +1241,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483506</v>
+        <v>483520</v>
       </c>
       <c r="R6" t="n">
-        <v>6991681</v>
+        <v>6991663</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1288,11 +1283,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1344,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122708546</v>
+        <v>122708958</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1378,16 +1368,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483452</v>
+        <v>483506</v>
       </c>
       <c r="R7" t="n">
-        <v>6991602</v>
+        <v>6991681</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1420,6 +1415,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -802,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122709756</v>
+        <v>122709111</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -836,24 +836,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483522</v>
+        <v>483508</v>
       </c>
       <c r="R3" t="n">
-        <v>6991771</v>
+        <v>6991741</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,11 +878,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -939,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709111</v>
+        <v>122709081</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,34 +945,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483508</v>
+        <v>483515</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1043,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122709081</v>
+        <v>122708596</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1082,51 +1086,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483515</v>
+        <v>483520</v>
       </c>
       <c r="R5" t="n">
-        <v>6991731</v>
+        <v>6991663</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1184,12 +1174,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1207,7 +1197,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708596</v>
+        <v>122708958</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1241,16 +1231,21 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483520</v>
+        <v>483506</v>
       </c>
       <c r="R6" t="n">
-        <v>6991663</v>
+        <v>6991681</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1283,6 +1278,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1334,7 +1334,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122708958</v>
+        <v>122709756</v>
       </c>
       <c r="B7" t="n">
         <v>78766</v>
@@ -1370,7 +1370,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483506</v>
+        <v>483522</v>
       </c>
       <c r="R7" t="n">
-        <v>6991681</v>
+        <v>6991771</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Fertila bålar.</t>
+          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -929,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709081</v>
+        <v>122708596</v>
       </c>
       <c r="B4" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,51 +945,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483515</v>
+        <v>483520</v>
       </c>
       <c r="R4" t="n">
-        <v>6991731</v>
+        <v>6991663</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1047,12 +1033,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1070,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122708596</v>
+        <v>122709081</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,37 +1072,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483520</v>
+        <v>483515</v>
       </c>
       <c r="R5" t="n">
-        <v>6991663</v>
+        <v>6991731</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708546</v>
+        <v>122708958</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483452</v>
+        <v>483506</v>
       </c>
       <c r="R2" t="n">
-        <v>6991602</v>
+        <v>6991681</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +812,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122709111</v>
+        <v>122708546</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -842,13 +852,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483508</v>
+        <v>483452</v>
       </c>
       <c r="R3" t="n">
-        <v>6991741</v>
+        <v>6991602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -929,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122708596</v>
+        <v>122709111</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -969,13 +979,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483520</v>
+        <v>483508</v>
       </c>
       <c r="R4" t="n">
-        <v>6991663</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122709081</v>
+        <v>122708596</v>
       </c>
       <c r="B5" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,51 +1082,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483515</v>
+        <v>483520</v>
       </c>
       <c r="R5" t="n">
-        <v>6991731</v>
+        <v>6991663</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1174,12 +1170,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1197,10 +1193,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708958</v>
+        <v>122709081</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1213,27 +1209,36 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1242,13 +1247,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483506</v>
+        <v>483515</v>
       </c>
       <c r="R6" t="n">
-        <v>6991681</v>
+        <v>6991731</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1280,11 +1285,6 @@
           <t>2025-02-22</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1469,6 +1469,2132 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123179071</v>
+      </c>
+      <c r="B8" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>483575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6991710</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123176924</v>
+      </c>
+      <c r="B9" t="n">
+        <v>74863</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>483383</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6991656</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123180297</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79876</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>483829</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6991767</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grenar på gran stående under gamla aspar</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123176943</v>
+      </c>
+      <c r="B11" t="n">
+        <v>77699</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>483380</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6991656</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123184445</v>
+      </c>
+      <c r="B12" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>483565</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6991603</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123180336</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79302</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1352</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Småflikig brosklav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Ramalina sinensis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>483833</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6991771</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123177397</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>483605</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6991834</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123182534</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79847</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>484029</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6991692</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123176616</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>483371</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6991602</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123176917</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>483378</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6991654</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123179132</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90970</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>483553</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6991669</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123177862</v>
+      </c>
+      <c r="B19" t="n">
+        <v>74863</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6991838</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123182555</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79751</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>484005</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6991716</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På asp (40 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123182989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>483820</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6991546</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123177015</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>483436</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6991677</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123181366</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>483899</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6991685</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708958</v>
+        <v>122708596</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,21 +709,16 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483506</v>
+        <v>483520</v>
       </c>
       <c r="R2" t="n">
-        <v>6991681</v>
+        <v>6991663</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -812,7 +802,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122708546</v>
+        <v>122709111</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -852,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483452</v>
+        <v>483508</v>
       </c>
       <c r="R3" t="n">
-        <v>6991602</v>
+        <v>6991741</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -939,10 +929,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709111</v>
+        <v>122709081</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -955,34 +945,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483508</v>
+        <v>483515</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991731</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1043,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1066,7 +1070,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122708596</v>
+        <v>122708958</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1100,16 +1104,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483520</v>
+        <v>483506</v>
       </c>
       <c r="R5" t="n">
-        <v>6991663</v>
+        <v>6991681</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1142,6 +1151,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1193,10 +1207,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122709081</v>
+        <v>122708546</v>
       </c>
       <c r="B6" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1209,51 +1223,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483515</v>
+        <v>483452</v>
       </c>
       <c r="R6" t="n">
-        <v>6991731</v>
+        <v>6991602</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123176924</v>
+        <v>123182534</v>
       </c>
       <c r="B9" t="n">
-        <v>74863</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,34 +1628,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483383</v>
+        <v>484029</v>
       </c>
       <c r="R9" t="n">
-        <v>6991656</v>
+        <v>6991692</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,12 +1697,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1744,10 +1744,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123180297</v>
+        <v>123184445</v>
       </c>
       <c r="B10" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,41 +1756,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483829</v>
+        <v>483565</v>
       </c>
       <c r="R10" t="n">
-        <v>6991767</v>
+        <v>6991603</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,21 +1845,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1876,10 +1861,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123176943</v>
+        <v>123177015</v>
       </c>
       <c r="B11" t="n">
-        <v>77699</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1892,34 +1877,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483380</v>
+        <v>483436</v>
       </c>
       <c r="R11" t="n">
-        <v>6991656</v>
+        <v>6991677</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1951,7 +1945,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1961,7 +1955,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2008,7 +2002,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123184445</v>
+        <v>123176616</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -2041,17 +2035,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483565</v>
+        <v>483371</v>
       </c>
       <c r="R12" t="n">
-        <v>6991603</v>
+        <v>6991602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2083,7 +2086,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2093,12 +2096,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2125,10 +2128,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123180336</v>
+        <v>123176924</v>
       </c>
       <c r="B13" t="n">
-        <v>79302</v>
+        <v>74863</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2141,43 +2144,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1352</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483833</v>
+        <v>483383</v>
       </c>
       <c r="R13" t="n">
-        <v>6991771</v>
+        <v>6991656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2209,7 +2203,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2219,12 +2213,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2238,17 +2232,17 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2266,7 +2260,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123177397</v>
+        <v>123176917</v>
       </c>
       <c r="B14" t="n">
         <v>78766</v>
@@ -2301,7 +2295,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2311,14 +2305,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483605</v>
+        <v>483378</v>
       </c>
       <c r="R14" t="n">
-        <v>6991834</v>
+        <v>6991654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2350,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2360,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2407,10 +2401,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123182534</v>
+        <v>123179132</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2423,34 +2417,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484029</v>
+        <v>483553</v>
       </c>
       <c r="R15" t="n">
-        <v>6991692</v>
+        <v>6991669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2482,7 +2481,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2492,12 +2491,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2511,17 +2510,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2539,10 +2538,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123176616</v>
+        <v>123176943</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2555,43 +2554,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483371</v>
+        <v>483380</v>
       </c>
       <c r="R16" t="n">
-        <v>6991602</v>
+        <v>6991656</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2623,7 +2613,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2633,12 +2623,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2649,6 +2639,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2665,7 +2670,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123176917</v>
+        <v>123181366</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2698,26 +2703,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483378</v>
+        <v>483899</v>
       </c>
       <c r="R17" t="n">
-        <v>6991654</v>
+        <v>6991685</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2745,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2759,12 +2755,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2806,10 +2797,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123179132</v>
+        <v>123177397</v>
       </c>
       <c r="B18" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2822,27 +2813,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2851,10 +2846,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483553</v>
+        <v>483605</v>
       </c>
       <c r="R18" t="n">
-        <v>6991669</v>
+        <v>6991834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2886,7 +2881,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2896,12 +2891,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2943,10 +2938,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123177862</v>
+        <v>123182555</v>
       </c>
       <c r="B19" t="n">
-        <v>74863</v>
+        <v>79751</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2955,46 +2950,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6456</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483615</v>
+        <v>484005</v>
       </c>
       <c r="R19" t="n">
-        <v>6991838</v>
+        <v>6991716</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3023,7 +3013,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3033,12 +3023,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3052,17 +3042,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3080,10 +3070,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123182555</v>
+        <v>123177862</v>
       </c>
       <c r="B20" t="n">
-        <v>79751</v>
+        <v>74863</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3092,41 +3082,46 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484005</v>
+        <v>483615</v>
       </c>
       <c r="R20" t="n">
-        <v>6991716</v>
+        <v>6991838</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3155,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3165,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3184,17 +3179,17 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3212,10 +3207,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123182989</v>
+        <v>123180336</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79302</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3228,34 +3223,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483820</v>
+        <v>483833</v>
       </c>
       <c r="R21" t="n">
-        <v>6991546</v>
+        <v>6991771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3287,7 +3291,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3297,12 +3301,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3313,6 +3317,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3329,7 +3348,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123177015</v>
+        <v>123182989</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3362,26 +3381,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483436</v>
+        <v>483820</v>
       </c>
       <c r="R22" t="n">
-        <v>6991677</v>
+        <v>6991546</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3413,7 +3423,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3423,12 +3433,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3439,21 +3449,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3470,10 +3465,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123181366</v>
+        <v>123180297</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3482,25 +3477,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3510,13 +3505,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483899</v>
+        <v>483829</v>
       </c>
       <c r="R23" t="n">
-        <v>6991685</v>
+        <v>6991767</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3545,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3555,7 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708596</v>
+        <v>122708546</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483520</v>
+        <v>483452</v>
       </c>
       <c r="R2" t="n">
-        <v>6991663</v>
+        <v>6991602</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122709111</v>
+        <v>122709081</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +818,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483508</v>
+        <v>483515</v>
       </c>
       <c r="R3" t="n">
-        <v>6991741</v>
+        <v>6991731</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,12 +920,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,10 +943,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709081</v>
+        <v>122709111</v>
       </c>
       <c r="B4" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,48 +959,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483515</v>
+        <v>483508</v>
       </c>
       <c r="R4" t="n">
-        <v>6991731</v>
+        <v>6991741</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1207,7 +1207,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708546</v>
+        <v>122708596</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1247,10 +1247,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483452</v>
+        <v>483520</v>
       </c>
       <c r="R6" t="n">
-        <v>6991602</v>
+        <v>6991663</v>
       </c>
       <c r="S6" t="n">
         <v>8</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123179071</v>
+        <v>123176917</v>
       </c>
       <c r="B8" t="n">
         <v>78766</v>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483575</v>
+        <v>483378</v>
       </c>
       <c r="R8" t="n">
-        <v>6991710</v>
+        <v>6991654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123182534</v>
+        <v>123181366</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,21 +1628,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>484029</v>
+        <v>483899</v>
       </c>
       <c r="R9" t="n">
-        <v>6991692</v>
+        <v>6991685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,12 +1697,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1716,17 +1711,17 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2002,10 +1997,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123176616</v>
+        <v>123182534</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2018,43 +2013,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483371</v>
+        <v>484029</v>
       </c>
       <c r="R12" t="n">
-        <v>6991602</v>
+        <v>6991692</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2086,7 +2072,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2096,12 +2082,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2112,6 +2098,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2128,10 +2129,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123176924</v>
+        <v>123176616</v>
       </c>
       <c r="B13" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2144,34 +2145,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483383</v>
+        <v>483371</v>
       </c>
       <c r="R13" t="n">
-        <v>6991656</v>
+        <v>6991602</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2203,7 +2213,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2213,12 +2223,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,21 +2239,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123176917</v>
+        <v>123177862</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2276,46 +2271,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483378</v>
+        <v>483615</v>
       </c>
       <c r="R14" t="n">
-        <v>6991654</v>
+        <v>6991838</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2344,7 +2335,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,12 +2345,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2538,10 +2529,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123176943</v>
+        <v>123180297</v>
       </c>
       <c r="B16" t="n">
-        <v>77699</v>
+        <v>79876</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2550,41 +2541,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483380</v>
+        <v>483829</v>
       </c>
       <c r="R16" t="n">
-        <v>6991656</v>
+        <v>6991767</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2613,7 +2604,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2623,12 +2614,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2670,10 +2661,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123181366</v>
+        <v>123176943</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,34 +2677,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483899</v>
+        <v>483380</v>
       </c>
       <c r="R17" t="n">
-        <v>6991685</v>
+        <v>6991656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2745,7 +2736,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2755,7 +2746,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2797,10 +2793,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123177397</v>
+        <v>123176924</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2813,43 +2809,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483605</v>
+        <v>483383</v>
       </c>
       <c r="R18" t="n">
-        <v>6991834</v>
+        <v>6991656</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2881,7 +2868,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2891,12 +2878,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3070,10 +3057,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123177862</v>
+        <v>123182989</v>
       </c>
       <c r="B20" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3086,42 +3073,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483615</v>
+        <v>483820</v>
       </c>
       <c r="R20" t="n">
-        <v>6991838</v>
+        <v>6991546</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3150,7 +3132,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3160,12 +3142,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3176,21 +3158,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3348,7 +3315,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123182989</v>
+        <v>123179071</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -3381,17 +3348,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483820</v>
+        <v>483575</v>
       </c>
       <c r="R22" t="n">
-        <v>6991546</v>
+        <v>6991710</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3423,7 +3399,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3433,7 +3409,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3449,6 +3425,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3465,10 +3456,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123180297</v>
+        <v>123177397</v>
       </c>
       <c r="B23" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3477,41 +3468,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483829</v>
+        <v>483605</v>
       </c>
       <c r="R23" t="n">
-        <v>6991767</v>
+        <v>6991834</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708546</v>
+        <v>122708958</v>
       </c>
       <c r="B2" t="n">
         <v>78766</v>
@@ -709,16 +709,21 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483452</v>
+        <v>483506</v>
       </c>
       <c r="R2" t="n">
-        <v>6991602</v>
+        <v>6991681</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122709081</v>
+        <v>122708546</v>
       </c>
       <c r="B3" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,51 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483515</v>
+        <v>483452</v>
       </c>
       <c r="R3" t="n">
-        <v>6991731</v>
+        <v>6991602</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -920,12 +916,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1070,10 +1066,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122708958</v>
+        <v>122709081</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,27 +1082,36 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1115,13 +1120,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483506</v>
+        <v>483515</v>
       </c>
       <c r="R5" t="n">
-        <v>6991681</v>
+        <v>6991731</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1153,11 +1158,6 @@
           <t>2025-02-22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123176917</v>
+        <v>123177862</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>74863</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,46 +1487,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483378</v>
+        <v>483615</v>
       </c>
       <c r="R8" t="n">
-        <v>6991654</v>
+        <v>6991838</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1551,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1561,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,7 +1608,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123181366</v>
+        <v>123176616</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1645,17 +1641,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483899</v>
+        <v>483371</v>
       </c>
       <c r="R9" t="n">
-        <v>6991685</v>
+        <v>6991602</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1692,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,7 +1702,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,21 +1718,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1739,10 +1734,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123184445</v>
+        <v>123176943</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>77699</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1755,21 +1750,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1779,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483565</v>
+        <v>483380</v>
       </c>
       <c r="R10" t="n">
-        <v>6991603</v>
+        <v>6991656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1814,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,12 +1819,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,6 +1835,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1856,7 +1866,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123177015</v>
+        <v>123181366</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1889,26 +1899,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483436</v>
+        <v>483899</v>
       </c>
       <c r="R11" t="n">
-        <v>6991677</v>
+        <v>6991685</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1941,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,12 +1951,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1997,10 +1993,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123182534</v>
+        <v>123179132</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2013,34 +2009,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484029</v>
+        <v>483553</v>
       </c>
       <c r="R12" t="n">
-        <v>6991692</v>
+        <v>6991669</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2072,7 +2073,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2082,12 +2083,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2101,17 +2102,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2129,7 +2130,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123176616</v>
+        <v>123177015</v>
       </c>
       <c r="B13" t="n">
         <v>78766</v>
@@ -2164,7 +2165,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483371</v>
+        <v>483436</v>
       </c>
       <c r="R13" t="n">
-        <v>6991602</v>
+        <v>6991677</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2213,7 +2214,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2223,12 +2224,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2239,6 +2240,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2255,10 +2271,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123177862</v>
+        <v>123177397</v>
       </c>
       <c r="B14" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2271,27 +2287,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2300,13 +2320,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483615</v>
+        <v>483605</v>
       </c>
       <c r="R14" t="n">
-        <v>6991838</v>
+        <v>6991834</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2335,7 +2355,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2345,12 +2365,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2392,10 +2412,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123179132</v>
+        <v>123182555</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>79751</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2404,43 +2424,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483553</v>
+        <v>484005</v>
       </c>
       <c r="R15" t="n">
-        <v>6991669</v>
+        <v>6991716</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2472,7 +2487,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2482,12 +2497,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2501,17 +2516,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2529,10 +2544,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123180297</v>
+        <v>123176917</v>
       </c>
       <c r="B16" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2541,41 +2556,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483829</v>
+        <v>483378</v>
       </c>
       <c r="R16" t="n">
-        <v>6991767</v>
+        <v>6991654</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2604,7 +2628,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2614,12 +2638,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2661,10 +2685,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123176943</v>
+        <v>123182534</v>
       </c>
       <c r="B17" t="n">
-        <v>77699</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2677,34 +2701,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483380</v>
+        <v>484029</v>
       </c>
       <c r="R17" t="n">
-        <v>6991656</v>
+        <v>6991692</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2736,7 +2760,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2746,12 +2770,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2765,17 +2789,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2793,10 +2817,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123176924</v>
+        <v>123182989</v>
       </c>
       <c r="B18" t="n">
-        <v>74863</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2809,21 +2833,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2833,10 +2857,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483383</v>
+        <v>483820</v>
       </c>
       <c r="R18" t="n">
-        <v>6991656</v>
+        <v>6991546</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2868,7 +2892,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2878,12 +2902,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2894,21 +2918,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2925,10 +2934,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123182555</v>
+        <v>123179071</v>
       </c>
       <c r="B19" t="n">
-        <v>79751</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2937,38 +2946,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484005</v>
+        <v>483575</v>
       </c>
       <c r="R19" t="n">
-        <v>6991716</v>
+        <v>6991710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3000,7 +3018,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3010,12 +3028,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3029,17 +3047,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3057,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123182989</v>
+        <v>123180297</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3069,41 +3087,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483820</v>
+        <v>483829</v>
       </c>
       <c r="R20" t="n">
-        <v>6991546</v>
+        <v>6991767</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3132,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3142,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3158,6 +3176,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3174,10 +3207,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123180336</v>
+        <v>123176924</v>
       </c>
       <c r="B21" t="n">
-        <v>79302</v>
+        <v>74863</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3190,43 +3223,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1352</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483833</v>
+        <v>483383</v>
       </c>
       <c r="R21" t="n">
-        <v>6991771</v>
+        <v>6991656</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3258,7 +3282,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3268,12 +3292,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3287,17 +3311,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3315,10 +3339,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123179071</v>
+        <v>123180336</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79302</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3331,26 +3355,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3360,14 +3384,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483575</v>
+        <v>483833</v>
       </c>
       <c r="R22" t="n">
-        <v>6991710</v>
+        <v>6991771</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3399,7 +3423,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3409,12 +3433,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3428,17 +3452,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3456,7 +3480,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123177397</v>
+        <v>123184445</v>
       </c>
       <c r="B23" t="n">
         <v>78766</v>
@@ -3489,26 +3513,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483605</v>
+        <v>483565</v>
       </c>
       <c r="R23" t="n">
-        <v>6991834</v>
+        <v>6991603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3540,7 +3555,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3550,12 +3565,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3566,21 +3581,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3339,10 +3339,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123180336</v>
+        <v>123184445</v>
       </c>
       <c r="B22" t="n">
-        <v>79302</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3355,43 +3355,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483833</v>
+        <v>483565</v>
       </c>
       <c r="R22" t="n">
-        <v>6991771</v>
+        <v>6991603</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3423,7 +3414,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3433,12 +3424,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,21 +3440,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3480,10 +3456,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123184445</v>
+        <v>123180336</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79302</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3496,34 +3472,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483565</v>
+        <v>483833</v>
       </c>
       <c r="R23" t="n">
-        <v>6991603</v>
+        <v>6991771</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3555,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3565,12 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,6 +3566,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122709756</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123177862</v>
+        <v>123179071</v>
       </c>
       <c r="B8" t="n">
-        <v>74863</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,27 +1487,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1516,13 +1520,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483615</v>
+        <v>483575</v>
       </c>
       <c r="R8" t="n">
-        <v>6991838</v>
+        <v>6991710</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1551,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1561,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123176616</v>
+        <v>123177015</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1657,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483371</v>
+        <v>483436</v>
       </c>
       <c r="R9" t="n">
-        <v>6991602</v>
+        <v>6991677</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1692,7 +1696,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1702,12 +1706,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1718,6 +1722,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1734,10 +1753,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123176943</v>
+        <v>123182534</v>
       </c>
       <c r="B10" t="n">
-        <v>77699</v>
+        <v>79850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1750,34 +1769,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483380</v>
+        <v>484029</v>
       </c>
       <c r="R10" t="n">
-        <v>6991656</v>
+        <v>6991692</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1828,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,12 +1838,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1838,17 +1857,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1866,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123181366</v>
+        <v>123184445</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1902,14 +1921,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483899</v>
+        <v>483565</v>
       </c>
       <c r="R11" t="n">
-        <v>6991685</v>
+        <v>6991603</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1941,7 +1960,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1951,7 +1970,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1962,21 +1986,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1993,10 +2002,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123179132</v>
+        <v>123177397</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2009,27 +2018,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2038,10 +2051,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483553</v>
+        <v>483605</v>
       </c>
       <c r="R12" t="n">
-        <v>6991669</v>
+        <v>6991834</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2073,7 +2086,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2083,12 +2096,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2130,10 +2143,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123177015</v>
+        <v>123182989</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2163,26 +2176,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483436</v>
+        <v>483820</v>
       </c>
       <c r="R13" t="n">
-        <v>6991677</v>
+        <v>6991546</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2214,7 +2218,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2224,12 +2228,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,21 +2244,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2271,10 +2260,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123177397</v>
+        <v>123176917</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2306,7 +2295,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2316,14 +2305,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483605</v>
+        <v>483378</v>
       </c>
       <c r="R14" t="n">
-        <v>6991834</v>
+        <v>6991654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2355,7 +2344,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2365,7 +2354,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2412,10 +2401,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123182555</v>
+        <v>123177862</v>
       </c>
       <c r="B15" t="n">
-        <v>79751</v>
+        <v>74866</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2424,41 +2413,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484005</v>
+        <v>483615</v>
       </c>
       <c r="R15" t="n">
-        <v>6991716</v>
+        <v>6991838</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2487,7 +2481,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2497,12 +2491,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2516,17 +2510,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2544,10 +2538,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123176917</v>
+        <v>123182555</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79754</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2556,47 +2550,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483378</v>
+        <v>484005</v>
       </c>
       <c r="R16" t="n">
-        <v>6991654</v>
+        <v>6991716</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2628,7 +2613,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2638,12 +2623,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2657,17 +2642,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2685,10 +2670,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123182534</v>
+        <v>123176943</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>77702</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2701,34 +2686,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484029</v>
+        <v>483380</v>
       </c>
       <c r="R17" t="n">
-        <v>6991692</v>
+        <v>6991656</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2760,7 +2745,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2770,12 +2755,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2789,17 +2774,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2817,10 +2802,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123182989</v>
+        <v>123176616</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2850,17 +2835,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483820</v>
+        <v>483371</v>
       </c>
       <c r="R18" t="n">
-        <v>6991546</v>
+        <v>6991602</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2892,7 +2886,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2902,12 +2896,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2934,10 +2928,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123179071</v>
+        <v>123180336</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>79305</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2950,26 +2944,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Jatta</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2979,14 +2973,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483575</v>
+        <v>483833</v>
       </c>
       <c r="R19" t="n">
-        <v>6991710</v>
+        <v>6991771</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3018,7 +3012,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3028,12 +3022,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3047,17 +3041,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3078,7 +3072,7 @@
         <v>123180297</v>
       </c>
       <c r="B20" t="n">
-        <v>79876</v>
+        <v>79879</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3210,7 +3204,7 @@
         <v>123176924</v>
       </c>
       <c r="B21" t="n">
-        <v>74863</v>
+        <v>74866</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3339,10 +3333,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123184445</v>
+        <v>123179132</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3355,34 +3349,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483565</v>
+        <v>483553</v>
       </c>
       <c r="R22" t="n">
-        <v>6991603</v>
+        <v>6991669</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3414,7 +3413,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3424,12 +3423,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3440,6 +3439,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3456,10 +3470,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123180336</v>
+        <v>123181366</v>
       </c>
       <c r="B23" t="n">
-        <v>79302</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3472,43 +3486,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483833</v>
+        <v>483899</v>
       </c>
       <c r="R23" t="n">
-        <v>6991771</v>
+        <v>6991685</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3540,7 +3545,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3550,12 +3555,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122709756</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123179071</v>
+        <v>123177015</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483575</v>
+        <v>483436</v>
       </c>
       <c r="R8" t="n">
-        <v>6991710</v>
+        <v>6991677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123177015</v>
+        <v>123176917</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483436</v>
+        <v>483378</v>
       </c>
       <c r="R9" t="n">
-        <v>6991677</v>
+        <v>6991654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1756,7 +1756,7 @@
         <v>123182534</v>
       </c>
       <c r="B10" t="n">
-        <v>79850</v>
+        <v>79852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123184445</v>
+        <v>123180297</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>79881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,41 +1897,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483565</v>
+        <v>483829</v>
       </c>
       <c r="R11" t="n">
-        <v>6991603</v>
+        <v>6991767</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1986,6 +1986,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2002,10 +2017,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123177397</v>
+        <v>123177862</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2018,31 +2033,27 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2051,13 +2062,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483605</v>
+        <v>483615</v>
       </c>
       <c r="R12" t="n">
-        <v>6991834</v>
+        <v>6991838</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2086,7 +2097,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2096,12 +2107,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2143,10 +2154,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123182989</v>
+        <v>123176924</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>74866</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2159,21 +2170,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2183,10 +2194,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483820</v>
+        <v>483383</v>
       </c>
       <c r="R13" t="n">
-        <v>6991546</v>
+        <v>6991656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2218,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2228,12 +2239,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2244,6 +2255,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2260,10 +2286,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123176917</v>
+        <v>123182555</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>79756</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2272,47 +2298,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483378</v>
+        <v>484005</v>
       </c>
       <c r="R14" t="n">
-        <v>6991654</v>
+        <v>6991716</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2344,7 +2361,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2354,12 +2371,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2373,17 +2390,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2401,10 +2418,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123177862</v>
+        <v>123182989</v>
       </c>
       <c r="B15" t="n">
-        <v>74866</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2417,42 +2434,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483615</v>
+        <v>483820</v>
       </c>
       <c r="R15" t="n">
-        <v>6991838</v>
+        <v>6991546</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2481,7 +2493,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2491,12 +2503,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2507,21 +2519,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2538,10 +2535,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123182555</v>
+        <v>123181366</v>
       </c>
       <c r="B16" t="n">
-        <v>79754</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2550,25 +2547,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2578,10 +2575,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484005</v>
+        <v>483899</v>
       </c>
       <c r="R16" t="n">
-        <v>6991716</v>
+        <v>6991685</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2613,7 +2610,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2623,12 +2620,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2642,17 +2634,17 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2673,7 +2665,7 @@
         <v>123176943</v>
       </c>
       <c r="B17" t="n">
-        <v>77702</v>
+        <v>77704</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2802,10 +2794,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123176616</v>
+        <v>123179132</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>90975</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2818,43 +2810,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483371</v>
+        <v>483553</v>
       </c>
       <c r="R18" t="n">
-        <v>6991602</v>
+        <v>6991669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2886,7 +2874,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2896,12 +2884,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2912,6 +2900,21 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2928,10 +2931,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123180336</v>
+        <v>123179071</v>
       </c>
       <c r="B19" t="n">
-        <v>79305</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2944,26 +2947,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2973,14 +2976,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483833</v>
+        <v>483575</v>
       </c>
       <c r="R19" t="n">
-        <v>6991771</v>
+        <v>6991710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3012,7 +3015,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3022,12 +3025,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3041,17 +3044,17 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -3069,10 +3072,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123180297</v>
+        <v>123184445</v>
       </c>
       <c r="B20" t="n">
-        <v>79879</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3081,41 +3084,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483829</v>
+        <v>483565</v>
       </c>
       <c r="R20" t="n">
-        <v>6991767</v>
+        <v>6991603</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3144,7 +3147,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3154,12 +3157,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3170,21 +3173,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3201,10 +3189,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123176924</v>
+        <v>123180336</v>
       </c>
       <c r="B21" t="n">
-        <v>74866</v>
+        <v>79307</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3217,34 +3205,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1352</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483383</v>
+        <v>483833</v>
       </c>
       <c r="R21" t="n">
-        <v>6991656</v>
+        <v>6991771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3276,7 +3273,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3286,12 +3283,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3305,17 +3302,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3333,10 +3330,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123179132</v>
+        <v>123176616</v>
       </c>
       <c r="B22" t="n">
-        <v>90973</v>
+        <v>78771</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3349,39 +3346,43 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483553</v>
+        <v>483371</v>
       </c>
       <c r="R22" t="n">
-        <v>6991669</v>
+        <v>6991602</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3413,7 +3414,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3423,12 +3424,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3439,21 +3440,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3470,10 +3456,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123181366</v>
+        <v>123177397</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3503,17 +3489,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483899</v>
+        <v>483605</v>
       </c>
       <c r="R23" t="n">
-        <v>6991685</v>
+        <v>6991834</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3545,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3555,7 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122709756</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123177015</v>
+        <v>123182555</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>79757</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1483,47 +1483,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483436</v>
+        <v>484005</v>
       </c>
       <c r="R8" t="n">
-        <v>6991677</v>
+        <v>6991716</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1556,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,17 +1575,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,10 +1603,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123176917</v>
+        <v>123176924</v>
       </c>
       <c r="B9" t="n">
-        <v>78771</v>
+        <v>74866</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,43 +1619,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483378</v>
+        <v>483383</v>
       </c>
       <c r="R9" t="n">
-        <v>6991654</v>
+        <v>6991656</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1696,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1706,12 +1688,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1753,10 +1735,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123182534</v>
+        <v>123177862</v>
       </c>
       <c r="B10" t="n">
-        <v>79852</v>
+        <v>74866</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1769,37 +1751,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>484029</v>
+        <v>483615</v>
       </c>
       <c r="R10" t="n">
-        <v>6991692</v>
+        <v>6991838</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1828,7 +1815,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1838,12 +1825,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1857,17 +1844,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1885,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123180297</v>
+        <v>123176943</v>
       </c>
       <c r="B11" t="n">
-        <v>79881</v>
+        <v>77705</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1897,41 +1884,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483829</v>
+        <v>483380</v>
       </c>
       <c r="R11" t="n">
-        <v>6991767</v>
+        <v>6991656</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1960,7 +1947,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1970,12 +1957,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2017,10 +2004,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123177862</v>
+        <v>123180336</v>
       </c>
       <c r="B12" t="n">
-        <v>74866</v>
+        <v>79308</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2033,42 +2020,46 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>1352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483615</v>
+        <v>483833</v>
       </c>
       <c r="R12" t="n">
-        <v>6991838</v>
+        <v>6991771</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2097,7 +2088,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2107,12 +2098,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2126,17 +2117,17 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2154,10 +2145,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123176924</v>
+        <v>123177015</v>
       </c>
       <c r="B13" t="n">
-        <v>74866</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2170,34 +2161,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483383</v>
+        <v>483436</v>
       </c>
       <c r="R13" t="n">
-        <v>6991656</v>
+        <v>6991677</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2229,7 +2229,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2286,10 +2286,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123182555</v>
+        <v>123176616</v>
       </c>
       <c r="B14" t="n">
-        <v>79756</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2298,38 +2298,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484005</v>
+        <v>483371</v>
       </c>
       <c r="R14" t="n">
-        <v>6991716</v>
+        <v>6991602</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2361,7 +2370,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2371,12 +2380,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2387,21 +2396,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2418,10 +2412,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123182989</v>
+        <v>123176917</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2451,17 +2445,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483820</v>
+        <v>483378</v>
       </c>
       <c r="R15" t="n">
-        <v>6991546</v>
+        <v>6991654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2493,7 +2496,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2503,12 +2506,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2519,6 +2522,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2535,10 +2553,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123181366</v>
+        <v>123180297</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>79882</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2547,25 +2565,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2575,13 +2593,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483899</v>
+        <v>483829</v>
       </c>
       <c r="R16" t="n">
-        <v>6991685</v>
+        <v>6991767</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2610,7 +2628,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2620,7 +2638,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2662,10 +2685,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123176943</v>
+        <v>123179071</v>
       </c>
       <c r="B17" t="n">
-        <v>77704</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2678,34 +2701,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483380</v>
+        <v>483575</v>
       </c>
       <c r="R17" t="n">
-        <v>6991656</v>
+        <v>6991710</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2737,7 +2769,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2747,12 +2779,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2794,10 +2826,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123179132</v>
+        <v>123182534</v>
       </c>
       <c r="B18" t="n">
-        <v>90975</v>
+        <v>79853</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2810,39 +2842,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483553</v>
+        <v>484029</v>
       </c>
       <c r="R18" t="n">
-        <v>6991669</v>
+        <v>6991692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2874,7 +2901,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2884,12 +2911,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2903,17 +2930,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2931,10 +2958,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123179071</v>
+        <v>123184445</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2964,26 +2991,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483575</v>
+        <v>483565</v>
       </c>
       <c r="R19" t="n">
-        <v>6991710</v>
+        <v>6991603</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3015,7 +3033,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3025,12 +3043,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3041,21 +3059,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3072,10 +3075,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123184445</v>
+        <v>123182989</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3112,10 +3115,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483565</v>
+        <v>483820</v>
       </c>
       <c r="R20" t="n">
-        <v>6991603</v>
+        <v>6991546</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3147,7 +3150,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3157,12 +3160,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3189,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123180336</v>
+        <v>123179132</v>
       </c>
       <c r="B21" t="n">
-        <v>79307</v>
+        <v>90981</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3205,43 +3208,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1352</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483833</v>
+        <v>483553</v>
       </c>
       <c r="R21" t="n">
-        <v>6991771</v>
+        <v>6991669</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3273,7 +3272,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3283,12 +3282,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3302,17 +3301,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3330,10 +3329,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123176616</v>
+        <v>123181366</v>
       </c>
       <c r="B22" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3363,26 +3362,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483371</v>
+        <v>483899</v>
       </c>
       <c r="R22" t="n">
-        <v>6991602</v>
+        <v>6991685</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3414,7 +3404,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3424,12 +3414,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3440,6 +3425,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3459,7 +3459,7 @@
         <v>123177397</v>
       </c>
       <c r="B23" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1337,7 +1337,7 @@
         <v>122709756</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123180336</v>
+        <v>123177397</v>
       </c>
       <c r="B8" t="n">
-        <v>79311</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,26 +1487,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1516,14 +1516,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483833</v>
+        <v>483605</v>
       </c>
       <c r="R8" t="n">
-        <v>6991771</v>
+        <v>6991834</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1612,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123181366</v>
+        <v>123184445</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1648,14 +1648,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483899</v>
+        <v>483565</v>
       </c>
       <c r="R9" t="n">
-        <v>6991685</v>
+        <v>6991603</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1687,7 +1687,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,7 +1697,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,21 +1713,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1739,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123179071</v>
+        <v>123181366</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1772,26 +1762,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483575</v>
+        <v>483899</v>
       </c>
       <c r="R10" t="n">
-        <v>6991710</v>
+        <v>6991685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1833,12 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1880,10 +1856,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123176917</v>
+        <v>123182534</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>79862</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1896,43 +1872,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483378</v>
+        <v>484029</v>
       </c>
       <c r="R11" t="n">
-        <v>6991654</v>
+        <v>6991692</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1964,7 +1931,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1974,12 +1941,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1993,17 +1960,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2021,10 +1988,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123182555</v>
+        <v>123176616</v>
       </c>
       <c r="B12" t="n">
-        <v>79760</v>
+        <v>78781</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2033,38 +2000,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484005</v>
+        <v>483371</v>
       </c>
       <c r="R12" t="n">
-        <v>6991716</v>
+        <v>6991602</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2096,7 +2072,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2106,12 +2082,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2122,21 +2098,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2153,10 +2114,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123182989</v>
+        <v>123176924</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2169,21 +2130,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2193,10 +2154,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483820</v>
+        <v>483383</v>
       </c>
       <c r="R13" t="n">
-        <v>6991546</v>
+        <v>6991656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2228,7 +2189,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2238,12 +2199,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2254,6 +2215,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2270,10 +2246,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123176943</v>
+        <v>123179132</v>
       </c>
       <c r="B14" t="n">
-        <v>77708</v>
+        <v>91001</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2286,34 +2262,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483380</v>
+        <v>483553</v>
       </c>
       <c r="R14" t="n">
-        <v>6991656</v>
+        <v>6991669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2345,7 +2326,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2355,12 +2336,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2402,10 +2383,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123182534</v>
+        <v>123176917</v>
       </c>
       <c r="B15" t="n">
-        <v>79856</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2418,34 +2399,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484029</v>
+        <v>483378</v>
       </c>
       <c r="R15" t="n">
-        <v>6991692</v>
+        <v>6991654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2477,7 +2467,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2487,12 +2477,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2506,17 +2496,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2534,10 +2524,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123180297</v>
+        <v>123177015</v>
       </c>
       <c r="B16" t="n">
-        <v>79885</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2546,41 +2536,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483829</v>
+        <v>483436</v>
       </c>
       <c r="R16" t="n">
-        <v>6991767</v>
+        <v>6991677</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2609,7 +2608,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2619,12 +2618,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2666,10 +2665,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123177862</v>
+        <v>123179071</v>
       </c>
       <c r="B17" t="n">
-        <v>74869</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2682,27 +2681,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2711,13 +2714,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483615</v>
+        <v>483575</v>
       </c>
       <c r="R17" t="n">
-        <v>6991838</v>
+        <v>6991710</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2746,7 +2749,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2756,12 +2759,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2803,10 +2806,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123177397</v>
+        <v>123176943</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>77714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2819,43 +2822,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483605</v>
+        <v>483380</v>
       </c>
       <c r="R18" t="n">
-        <v>6991834</v>
+        <v>6991656</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2887,7 +2881,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2897,12 +2891,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2944,10 +2938,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123177015</v>
+        <v>123182989</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2977,26 +2971,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483436</v>
+        <v>483820</v>
       </c>
       <c r="R19" t="n">
-        <v>6991677</v>
+        <v>6991546</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3028,7 +3013,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3038,12 +3023,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3054,21 +3039,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3085,10 +3055,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123176616</v>
+        <v>123177862</v>
       </c>
       <c r="B20" t="n">
-        <v>78775</v>
+        <v>74875</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3101,46 +3071,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483371</v>
+        <v>483615</v>
       </c>
       <c r="R20" t="n">
-        <v>6991602</v>
+        <v>6991838</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3169,7 +3135,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3179,12 +3145,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3195,6 +3161,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3211,10 +3192,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123184445</v>
+        <v>123180336</v>
       </c>
       <c r="B21" t="n">
-        <v>78775</v>
+        <v>79317</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3227,34 +3208,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483565</v>
+        <v>483833</v>
       </c>
       <c r="R21" t="n">
-        <v>6991603</v>
+        <v>6991771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3286,7 +3276,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3296,12 +3286,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3312,6 +3302,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3328,10 +3333,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123176924</v>
+        <v>123180297</v>
       </c>
       <c r="B22" t="n">
-        <v>74869</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3340,41 +3345,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483383</v>
+        <v>483829</v>
       </c>
       <c r="R22" t="n">
-        <v>6991656</v>
+        <v>6991767</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3403,7 +3408,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3413,12 +3418,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3460,10 +3465,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123179132</v>
+        <v>123182555</v>
       </c>
       <c r="B23" t="n">
-        <v>90984</v>
+        <v>79766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3472,43 +3477,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483553</v>
+        <v>484005</v>
       </c>
       <c r="R23" t="n">
-        <v>6991669</v>
+        <v>6991716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123177397</v>
+        <v>123177862</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>74878</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,31 +1487,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1520,13 +1516,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483605</v>
+        <v>483615</v>
       </c>
       <c r="R8" t="n">
-        <v>6991834</v>
+        <v>6991838</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1555,7 +1551,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1561,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1612,10 +1608,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123184445</v>
+        <v>123180297</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>79896</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1624,41 +1620,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483565</v>
+        <v>483829</v>
       </c>
       <c r="R9" t="n">
-        <v>6991603</v>
+        <v>6991767</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1687,7 +1683,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1697,12 +1693,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1713,6 +1709,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1729,10 +1740,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123181366</v>
+        <v>123176924</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>74878</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1745,34 +1756,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483899</v>
+        <v>483383</v>
       </c>
       <c r="R10" t="n">
-        <v>6991685</v>
+        <v>6991656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1815,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1825,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1856,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123182534</v>
+        <v>123176917</v>
       </c>
       <c r="B11" t="n">
-        <v>79862</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1872,34 +1888,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>484029</v>
+        <v>483378</v>
       </c>
       <c r="R11" t="n">
-        <v>6991692</v>
+        <v>6991654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1931,7 +1956,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1941,12 +1966,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1960,17 +1985,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1988,10 +2013,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123176616</v>
+        <v>123182534</v>
       </c>
       <c r="B12" t="n">
-        <v>78781</v>
+        <v>79867</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2004,43 +2029,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483371</v>
+        <v>484029</v>
       </c>
       <c r="R12" t="n">
-        <v>6991602</v>
+        <v>6991692</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2072,7 +2088,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2082,12 +2098,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2098,6 +2114,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2114,10 +2145,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123176924</v>
+        <v>123179132</v>
       </c>
       <c r="B13" t="n">
-        <v>74875</v>
+        <v>91006</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2130,34 +2161,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483383</v>
+        <v>483553</v>
       </c>
       <c r="R13" t="n">
-        <v>6991656</v>
+        <v>6991669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2225,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2199,12 +2235,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2246,10 +2282,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123179132</v>
+        <v>123180336</v>
       </c>
       <c r="B14" t="n">
-        <v>91001</v>
+        <v>79322</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2262,39 +2298,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>1352</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483553</v>
+        <v>483833</v>
       </c>
       <c r="R14" t="n">
-        <v>6991669</v>
+        <v>6991771</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2326,7 +2366,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2336,12 +2376,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2355,17 +2395,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2383,10 +2423,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123176917</v>
+        <v>123181366</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2416,26 +2456,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483378</v>
+        <v>483899</v>
       </c>
       <c r="R15" t="n">
-        <v>6991654</v>
+        <v>6991685</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2467,7 +2498,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2477,12 +2508,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2527,7 +2553,7 @@
         <v>123177015</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2665,10 +2691,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123179071</v>
+        <v>123177397</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2700,7 +2726,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2714,10 +2740,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483575</v>
+        <v>483605</v>
       </c>
       <c r="R17" t="n">
-        <v>6991710</v>
+        <v>6991834</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2749,7 +2775,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2759,12 +2785,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2809,7 +2835,7 @@
         <v>123176943</v>
       </c>
       <c r="B18" t="n">
-        <v>77714</v>
+        <v>77719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2938,10 +2964,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123182989</v>
+        <v>123179071</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2971,17 +2997,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483820</v>
+        <v>483575</v>
       </c>
       <c r="R19" t="n">
-        <v>6991546</v>
+        <v>6991710</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3013,7 +3048,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3023,7 +3058,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -3039,6 +3074,21 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -3055,10 +3105,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123177862</v>
+        <v>123184445</v>
       </c>
       <c r="B20" t="n">
-        <v>74875</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3071,42 +3121,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483615</v>
+        <v>483565</v>
       </c>
       <c r="R20" t="n">
-        <v>6991838</v>
+        <v>6991603</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3135,7 +3180,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3145,12 +3190,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3161,21 +3206,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3192,10 +3222,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123180336</v>
+        <v>123176616</v>
       </c>
       <c r="B21" t="n">
-        <v>79317</v>
+        <v>78786</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3208,26 +3238,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1352</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jatta</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3237,14 +3267,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483833</v>
+        <v>483371</v>
       </c>
       <c r="R21" t="n">
-        <v>6991771</v>
+        <v>6991602</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3276,7 +3306,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3286,12 +3316,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3302,21 +3332,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3333,10 +3348,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123180297</v>
+        <v>123182989</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>78786</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3345,41 +3360,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483829</v>
+        <v>483820</v>
       </c>
       <c r="R22" t="n">
-        <v>6991767</v>
+        <v>6991546</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3408,7 +3423,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3418,12 +3433,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3434,21 +3449,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3468,7 +3468,7 @@
         <v>123182555</v>
       </c>
       <c r="B23" t="n">
-        <v>79766</v>
+        <v>79771</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1471,10 +1471,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123177862</v>
+        <v>123176616</v>
       </c>
       <c r="B8" t="n">
-        <v>74878</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1487,42 +1487,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483615</v>
+        <v>483371</v>
       </c>
       <c r="R8" t="n">
-        <v>6991838</v>
+        <v>6991602</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1551,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1561,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1577,21 +1581,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1608,10 +1597,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123180297</v>
+        <v>123176943</v>
       </c>
       <c r="B9" t="n">
-        <v>79896</v>
+        <v>77721</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1620,41 +1609,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>228579</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483829</v>
+        <v>483380</v>
       </c>
       <c r="R9" t="n">
-        <v>6991767</v>
+        <v>6991656</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1683,7 +1672,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1693,12 +1682,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,10 +1729,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123176924</v>
+        <v>123177015</v>
       </c>
       <c r="B10" t="n">
-        <v>74878</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1756,34 +1745,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483383</v>
+        <v>483436</v>
       </c>
       <c r="R10" t="n">
-        <v>6991656</v>
+        <v>6991677</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1815,7 +1813,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1825,7 +1823,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1872,10 +1870,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123176917</v>
+        <v>123182989</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1905,26 +1903,17 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483378</v>
+        <v>483820</v>
       </c>
       <c r="R11" t="n">
-        <v>6991654</v>
+        <v>6991546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1956,7 +1945,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1966,12 +1955,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,21 +1971,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -2016,7 +1990,7 @@
         <v>123182534</v>
       </c>
       <c r="B12" t="n">
-        <v>79867</v>
+        <v>79869</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2145,10 +2119,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123179132</v>
+        <v>123180297</v>
       </c>
       <c r="B13" t="n">
-        <v>91006</v>
+        <v>79898</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2157,46 +2131,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483553</v>
+        <v>483829</v>
       </c>
       <c r="R13" t="n">
-        <v>6991669</v>
+        <v>6991767</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2225,7 +2194,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2235,12 +2204,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2285,7 +2254,7 @@
         <v>123180336</v>
       </c>
       <c r="B14" t="n">
-        <v>79322</v>
+        <v>79324</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2423,10 +2392,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123181366</v>
+        <v>123176917</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2456,17 +2425,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483899</v>
+        <v>483378</v>
       </c>
       <c r="R15" t="n">
-        <v>6991685</v>
+        <v>6991654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2498,7 +2476,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2508,7 +2486,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2550,10 +2533,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123177015</v>
+        <v>123179132</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>91008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2566,43 +2549,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483436</v>
+        <v>483553</v>
       </c>
       <c r="R16" t="n">
-        <v>6991677</v>
+        <v>6991669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2634,7 +2613,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2644,12 +2623,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2694,7 +2673,7 @@
         <v>123177397</v>
       </c>
       <c r="B17" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2832,10 +2811,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123176943</v>
+        <v>123179071</v>
       </c>
       <c r="B18" t="n">
-        <v>77719</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2848,34 +2827,43 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483380</v>
+        <v>483575</v>
       </c>
       <c r="R18" t="n">
-        <v>6991656</v>
+        <v>6991710</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2907,7 +2895,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2917,12 +2905,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2964,10 +2952,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123179071</v>
+        <v>123177862</v>
       </c>
       <c r="B19" t="n">
-        <v>78786</v>
+        <v>74879</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2980,31 +2968,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3013,13 +2997,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483575</v>
+        <v>483615</v>
       </c>
       <c r="R19" t="n">
-        <v>6991710</v>
+        <v>6991838</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3048,7 +3032,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3058,12 +3042,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3105,10 +3089,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123184445</v>
+        <v>123181366</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3141,14 +3125,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483565</v>
+        <v>483899</v>
       </c>
       <c r="R20" t="n">
-        <v>6991603</v>
+        <v>6991685</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3180,7 +3164,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3190,12 +3174,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3206,6 +3185,21 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3222,10 +3216,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123176616</v>
+        <v>123176924</v>
       </c>
       <c r="B21" t="n">
-        <v>78786</v>
+        <v>74879</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3238,43 +3232,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483371</v>
+        <v>483383</v>
       </c>
       <c r="R21" t="n">
-        <v>6991602</v>
+        <v>6991656</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3306,7 +3291,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3316,12 +3301,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3332,6 +3317,21 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3348,10 +3348,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123182989</v>
+        <v>123182555</v>
       </c>
       <c r="B22" t="n">
-        <v>78786</v>
+        <v>79773</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3360,38 +3360,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483820</v>
+        <v>484005</v>
       </c>
       <c r="R22" t="n">
-        <v>6991546</v>
+        <v>6991716</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3423,7 +3423,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3449,6 +3449,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3465,10 +3480,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123182555</v>
+        <v>123184445</v>
       </c>
       <c r="B23" t="n">
-        <v>79771</v>
+        <v>78788</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3477,38 +3492,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484005</v>
+        <v>483565</v>
       </c>
       <c r="R23" t="n">
-        <v>6991716</v>
+        <v>6991603</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3540,7 +3555,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3550,12 +3565,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3566,21 +3581,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -1471,7 +1471,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123176616</v>
+        <v>123177015</v>
       </c>
       <c r="B8" t="n">
         <v>78788</v>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483371</v>
+        <v>483436</v>
       </c>
       <c r="R8" t="n">
-        <v>6991602</v>
+        <v>6991677</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,6 +1581,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1597,10 +1612,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123176943</v>
+        <v>123177397</v>
       </c>
       <c r="B9" t="n">
-        <v>77721</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1613,34 +1628,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483380</v>
+        <v>483605</v>
       </c>
       <c r="R9" t="n">
-        <v>6991656</v>
+        <v>6991834</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1696,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1682,12 +1706,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1729,10 +1753,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123177015</v>
+        <v>123176924</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1745,43 +1769,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483436</v>
+        <v>483383</v>
       </c>
       <c r="R10" t="n">
-        <v>6991677</v>
+        <v>6991656</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1813,7 +1828,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1823,7 +1838,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1870,10 +1885,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123182989</v>
+        <v>123179132</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1886,34 +1901,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483820</v>
+        <v>483553</v>
       </c>
       <c r="R11" t="n">
-        <v>6991546</v>
+        <v>6991669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1945,7 +1965,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1955,12 +1975,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1971,6 +1991,21 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1987,10 +2022,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123182534</v>
+        <v>123182989</v>
       </c>
       <c r="B12" t="n">
-        <v>79869</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2003,34 +2038,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484029</v>
+        <v>483820</v>
       </c>
       <c r="R12" t="n">
-        <v>6991692</v>
+        <v>6991546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2062,7 +2097,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2072,12 +2107,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2088,21 +2123,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2119,10 +2139,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123180297</v>
+        <v>123176616</v>
       </c>
       <c r="B13" t="n">
-        <v>79898</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2131,41 +2151,50 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483829</v>
+        <v>483371</v>
       </c>
       <c r="R13" t="n">
-        <v>6991767</v>
+        <v>6991602</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2194,7 +2223,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2204,12 +2233,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2220,21 +2249,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2251,10 +2265,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123180336</v>
+        <v>123180297</v>
       </c>
       <c r="B14" t="n">
-        <v>79324</v>
+        <v>79898</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2263,50 +2277,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1352</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483833</v>
+        <v>483829</v>
       </c>
       <c r="R14" t="n">
-        <v>6991771</v>
+        <v>6991767</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2345,12 +2350,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2364,17 +2369,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2392,10 +2397,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123176917</v>
+        <v>123176943</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>77721</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2408,43 +2413,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483378</v>
+        <v>483380</v>
       </c>
       <c r="R15" t="n">
-        <v>6991654</v>
+        <v>6991656</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2476,7 +2472,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2486,12 +2482,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2533,10 +2529,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123179132</v>
+        <v>123184445</v>
       </c>
       <c r="B16" t="n">
-        <v>91008</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2549,39 +2545,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483553</v>
+        <v>483565</v>
       </c>
       <c r="R16" t="n">
-        <v>6991669</v>
+        <v>6991603</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2613,7 +2604,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2623,12 +2614,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2639,21 +2630,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2670,10 +2646,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123177397</v>
+        <v>123177862</v>
       </c>
       <c r="B17" t="n">
-        <v>78788</v>
+        <v>74879</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2686,31 +2662,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2719,13 +2691,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483605</v>
+        <v>483615</v>
       </c>
       <c r="R17" t="n">
-        <v>6991834</v>
+        <v>6991838</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2754,7 +2726,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2764,12 +2736,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2811,10 +2783,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123179071</v>
+        <v>123182534</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2827,43 +2799,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>483575</v>
+        <v>484029</v>
       </c>
       <c r="R18" t="n">
-        <v>6991710</v>
+        <v>6991692</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2895,7 +2858,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2905,12 +2868,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2924,17 +2887,17 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2952,10 +2915,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123177862</v>
+        <v>123181366</v>
       </c>
       <c r="B19" t="n">
-        <v>74879</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2968,42 +2931,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483615</v>
+        <v>483899</v>
       </c>
       <c r="R19" t="n">
-        <v>6991838</v>
+        <v>6991685</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -3032,7 +2990,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -3042,12 +3000,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3089,7 +3042,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123181366</v>
+        <v>123176917</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -3122,17 +3075,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483899</v>
+        <v>483378</v>
       </c>
       <c r="R20" t="n">
-        <v>6991685</v>
+        <v>6991654</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3164,7 +3126,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3174,7 +3136,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3216,10 +3183,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123176924</v>
+        <v>123180336</v>
       </c>
       <c r="B21" t="n">
-        <v>74879</v>
+        <v>79324</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3232,34 +3199,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>1352</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483383</v>
+        <v>483833</v>
       </c>
       <c r="R21" t="n">
-        <v>6991656</v>
+        <v>6991771</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3291,7 +3267,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3301,12 +3277,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3320,17 +3296,17 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3348,10 +3324,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123182555</v>
+        <v>123179071</v>
       </c>
       <c r="B22" t="n">
-        <v>79773</v>
+        <v>78788</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3360,38 +3336,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484005</v>
+        <v>483575</v>
       </c>
       <c r="R22" t="n">
-        <v>6991716</v>
+        <v>6991710</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3423,7 +3408,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3433,12 +3418,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3452,17 +3437,17 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3480,10 +3465,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123184445</v>
+        <v>123182555</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>79773</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3492,38 +3477,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>483565</v>
+        <v>484005</v>
       </c>
       <c r="R23" t="n">
-        <v>6991603</v>
+        <v>6991716</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3555,7 +3540,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3565,12 +3550,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog</t>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3581,6 +3566,21 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,6 +3595,6724 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128148746</v>
+      </c>
+      <c r="B24" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>483384</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6991763</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128146899</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>483803</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6991652</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128145243</v>
+      </c>
+      <c r="B26" t="n">
+        <v>92285</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>484061</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6991711</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128151830</v>
+      </c>
+      <c r="B27" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>483768</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6991562</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128151674</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>483639</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6991536</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128151907</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>483759</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6991515</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128148629</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92672</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>483486</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6991836</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128145822</v>
+      </c>
+      <c r="B31" t="n">
+        <v>90895</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>483907</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6991607</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128148843</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>483370</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6991758</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128148749</v>
+      </c>
+      <c r="B33" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>483384</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6991763</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128148801</v>
+      </c>
+      <c r="B34" t="n">
+        <v>92639</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1435</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bitter taggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hydnellum fennicum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>483378</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6991763</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128151242</v>
+      </c>
+      <c r="B35" t="n">
+        <v>88621</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>824</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skäggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hygrophorus inocybiformis</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>A.H.Sm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>483560</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6991627</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128146454</v>
+      </c>
+      <c r="B36" t="n">
+        <v>90880</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>483803</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6991669</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128153456</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97494</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222741</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Finbräken</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cystopteris montana</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>483832</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6991926</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128149062</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>483381</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6991732</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128151475</v>
+      </c>
+      <c r="B39" t="n">
+        <v>90895</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6991623</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128147638</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>483719</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6991835</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128145519</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100557</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>483943</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6991638</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128146450</v>
+      </c>
+      <c r="B42" t="n">
+        <v>91350</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>483803</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6991669</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128151646</v>
+      </c>
+      <c r="B43" t="n">
+        <v>88622</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>483638</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6991579</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128152204</v>
+      </c>
+      <c r="B44" t="n">
+        <v>88621</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>824</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Skäggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Hygrophorus inocybiformis</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>A.H.Sm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>483808</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6991708</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128147461</v>
+      </c>
+      <c r="B45" t="n">
+        <v>88622</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>483735</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6991823</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128148255</v>
+      </c>
+      <c r="B46" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>483625</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6991850</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128151897</v>
+      </c>
+      <c r="B47" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>483761</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6991506</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128146959</v>
+      </c>
+      <c r="B48" t="n">
+        <v>90813</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>483814</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6991692</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128151718</v>
+      </c>
+      <c r="B49" t="n">
+        <v>90872</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>483661</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6991539</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128149405</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>483367</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6991677</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128145589</v>
+      </c>
+      <c r="B51" t="n">
+        <v>92674</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>483946</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6991610</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128147670</v>
+      </c>
+      <c r="B52" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>483723</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6991850</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128151643</v>
+      </c>
+      <c r="B53" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>483638</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6991579</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128151407</v>
+      </c>
+      <c r="B54" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>483602</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6991610</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128151387</v>
+      </c>
+      <c r="B55" t="n">
+        <v>88621</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>824</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skäggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hygrophorus inocybiformis</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>A.H.Sm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>483598</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6991632</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128152853</v>
+      </c>
+      <c r="B56" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>483774</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6991911</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128148839</v>
+      </c>
+      <c r="B57" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>483370</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6991758</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128146291</v>
+      </c>
+      <c r="B58" t="n">
+        <v>90813</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3286</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Flattoppad klubbsvamp</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Clavariadelphus truncatus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>483855</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6991698</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128146254</v>
+      </c>
+      <c r="B59" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>483825</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6991736</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128148620</v>
+      </c>
+      <c r="B60" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>483486</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6991836</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128148828</v>
+      </c>
+      <c r="B61" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>483378</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6991763</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128145365</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92672</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1968</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Grantaggsvamp</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Phellodon violascens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>483955</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6991637</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128152970</v>
+      </c>
+      <c r="B63" t="n">
+        <v>90895</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>483774</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6991911</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128148761</v>
+      </c>
+      <c r="B64" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>483384</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6991763</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128145274</v>
+      </c>
+      <c r="B65" t="n">
+        <v>92302</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granriska</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Lactarius zonarioides</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kühner &amp; Romagn.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>484038</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6991684</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128148640</v>
+      </c>
+      <c r="B66" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>483483</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6991836</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128148616</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90885</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>233196</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Fjällfotad fingersvamp</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Ramaria rufescens</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Corner</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>483486</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6991836</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128146630</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>483783</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6991660</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128150949</v>
+      </c>
+      <c r="B69" t="n">
+        <v>92658</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>483503</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6991606</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128152208</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>483808</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6991708</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128151479</v>
+      </c>
+      <c r="B71" t="n">
+        <v>90848</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>5734</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Druvfingersvampar</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6991623</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128150924</v>
+      </c>
+      <c r="B72" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>483503</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6991606</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128151166</v>
+      </c>
+      <c r="B73" t="n">
+        <v>90872</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>256335</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Taggfingersvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>483551</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6991637</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>128146568</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86882</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>3624</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Strimspindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>483803</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6991669</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>128145502</v>
+      </c>
+      <c r="B75" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>483943</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6991638</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>128151611</v>
+      </c>
+      <c r="B76" t="n">
+        <v>90154</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Fjällfotad musseron</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Tricholoma olivaceotinctum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>483633</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6991596</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>128146085</v>
+      </c>
+      <c r="B77" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>483847</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6991688</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>128151367</v>
+      </c>
+      <c r="B78" t="n">
+        <v>89402</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>275</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kejsarskivling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Catathelasma imperiale</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Singer</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>483589</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6991633</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>128147310</v>
+      </c>
+      <c r="B79" t="n">
+        <v>88622</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>483747</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6991783</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128145310</v>
+      </c>
+      <c r="B80" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>484048</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6991644</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128145240</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>484061</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6991711</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128149279</v>
+      </c>
+      <c r="B82" t="n">
+        <v>89331</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>483326</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6991694</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128149429</v>
+      </c>
+      <c r="B83" t="n">
+        <v>88622</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>4412</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Äggvaxskivling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hygrophorus karstenii</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>483367</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6991677</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF83" t="inlineStr"/>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128149640</v>
+      </c>
+      <c r="B84" t="n">
+        <v>91470</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>3277</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Luddfingersvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lillhägnen, Lillhägnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>483366</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6991587</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128149500</v>
+      </c>
+      <c r="B85" t="n">
+        <v>90887</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5747</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Läderdoftande fingersvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>483377</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6991679</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>128149450</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>483377</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6991684</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>128149268</v>
+      </c>
+      <c r="B87" t="n">
+        <v>90154</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1599</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Fjällfotad musseron</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Tricholoma olivaceotinctum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483328</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991694</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128148746</v>
+        <v>128145243</v>
       </c>
       <c r="B24" t="n">
-        <v>92632</v>
+        <v>92285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4769</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483384</v>
+        <v>484061</v>
       </c>
       <c r="R24" t="n">
-        <v>6991763</v>
+        <v>6991711</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146899</v>
+        <v>128148746</v>
       </c>
       <c r="B25" t="n">
-        <v>91470</v>
+        <v>92632</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3714,34 +3714,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3277</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483803</v>
+        <v>483384</v>
       </c>
       <c r="R25" t="n">
-        <v>6991652</v>
+        <v>6991763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3782,6 +3785,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3805,32 +3809,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128145243</v>
+        <v>128151830</v>
       </c>
       <c r="B26" t="n">
-        <v>92285</v>
+        <v>90887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3839,14 +3843,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484061</v>
+        <v>483768</v>
       </c>
       <c r="R26" t="n">
-        <v>6991711</v>
+        <v>6991562</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3911,32 +3915,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151830</v>
+        <v>128151674</v>
       </c>
       <c r="B27" t="n">
-        <v>90887</v>
+        <v>92658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3949,10 +3953,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483768</v>
+        <v>483639</v>
       </c>
       <c r="R27" t="n">
-        <v>6991562</v>
+        <v>6991536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,10 +4021,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151674</v>
+        <v>128146899</v>
       </c>
       <c r="B28" t="n">
-        <v>92658</v>
+        <v>91470</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4028,37 +4032,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483639</v>
+        <v>483803</v>
       </c>
       <c r="R28" t="n">
-        <v>6991536</v>
+        <v>6991652</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4099,7 +4100,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B29" t="n">
-        <v>92632</v>
+        <v>91368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4157,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R29" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B30" t="n">
-        <v>92672</v>
+        <v>90895</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,37 +4240,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R30" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,7 +4308,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128151907</v>
       </c>
       <c r="B31" t="n">
-        <v>90895</v>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4342,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483759</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4413,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B32" t="n">
-        <v>91368</v>
+        <v>92672</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R32" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128151475</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>90895</v>
+        <v>92632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5219,14 +5219,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483615</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991623</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,10 +5291,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128147638</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>92632</v>
+        <v>90895</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5302,21 +5302,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5325,14 +5325,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483719</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991835</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5397,32 +5397,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128145519</v>
+        <v>128146450</v>
       </c>
       <c r="B41" t="n">
-        <v>100557</v>
+        <v>91350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483943</v>
+        <v>483803</v>
       </c>
       <c r="R41" t="n">
-        <v>6991638</v>
+        <v>6991669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>91350</v>
+        <v>100557</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,32 +5601,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128151646</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88622</v>
+        <v>88621</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5635,14 +5635,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483638</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991579</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5707,32 +5707,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128152204</v>
+        <v>128151646</v>
       </c>
       <c r="B44" t="n">
-        <v>88621</v>
+        <v>88622</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5741,14 +5741,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483808</v>
+        <v>483638</v>
       </c>
       <c r="R44" t="n">
-        <v>6991708</v>
+        <v>6991579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6861,32 +6861,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128151387</v>
+        <v>128148839</v>
       </c>
       <c r="B55" t="n">
-        <v>88621</v>
+        <v>92658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>824</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,14 +6895,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483598</v>
+        <v>483370</v>
       </c>
       <c r="R55" t="n">
-        <v>6991632</v>
+        <v>6991758</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6967,48 +6967,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B56" t="n">
-        <v>91368</v>
+        <v>90887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R56" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7049,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7073,32 +7069,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128148839</v>
+        <v>128151387</v>
       </c>
       <c r="B57" t="n">
-        <v>92658</v>
+        <v>88621</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>824</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7107,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483370</v>
+        <v>483598</v>
       </c>
       <c r="R57" t="n">
-        <v>6991758</v>
+        <v>6991632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7179,10 +7175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128146291</v>
+        <v>128152853</v>
       </c>
       <c r="B58" t="n">
-        <v>90813</v>
+        <v>91368</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7190,34 +7186,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483855</v>
+        <v>483774</v>
       </c>
       <c r="R58" t="n">
-        <v>6991698</v>
+        <v>6991911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7258,6 +7257,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7281,32 +7281,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128146291</v>
       </c>
       <c r="B59" t="n">
-        <v>90887</v>
+        <v>90813</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483855</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991698</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>92658</v>
+        <v>92302</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R64" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,32 +7909,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128145274</v>
+        <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>92302</v>
+        <v>91368</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7943,14 +7943,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484038</v>
+        <v>483483</v>
       </c>
       <c r="R65" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148640</v>
+        <v>128148761</v>
       </c>
       <c r="B66" t="n">
-        <v>91368</v>
+        <v>92658</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483483</v>
+        <v>483384</v>
       </c>
       <c r="R66" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8227,34 +8227,30 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128146630</v>
+        <v>128146568</v>
       </c>
       <c r="B68" t="n">
-        <v>90887</v>
+        <v>86882</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5747</v>
+        <v>3624</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8262,10 +8258,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483783</v>
+        <v>483803</v>
       </c>
       <c r="R68" t="n">
-        <v>6991660</v>
+        <v>6991669</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8329,10 +8325,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128150949</v>
+        <v>128151479</v>
       </c>
       <c r="B69" t="n">
-        <v>92658</v>
+        <v>90848</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,37 +8336,33 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4368</v>
+        <v>5734</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483503</v>
+        <v>483615</v>
       </c>
       <c r="R69" t="n">
-        <v>6991606</v>
+        <v>6991623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8435,10 +8427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128152208</v>
+        <v>128150924</v>
       </c>
       <c r="B70" t="n">
-        <v>91470</v>
+        <v>91368</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8446,21 +8438,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3277</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8469,14 +8461,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483808</v>
+        <v>483503</v>
       </c>
       <c r="R70" t="n">
-        <v>6991708</v>
+        <v>6991606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8541,10 +8533,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128151479</v>
+        <v>128150949</v>
       </c>
       <c r="B71" t="n">
-        <v>90848</v>
+        <v>92658</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8552,33 +8544,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5734</v>
+        <v>4368</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483615</v>
+        <v>483503</v>
       </c>
       <c r="R71" t="n">
-        <v>6991623</v>
+        <v>6991606</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8643,10 +8639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128150924</v>
+        <v>128152208</v>
       </c>
       <c r="B72" t="n">
-        <v>91368</v>
+        <v>91470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8654,21 +8650,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>3277</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8677,14 +8673,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R72" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8855,30 +8851,34 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146568</v>
+        <v>128146630</v>
       </c>
       <c r="B74" t="n">
-        <v>86882</v>
+        <v>90887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3624</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483803</v>
+        <v>483783</v>
       </c>
       <c r="R74" t="n">
-        <v>6991669</v>
+        <v>6991660</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9369,32 +9369,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128147310</v>
+        <v>128145310</v>
       </c>
       <c r="B79" t="n">
-        <v>88622</v>
+        <v>90887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9404,10 +9404,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>483747</v>
+        <v>484048</v>
       </c>
       <c r="R79" t="n">
-        <v>6991783</v>
+        <v>6991644</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9471,32 +9471,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128145310</v>
+        <v>128147310</v>
       </c>
       <c r="B80" t="n">
-        <v>90887</v>
+        <v>88622</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5747</v>
+        <v>4412</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9506,10 +9506,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>484048</v>
+        <v>483747</v>
       </c>
       <c r="R80" t="n">
-        <v>6991644</v>
+        <v>6991783</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128145243</v>
+        <v>128151674</v>
       </c>
       <c r="B24" t="n">
-        <v>92285</v>
+        <v>92659</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484061</v>
+        <v>483639</v>
       </c>
       <c r="R24" t="n">
-        <v>6991711</v>
+        <v>6991536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128148746</v>
+        <v>128151830</v>
       </c>
       <c r="B25" t="n">
-        <v>92632</v>
+        <v>90888</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3737,14 +3737,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483384</v>
+        <v>483768</v>
       </c>
       <c r="R25" t="n">
-        <v>6991763</v>
+        <v>6991562</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,32 +3809,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128151830</v>
+        <v>128148746</v>
       </c>
       <c r="B26" t="n">
-        <v>90887</v>
+        <v>92633</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3843,14 +3843,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483768</v>
+        <v>483384</v>
       </c>
       <c r="R26" t="n">
-        <v>6991562</v>
+        <v>6991763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3915,32 +3915,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B27" t="n">
-        <v>92658</v>
+        <v>92286</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3949,14 +3949,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R27" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4024,7 +4024,7 @@
         <v>128146899</v>
       </c>
       <c r="B28" t="n">
-        <v>91470</v>
+        <v>91471</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>91368</v>
+        <v>92673</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128145822</v>
+        <v>128151907</v>
       </c>
       <c r="B30" t="n">
-        <v>90895</v>
+        <v>92633</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,34 +4240,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483907</v>
+        <v>483759</v>
       </c>
       <c r="R30" t="n">
-        <v>6991607</v>
+        <v>6991515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4308,6 +4311,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128151907</v>
+        <v>128145822</v>
       </c>
       <c r="B31" t="n">
-        <v>92632</v>
+        <v>90896</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,37 +4346,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483759</v>
+        <v>483907</v>
       </c>
       <c r="R31" t="n">
-        <v>6991515</v>
+        <v>6991607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4413,7 +4414,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148629</v>
+        <v>128148843</v>
       </c>
       <c r="B32" t="n">
-        <v>92672</v>
+        <v>91369</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1968</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483486</v>
+        <v>483370</v>
       </c>
       <c r="R32" t="n">
-        <v>6991836</v>
+        <v>6991758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4546,7 +4546,7 @@
         <v>128148749</v>
       </c>
       <c r="B33" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148801</v>
       </c>
       <c r="B34" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88621</v>
+        <v>90881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90880</v>
+        <v>88622</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4975,7 +4975,7 @@
         <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>97494</v>
+        <v>97495</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>90887</v>
+        <v>90888</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128151475</v>
       </c>
       <c r="B39" t="n">
-        <v>92632</v>
+        <v>90896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5219,14 +5219,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483615</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991623</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>90895</v>
+        <v>100558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5397,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B41" t="n">
-        <v>91350</v>
+        <v>92633</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5408,34 +5404,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R41" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5476,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128146450</v>
       </c>
       <c r="B42" t="n">
-        <v>100557</v>
+        <v>91351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483803</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,48 +5601,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128147461</v>
       </c>
       <c r="B43" t="n">
-        <v>88621</v>
+        <v>88623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483735</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991823</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5683,7 +5680,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5707,10 +5703,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128151646</v>
+        <v>128148255</v>
       </c>
       <c r="B44" t="n">
-        <v>88622</v>
+        <v>92635</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5718,21 +5714,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5741,14 +5737,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483638</v>
+        <v>483625</v>
       </c>
       <c r="R44" t="n">
-        <v>6991579</v>
+        <v>6991850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5813,10 +5809,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128147461</v>
+        <v>128151646</v>
       </c>
       <c r="B45" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5842,16 +5838,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483735</v>
+        <v>483638</v>
       </c>
       <c r="R45" t="n">
-        <v>6991823</v>
+        <v>6991579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5892,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5915,32 +5915,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128148255</v>
+        <v>128152204</v>
       </c>
       <c r="B46" t="n">
-        <v>92634</v>
+        <v>88622</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>824</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483625</v>
+        <v>483808</v>
       </c>
       <c r="R46" t="n">
-        <v>6991850</v>
+        <v>6991708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6024,7 +6024,7 @@
         <v>128151897</v>
       </c>
       <c r="B47" t="n">
-        <v>92658</v>
+        <v>92659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6127,45 +6127,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B48" t="n">
-        <v>90813</v>
+        <v>90873</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6209,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6229,48 +6233,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B49" t="n">
-        <v>90872</v>
+        <v>90814</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R49" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6311,7 +6312,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6335,48 +6335,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B50" t="n">
-        <v>91470</v>
+        <v>92675</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R50" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6417,7 +6414,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6441,45 +6437,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B51" t="n">
-        <v>92674</v>
+        <v>90888</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,6 +6519,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128149405</v>
       </c>
       <c r="B52" t="n">
-        <v>90887</v>
+        <v>91471</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6577,14 +6577,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483367</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991677</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>92632</v>
+        <v>90888</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>90887</v>
+        <v>92633</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R54" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6861,32 +6861,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128148839</v>
+        <v>128151387</v>
       </c>
       <c r="B55" t="n">
-        <v>92658</v>
+        <v>88622</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>824</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,14 +6895,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483370</v>
+        <v>483598</v>
       </c>
       <c r="R55" t="n">
-        <v>6991758</v>
+        <v>6991632</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6967,45 +6967,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B56" t="n">
-        <v>90887</v>
+        <v>91369</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R56" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7049,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,32 +7073,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128151387</v>
+        <v>128148839</v>
       </c>
       <c r="B57" t="n">
-        <v>88621</v>
+        <v>92659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>824</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7103,14 +7107,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483598</v>
+        <v>483370</v>
       </c>
       <c r="R57" t="n">
-        <v>6991632</v>
+        <v>6991758</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,48 +7179,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B58" t="n">
-        <v>91368</v>
+        <v>90888</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R58" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7257,7 +7258,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>128146291</v>
       </c>
       <c r="B59" t="n">
-        <v>90813</v>
+        <v>90814</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>128148620</v>
       </c>
       <c r="B60" t="n">
-        <v>90887</v>
+        <v>90888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>90887</v>
+        <v>90888</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128145365</v>
       </c>
       <c r="B62" t="n">
-        <v>92672</v>
+        <v>92673</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>128152970</v>
       </c>
       <c r="B63" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128145274</v>
+        <v>128148616</v>
       </c>
       <c r="B64" t="n">
-        <v>92302</v>
+        <v>90886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4787</v>
+        <v>233196</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484038</v>
+        <v>483486</v>
       </c>
       <c r="R64" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,32 +7909,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148640</v>
+        <v>128145274</v>
       </c>
       <c r="B65" t="n">
-        <v>91368</v>
+        <v>92303</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>4787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7943,14 +7943,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483483</v>
+        <v>484038</v>
       </c>
       <c r="R65" t="n">
-        <v>6991836</v>
+        <v>6991684</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148761</v>
+        <v>128148640</v>
       </c>
       <c r="B66" t="n">
-        <v>92658</v>
+        <v>91369</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483384</v>
+        <v>483483</v>
       </c>
       <c r="R66" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,32 +8121,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128148616</v>
+        <v>128148761</v>
       </c>
       <c r="B67" t="n">
-        <v>90885</v>
+        <v>92659</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>233196</v>
+        <v>4368</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8159,10 +8159,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483486</v>
+        <v>483384</v>
       </c>
       <c r="R67" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8227,41 +8227,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128146568</v>
+        <v>128150949</v>
       </c>
       <c r="B68" t="n">
-        <v>86882</v>
+        <v>92659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3624</v>
+        <v>4368</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483803</v>
+        <v>483503</v>
       </c>
       <c r="R68" t="n">
-        <v>6991669</v>
+        <v>6991606</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8302,6 +8309,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8328,7 +8336,7 @@
         <v>128151479</v>
       </c>
       <c r="B69" t="n">
-        <v>90848</v>
+        <v>90849</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8430,7 +8438,7 @@
         <v>128150924</v>
       </c>
       <c r="B70" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8533,10 +8541,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128150949</v>
+        <v>128152208</v>
       </c>
       <c r="B71" t="n">
-        <v>92658</v>
+        <v>91471</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8544,21 +8552,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8567,14 +8575,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R71" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8639,32 +8647,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128152208</v>
+        <v>128151166</v>
       </c>
       <c r="B72" t="n">
-        <v>91470</v>
+        <v>90873</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3277</v>
+        <v>256335</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8673,14 +8681,14 @@
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483808</v>
+        <v>483551</v>
       </c>
       <c r="R72" t="n">
-        <v>6991708</v>
+        <v>6991637</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8745,10 +8753,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128151166</v>
+        <v>128146630</v>
       </c>
       <c r="B73" t="n">
-        <v>90872</v>
+        <v>90888</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8756,37 +8764,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>256335</v>
+        <v>5747</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483551</v>
+        <v>483783</v>
       </c>
       <c r="R73" t="n">
-        <v>6991637</v>
+        <v>6991660</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8827,7 +8832,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8851,34 +8855,30 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146630</v>
+        <v>128146568</v>
       </c>
       <c r="B74" t="n">
-        <v>90887</v>
+        <v>86883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>3624</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8886,10 +8886,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483783</v>
+        <v>483803</v>
       </c>
       <c r="R74" t="n">
-        <v>6991660</v>
+        <v>6991669</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8956,7 +8956,7 @@
         <v>128145502</v>
       </c>
       <c r="B75" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9055,10 +9055,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B76" t="n">
-        <v>90154</v>
+        <v>90888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9066,37 +9066,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R76" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9137,7 +9134,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9161,10 +9157,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B77" t="n">
-        <v>90887</v>
+        <v>90155</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9172,34 +9168,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R77" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9240,6 +9239,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>89402</v>
+        <v>89403</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>128145310</v>
       </c>
       <c r="B79" t="n">
-        <v>90887</v>
+        <v>90888</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>128147310</v>
       </c>
       <c r="B80" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128145240</v>
       </c>
       <c r="B81" t="n">
-        <v>91470</v>
+        <v>91471</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149279</v>
       </c>
       <c r="B82" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149429</v>
       </c>
       <c r="B83" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149640</v>
       </c>
       <c r="B84" t="n">
-        <v>91470</v>
+        <v>91471</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149500</v>
       </c>
       <c r="B85" t="n">
-        <v>90887</v>
+        <v>90888</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128149450</v>
       </c>
       <c r="B86" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128149268</v>
       </c>
       <c r="B87" t="n">
-        <v>90154</v>
+        <v>90155</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,10 +3597,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128151674</v>
+        <v>128148746</v>
       </c>
       <c r="B24" t="n">
-        <v>92659</v>
+        <v>92634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,21 +3608,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483639</v>
+        <v>483384</v>
       </c>
       <c r="R24" t="n">
-        <v>6991536</v>
+        <v>6991763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128151830</v>
+        <v>128151674</v>
       </c>
       <c r="B25" t="n">
-        <v>90888</v>
+        <v>92660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3741,10 +3741,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483768</v>
+        <v>483639</v>
       </c>
       <c r="R25" t="n">
-        <v>6991562</v>
+        <v>6991536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B26" t="n">
-        <v>92633</v>
+        <v>91472</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3820,37 +3820,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R26" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3891,7 +3888,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3918,7 +3914,7 @@
         <v>128145243</v>
       </c>
       <c r="B27" t="n">
-        <v>92286</v>
+        <v>92287</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4021,45 +4017,48 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128146899</v>
+        <v>128151830</v>
       </c>
       <c r="B28" t="n">
-        <v>91471</v>
+        <v>90889</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483803</v>
+        <v>483768</v>
       </c>
       <c r="R28" t="n">
-        <v>6991652</v>
+        <v>6991562</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4100,6 +4099,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -4126,7 +4126,7 @@
         <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128151907</v>
+        <v>128145822</v>
       </c>
       <c r="B30" t="n">
-        <v>92633</v>
+        <v>90897</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,37 +4240,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483759</v>
+        <v>483907</v>
       </c>
       <c r="R30" t="n">
-        <v>6991515</v>
+        <v>6991607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,7 +4308,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>90896</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4342,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4413,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148843</v>
+        <v>128151907</v>
       </c>
       <c r="B32" t="n">
-        <v>91369</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483370</v>
+        <v>483759</v>
       </c>
       <c r="R32" t="n">
-        <v>6991758</v>
+        <v>6991515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4546,7 +4546,7 @@
         <v>128148749</v>
       </c>
       <c r="B33" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148801</v>
       </c>
       <c r="B34" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>90881</v>
+        <v>88623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,32 +4861,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>88622</v>
+        <v>90882</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4900,14 +4895,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4940,6 +4935,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,49 +4972,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B37" t="n">
-        <v>97495</v>
+        <v>90889</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,48 +5078,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B38" t="n">
-        <v>90888</v>
+        <v>97496</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5188,7 +5188,7 @@
         <v>128151475</v>
       </c>
       <c r="B39" t="n">
-        <v>90896</v>
+        <v>90897</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5291,45 +5291,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B40" t="n">
-        <v>100558</v>
+        <v>92634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5373,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5397,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B41" t="n">
-        <v>92633</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,37 +5408,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R41" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5476,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>91351</v>
+        <v>100559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5604,7 +5604,7 @@
         <v>128147461</v>
       </c>
       <c r="B43" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128148255</v>
       </c>
       <c r="B44" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5812,7 +5812,7 @@
         <v>128151646</v>
       </c>
       <c r="B45" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>128152204</v>
       </c>
       <c r="B46" t="n">
-        <v>88622</v>
+        <v>88623</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6021,32 +6021,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151897</v>
+        <v>128151718</v>
       </c>
       <c r="B47" t="n">
-        <v>92659</v>
+        <v>90874</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>256335</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483761</v>
+        <v>483661</v>
       </c>
       <c r="R47" t="n">
-        <v>6991506</v>
+        <v>6991539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6127,32 +6127,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151718</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90873</v>
+        <v>92660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>256335</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483661</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991539</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6236,7 +6236,7 @@
         <v>128146959</v>
       </c>
       <c r="B49" t="n">
-        <v>90814</v>
+        <v>90815</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6335,45 +6335,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128145589</v>
+        <v>128149405</v>
       </c>
       <c r="B50" t="n">
-        <v>92675</v>
+        <v>91472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>3277</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483946</v>
+        <v>483367</v>
       </c>
       <c r="R50" t="n">
-        <v>6991610</v>
+        <v>6991677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,6 +6417,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6440,7 +6444,7 @@
         <v>128147670</v>
       </c>
       <c r="B51" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6543,48 +6547,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B52" t="n">
-        <v>91471</v>
+        <v>92676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R52" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6625,7 +6626,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,48 +6861,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128151387</v>
+        <v>128146291</v>
       </c>
       <c r="B55" t="n">
-        <v>88622</v>
+        <v>90815</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>824</v>
+        <v>3286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483598</v>
+        <v>483855</v>
       </c>
       <c r="R55" t="n">
-        <v>6991632</v>
+        <v>6991698</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6943,7 +6940,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6967,10 +6963,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128152853</v>
+        <v>128148839</v>
       </c>
       <c r="B56" t="n">
-        <v>91369</v>
+        <v>92660</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,21 +6974,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7001,14 +6997,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483774</v>
+        <v>483370</v>
       </c>
       <c r="R56" t="n">
-        <v>6991911</v>
+        <v>6991758</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7073,10 +7069,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128148839</v>
+        <v>128152853</v>
       </c>
       <c r="B57" t="n">
-        <v>92659</v>
+        <v>91370</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7084,21 +7080,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7107,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483370</v>
+        <v>483774</v>
       </c>
       <c r="R57" t="n">
-        <v>6991758</v>
+        <v>6991911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7182,7 +7178,7 @@
         <v>128146254</v>
       </c>
       <c r="B58" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7281,45 +7277,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B59" t="n">
-        <v>90814</v>
+        <v>88623</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R59" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7360,6 +7359,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>128148620</v>
       </c>
       <c r="B60" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         <v>128145365</v>
       </c>
       <c r="B62" t="n">
-        <v>92673</v>
+        <v>92674</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128152970</v>
+        <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>90896</v>
+        <v>92304</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5754</v>
+        <v>4787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483774</v>
+        <v>484038</v>
       </c>
       <c r="R63" t="n">
-        <v>6991911</v>
+        <v>6991684</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148616</v>
+        <v>128148640</v>
       </c>
       <c r="B64" t="n">
-        <v>90886</v>
+        <v>91370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>233196</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7841,7 +7841,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483486</v>
+        <v>483483</v>
       </c>
       <c r="R64" t="n">
         <v>6991836</v>
@@ -7909,32 +7909,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128145274</v>
+        <v>128152970</v>
       </c>
       <c r="B65" t="n">
-        <v>92303</v>
+        <v>90897</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4787</v>
+        <v>5754</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484038</v>
+        <v>483774</v>
       </c>
       <c r="R65" t="n">
-        <v>6991684</v>
+        <v>6991911</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148640</v>
+        <v>128148761</v>
       </c>
       <c r="B66" t="n">
-        <v>91369</v>
+        <v>92660</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8053,10 +8053,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483483</v>
+        <v>483384</v>
       </c>
       <c r="R66" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,32 +8121,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128148761</v>
+        <v>128148616</v>
       </c>
       <c r="B67" t="n">
-        <v>92659</v>
+        <v>90887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4368</v>
+        <v>233196</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8159,10 +8159,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483384</v>
+        <v>483486</v>
       </c>
       <c r="R67" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8230,7 +8230,7 @@
         <v>128150949</v>
       </c>
       <c r="B68" t="n">
-        <v>92659</v>
+        <v>92660</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8333,10 +8333,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128151479</v>
+        <v>128152208</v>
       </c>
       <c r="B69" t="n">
-        <v>90849</v>
+        <v>91472</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,33 +8344,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5734</v>
+        <v>3277</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483615</v>
+        <v>483808</v>
       </c>
       <c r="R69" t="n">
-        <v>6991623</v>
+        <v>6991708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8435,48 +8439,41 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150924</v>
+        <v>128146568</v>
       </c>
       <c r="B70" t="n">
-        <v>91369</v>
+        <v>86884</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>3624</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483503</v>
+        <v>483803</v>
       </c>
       <c r="R70" t="n">
-        <v>6991606</v>
+        <v>6991669</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8517,7 +8514,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8541,10 +8537,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128152208</v>
+        <v>128151479</v>
       </c>
       <c r="B71" t="n">
-        <v>91471</v>
+        <v>90850</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8552,37 +8548,33 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3277</v>
+        <v>5734</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483808</v>
+        <v>483615</v>
       </c>
       <c r="R71" t="n">
-        <v>6991708</v>
+        <v>6991623</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8647,10 +8639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128151166</v>
+        <v>128146630</v>
       </c>
       <c r="B72" t="n">
-        <v>90873</v>
+        <v>90889</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8658,37 +8650,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>256335</v>
+        <v>5747</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483551</v>
+        <v>483783</v>
       </c>
       <c r="R72" t="n">
-        <v>6991637</v>
+        <v>6991660</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8729,7 +8718,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8753,45 +8741,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128146630</v>
+        <v>128150924</v>
       </c>
       <c r="B73" t="n">
-        <v>90888</v>
+        <v>91370</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483783</v>
+        <v>483503</v>
       </c>
       <c r="R73" t="n">
-        <v>6991660</v>
+        <v>6991606</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8832,6 +8823,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8855,41 +8847,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146568</v>
+        <v>128151166</v>
       </c>
       <c r="B74" t="n">
-        <v>86883</v>
+        <v>90874</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>3624</v>
+        <v>256335</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>Ramaria karstenii</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483803</v>
+        <v>483551</v>
       </c>
       <c r="R74" t="n">
-        <v>6991669</v>
+        <v>6991637</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8930,6 +8929,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8956,7 +8956,7 @@
         <v>128145502</v>
       </c>
       <c r="B75" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9055,10 +9055,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B76" t="n">
-        <v>90888</v>
+        <v>90156</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9066,34 +9066,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R76" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9134,6 +9137,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9157,10 +9161,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B77" t="n">
-        <v>90155</v>
+        <v>90889</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9168,37 +9172,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R77" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9239,7 +9240,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9266,7 +9266,7 @@
         <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>89403</v>
+        <v>89404</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         <v>128145310</v>
       </c>
       <c r="B79" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>128147310</v>
       </c>
       <c r="B80" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128145240</v>
       </c>
       <c r="B81" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149279</v>
       </c>
       <c r="B82" t="n">
-        <v>89332</v>
+        <v>89333</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149429</v>
       </c>
       <c r="B83" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149640</v>
       </c>
       <c r="B84" t="n">
-        <v>91471</v>
+        <v>91472</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149500</v>
       </c>
       <c r="B85" t="n">
-        <v>90888</v>
+        <v>90889</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128149450</v>
       </c>
       <c r="B86" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128149268</v>
       </c>
       <c r="B87" t="n">
-        <v>90155</v>
+        <v>90156</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,10 +3597,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B24" t="n">
-        <v>92634</v>
+        <v>91472</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,37 +3608,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R24" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3676,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3703,32 +3699,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B25" t="n">
-        <v>92660</v>
+        <v>92287</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3737,14 +3733,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R25" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,10 +3805,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146899</v>
+        <v>128148746</v>
       </c>
       <c r="B26" t="n">
-        <v>91472</v>
+        <v>92634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3820,34 +3816,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3277</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483803</v>
+        <v>483384</v>
       </c>
       <c r="R26" t="n">
-        <v>6991652</v>
+        <v>6991763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3888,6 +3887,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128145243</v>
+        <v>128151674</v>
       </c>
       <c r="B27" t="n">
-        <v>92287</v>
+        <v>92660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3945,14 +3945,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484061</v>
+        <v>483639</v>
       </c>
       <c r="R27" t="n">
-        <v>6991711</v>
+        <v>6991536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B30" t="n">
-        <v>90897</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,34 +4240,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R30" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4308,6 +4311,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148843</v>
+        <v>128145822</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>90897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,37 +4346,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483370</v>
+        <v>483907</v>
       </c>
       <c r="R31" t="n">
-        <v>6991758</v>
+        <v>6991607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4413,7 +4414,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4543,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128148749</v>
+        <v>128148801</v>
       </c>
       <c r="B33" t="n">
-        <v>92636</v>
+        <v>92641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483384</v>
+        <v>483378</v>
       </c>
       <c r="R33" t="n">
         <v>6991763</v>
@@ -4649,32 +4649,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128148801</v>
+        <v>128148749</v>
       </c>
       <c r="B34" t="n">
-        <v>92641</v>
+        <v>92636</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1435</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483378</v>
+        <v>483384</v>
       </c>
       <c r="R34" t="n">
         <v>6991763</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88623</v>
+        <v>90882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90882</v>
+        <v>88623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128151475</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>90897</v>
+        <v>92634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5219,14 +5219,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483615</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991623</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128147638</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>92634</v>
+        <v>100559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483719</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991835</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5499,45 +5495,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B42" t="n">
-        <v>100559</v>
+        <v>90897</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,45 +5601,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128147461</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88624</v>
+        <v>88623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483735</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991823</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5680,6 +5683,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5703,10 +5707,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128148255</v>
+        <v>128147461</v>
       </c>
       <c r="B44" t="n">
-        <v>92636</v>
+        <v>88624</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5714,37 +5718,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483625</v>
+        <v>483735</v>
       </c>
       <c r="R44" t="n">
-        <v>6991850</v>
+        <v>6991823</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5785,7 +5786,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5915,32 +5915,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128152204</v>
+        <v>128148255</v>
       </c>
       <c r="B46" t="n">
-        <v>88623</v>
+        <v>92636</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>824</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483808</v>
+        <v>483625</v>
       </c>
       <c r="R46" t="n">
-        <v>6991708</v>
+        <v>6991850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,48 +6021,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>90874</v>
+        <v>90815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6233,45 +6229,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B49" t="n">
-        <v>90815</v>
+        <v>90874</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R49" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6312,6 +6311,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6861,45 +6861,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B55" t="n">
-        <v>90815</v>
+        <v>88623</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R55" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6940,6 +6943,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6963,10 +6967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128148839</v>
+        <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>92660</v>
+        <v>90815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6974,37 +6978,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483370</v>
+        <v>483855</v>
       </c>
       <c r="R56" t="n">
-        <v>6991758</v>
+        <v>6991698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7045,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128152853</v>
+        <v>128148839</v>
       </c>
       <c r="B57" t="n">
-        <v>91370</v>
+        <v>92660</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7080,21 +7080,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7103,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483774</v>
+        <v>483370</v>
       </c>
       <c r="R57" t="n">
-        <v>6991911</v>
+        <v>6991758</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,45 +7175,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B58" t="n">
-        <v>90889</v>
+        <v>91370</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R58" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7254,6 +7257,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7277,10 +7281,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128151387</v>
+        <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>88623</v>
+        <v>90889</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7288,37 +7292,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>824</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483598</v>
+        <v>483825</v>
       </c>
       <c r="R59" t="n">
-        <v>6991632</v>
+        <v>6991736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7359,7 +7360,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7489,48 +7489,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128145365</v>
       </c>
       <c r="B61" t="n">
-        <v>90889</v>
+        <v>92674</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483955</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7571,7 +7568,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7595,45 +7591,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128145365</v>
+        <v>128148828</v>
       </c>
       <c r="B62" t="n">
-        <v>92674</v>
+        <v>90889</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483955</v>
+        <v>483378</v>
       </c>
       <c r="R62" t="n">
-        <v>6991637</v>
+        <v>6991763</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7674,6 +7673,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128145274</v>
+        <v>128148761</v>
       </c>
       <c r="B63" t="n">
-        <v>92304</v>
+        <v>92660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4787</v>
+        <v>4368</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484038</v>
+        <v>483384</v>
       </c>
       <c r="R63" t="n">
-        <v>6991684</v>
+        <v>6991763</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148640</v>
+        <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>91370</v>
+        <v>92304</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>4787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483483</v>
+        <v>484038</v>
       </c>
       <c r="R64" t="n">
-        <v>6991836</v>
+        <v>6991684</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128152970</v>
+        <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>90897</v>
+        <v>91370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7943,14 +7943,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483774</v>
+        <v>483483</v>
       </c>
       <c r="R65" t="n">
-        <v>6991911</v>
+        <v>6991836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148761</v>
+        <v>128152970</v>
       </c>
       <c r="B66" t="n">
-        <v>92660</v>
+        <v>90897</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483384</v>
+        <v>483774</v>
       </c>
       <c r="R66" t="n">
-        <v>6991763</v>
+        <v>6991911</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,32 +8121,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128148616</v>
+        <v>128152208</v>
       </c>
       <c r="B67" t="n">
-        <v>90887</v>
+        <v>91472</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>233196</v>
+        <v>3277</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Fjällfotad fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8155,14 +8155,14 @@
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483486</v>
+        <v>483808</v>
       </c>
       <c r="R67" t="n">
-        <v>6991836</v>
+        <v>6991708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8227,48 +8227,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128150949</v>
+        <v>128146568</v>
       </c>
       <c r="B68" t="n">
-        <v>92660</v>
+        <v>86884</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4368</v>
+        <v>3624</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483503</v>
+        <v>483803</v>
       </c>
       <c r="R68" t="n">
-        <v>6991606</v>
+        <v>6991669</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8309,7 +8302,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8333,10 +8325,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128152208</v>
+        <v>128150924</v>
       </c>
       <c r="B69" t="n">
-        <v>91472</v>
+        <v>91370</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8344,21 +8336,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3277</v>
+        <v>5432</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8367,14 +8359,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483808</v>
+        <v>483503</v>
       </c>
       <c r="R69" t="n">
-        <v>6991708</v>
+        <v>6991606</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8439,41 +8431,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128146568</v>
+        <v>128150949</v>
       </c>
       <c r="B70" t="n">
-        <v>86884</v>
+        <v>92660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3624</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483803</v>
+        <v>483503</v>
       </c>
       <c r="R70" t="n">
-        <v>6991669</v>
+        <v>6991606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8514,6 +8513,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8537,44 +8537,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128151479</v>
+        <v>128146630</v>
       </c>
       <c r="B71" t="n">
-        <v>90850</v>
+        <v>90889</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5734</v>
+        <v>5747</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483615</v>
+        <v>483783</v>
       </c>
       <c r="R71" t="n">
-        <v>6991623</v>
+        <v>6991660</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8615,7 +8616,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8639,45 +8639,44 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128146630</v>
+        <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>90889</v>
+        <v>90850</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5747</v>
+        <v>5734</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483783</v>
+        <v>483615</v>
       </c>
       <c r="R72" t="n">
-        <v>6991660</v>
+        <v>6991623</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8718,6 +8717,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8741,10 +8741,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128150924</v>
+        <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>91370</v>
+        <v>92634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8752,37 +8752,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483503</v>
+        <v>483943</v>
       </c>
       <c r="R73" t="n">
-        <v>6991606</v>
+        <v>6991638</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8823,7 +8820,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8847,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128151166</v>
+        <v>128151611</v>
       </c>
       <c r="B74" t="n">
-        <v>90874</v>
+        <v>90156</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8858,21 +8854,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>256335</v>
+        <v>1599</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8881,14 +8877,14 @@
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483551</v>
+        <v>483633</v>
       </c>
       <c r="R74" t="n">
-        <v>6991637</v>
+        <v>6991596</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8953,32 +8949,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128145502</v>
+        <v>128146085</v>
       </c>
       <c r="B75" t="n">
-        <v>92634</v>
+        <v>90889</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8988,10 +8984,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483943</v>
+        <v>483847</v>
       </c>
       <c r="R75" t="n">
-        <v>6991638</v>
+        <v>6991688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9055,10 +9051,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128151611</v>
+        <v>128151367</v>
       </c>
       <c r="B76" t="n">
-        <v>90156</v>
+        <v>89404</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9066,21 +9062,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1599</v>
+        <v>275</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9093,10 +9089,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483633</v>
+        <v>483589</v>
       </c>
       <c r="R76" t="n">
-        <v>6991596</v>
+        <v>6991633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9161,7 +9157,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128146085</v>
+        <v>128145310</v>
       </c>
       <c r="B77" t="n">
         <v>90889</v>
@@ -9196,10 +9192,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483847</v>
+        <v>484048</v>
       </c>
       <c r="R77" t="n">
-        <v>6991688</v>
+        <v>6991644</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9263,48 +9259,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B78" t="n">
-        <v>89404</v>
+        <v>88624</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R78" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9345,7 +9338,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9369,45 +9361,48 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128145310</v>
+        <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>90889</v>
+        <v>91472</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>484048</v>
+        <v>484061</v>
       </c>
       <c r="R79" t="n">
-        <v>6991644</v>
+        <v>6991711</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9448,6 +9443,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -9471,45 +9467,48 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128147310</v>
+        <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>88624</v>
+        <v>89333</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4412</v>
+        <v>236437</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483747</v>
+        <v>483326</v>
       </c>
       <c r="R80" t="n">
-        <v>6991783</v>
+        <v>6991694</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9550,12 +9549,13 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9573,10 +9573,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128145240</v>
+        <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>91472</v>
+        <v>88624</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9584,21 +9584,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3277</v>
+        <v>4412</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9607,14 +9607,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>484061</v>
+        <v>483367</v>
       </c>
       <c r="R81" t="n">
-        <v>6991711</v>
+        <v>6991677</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9679,32 +9679,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128149279</v>
+        <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>89333</v>
+        <v>91472</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>236437</v>
+        <v>3277</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9713,14 +9713,14 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Lillhägnen, Lillhägnen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483326</v>
+        <v>483366</v>
       </c>
       <c r="R82" t="n">
-        <v>6991694</v>
+        <v>6991587</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9785,32 +9785,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128149429</v>
+        <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>88624</v>
+        <v>90889</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9823,10 +9823,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483367</v>
+        <v>483377</v>
       </c>
       <c r="R83" t="n">
-        <v>6991677</v>
+        <v>6991679</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9891,10 +9891,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128149640</v>
+        <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>91472</v>
+        <v>92634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9902,21 +9902,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3277</v>
+        <v>4361</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9925,14 +9925,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Lillhägnen, Lillhägnen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483366</v>
+        <v>483377</v>
       </c>
       <c r="R84" t="n">
-        <v>6991587</v>
+        <v>6991684</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9997,10 +9997,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128149500</v>
+        <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90889</v>
+        <v>90156</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10008,21 +10008,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483377</v>
+        <v>483328</v>
       </c>
       <c r="R85" t="n">
-        <v>6991679</v>
+        <v>6991694</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10103,32 +10103,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128149450</v>
+        <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>92634</v>
+        <v>90890</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4361</v>
+        <v>233196</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483377</v>
+        <v>483486</v>
       </c>
       <c r="R86" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10209,10 +10209,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128149268</v>
+        <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90156</v>
+        <v>90877</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10220,21 +10220,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1599</v>
+        <v>256335</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10247,10 +10247,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>483328</v>
+        <v>483551</v>
       </c>
       <c r="R87" t="n">
-        <v>6991694</v>
+        <v>6991637</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10297,7 +10297,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B29" t="n">
-        <v>92674</v>
+        <v>90897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,37 +4134,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4202,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4229,10 +4225,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>92674</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,21 +4236,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4267,10 +4263,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R30" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>90897</v>
+        <v>91370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4342,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4413,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B47" t="n">
-        <v>90815</v>
+        <v>92660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,34 +6032,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B48" t="n">
-        <v>92660</v>
+        <v>90815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,37 +6138,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,7 +6206,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>90889</v>
+        <v>92634</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R53" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>92634</v>
+        <v>90889</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R54" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>92660</v>
+        <v>92304</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R63" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128145274</v>
+        <v>128148640</v>
       </c>
       <c r="B64" t="n">
-        <v>92304</v>
+        <v>91370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484038</v>
+        <v>483483</v>
       </c>
       <c r="R64" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148640</v>
+        <v>128148761</v>
       </c>
       <c r="B65" t="n">
-        <v>91370</v>
+        <v>92660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483483</v>
+        <v>483384</v>
       </c>
       <c r="R65" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8431,48 +8431,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150949</v>
+        <v>128146630</v>
       </c>
       <c r="B70" t="n">
-        <v>92660</v>
+        <v>90889</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483503</v>
+        <v>483783</v>
       </c>
       <c r="R70" t="n">
-        <v>6991606</v>
+        <v>6991660</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8513,7 +8510,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8537,45 +8533,44 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128146630</v>
+        <v>128151479</v>
       </c>
       <c r="B71" t="n">
-        <v>90889</v>
+        <v>90850</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5747</v>
+        <v>5734</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483783</v>
+        <v>483615</v>
       </c>
       <c r="R71" t="n">
-        <v>6991660</v>
+        <v>6991623</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8616,6 +8611,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8639,10 +8635,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128151479</v>
+        <v>128150949</v>
       </c>
       <c r="B72" t="n">
-        <v>90850</v>
+        <v>92660</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8650,33 +8646,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5734</v>
+        <v>4368</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483615</v>
+        <v>483503</v>
       </c>
       <c r="R72" t="n">
-        <v>6991623</v>
+        <v>6991606</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128145822</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>90897</v>
+        <v>92674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,34 +4134,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5754</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483907</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991607</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4202,6 +4205,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148629</v>
+        <v>128148843</v>
       </c>
       <c r="B30" t="n">
-        <v>92674</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,21 +4240,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1968</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4263,10 +4267,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483486</v>
+        <v>483370</v>
       </c>
       <c r="R30" t="n">
-        <v>6991836</v>
+        <v>6991758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148843</v>
+        <v>128145822</v>
       </c>
       <c r="B31" t="n">
-        <v>91370</v>
+        <v>90897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,37 +4346,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483370</v>
+        <v>483907</v>
       </c>
       <c r="R31" t="n">
-        <v>6991758</v>
+        <v>6991607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4413,7 +4414,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4972,48 +4972,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>90889</v>
+        <v>97496</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,49 +5079,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>97496</v>
+        <v>90889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R38" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>91352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,45 +5287,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>100559</v>
+        <v>90897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>92634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,34 +5404,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R41" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,48 +5499,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>90897</v>
+        <v>100559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>92660</v>
+        <v>90815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,37 +6032,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6127,10 +6123,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90815</v>
+        <v>92660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6138,34 +6134,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6205,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6441,48 +6441,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>90889</v>
+        <v>92676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R51" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6547,45 +6543,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B52" t="n">
-        <v>92676</v>
+        <v>90889</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R52" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6626,6 +6625,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>92634</v>
+        <v>90889</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>90889</v>
+        <v>92634</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R54" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146291</v>
+        <v>128152853</v>
       </c>
       <c r="B56" t="n">
-        <v>90815</v>
+        <v>91370</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,34 +6978,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483855</v>
+        <v>483774</v>
       </c>
       <c r="R56" t="n">
-        <v>6991698</v>
+        <v>6991911</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7049,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7175,48 +7179,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B58" t="n">
-        <v>91370</v>
+        <v>90889</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R58" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7257,7 +7258,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7281,32 +7281,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128146291</v>
       </c>
       <c r="B59" t="n">
-        <v>90889</v>
+        <v>90815</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483855</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991698</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7383,48 +7383,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128148620</v>
+        <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>90889</v>
+        <v>92674</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483486</v>
+        <v>483955</v>
       </c>
       <c r="R60" t="n">
-        <v>6991836</v>
+        <v>6991637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7465,7 +7462,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7489,45 +7485,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128145365</v>
+        <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>92674</v>
+        <v>90889</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483955</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991637</v>
+        <v>6991763</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7568,6 +7567,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B62" t="n">
         <v>90889</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R62" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128145274</v>
+        <v>128148761</v>
       </c>
       <c r="B63" t="n">
-        <v>92304</v>
+        <v>92660</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4787</v>
+        <v>4368</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484038</v>
+        <v>483384</v>
       </c>
       <c r="R63" t="n">
-        <v>6991684</v>
+        <v>6991763</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148640</v>
+        <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>91370</v>
+        <v>92304</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>4787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483483</v>
+        <v>484038</v>
       </c>
       <c r="R64" t="n">
-        <v>6991836</v>
+        <v>6991684</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148761</v>
+        <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>92660</v>
+        <v>91370</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483384</v>
+        <v>483483</v>
       </c>
       <c r="R65" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8431,45 +8431,48 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128146630</v>
+        <v>128150949</v>
       </c>
       <c r="B70" t="n">
-        <v>90889</v>
+        <v>92660</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483783</v>
+        <v>483503</v>
       </c>
       <c r="R70" t="n">
-        <v>6991660</v>
+        <v>6991606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8510,6 +8513,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -8533,44 +8537,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128151479</v>
+        <v>128146630</v>
       </c>
       <c r="B71" t="n">
-        <v>90850</v>
+        <v>90889</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5734</v>
+        <v>5747</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483615</v>
+        <v>483783</v>
       </c>
       <c r="R71" t="n">
-        <v>6991623</v>
+        <v>6991660</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8611,7 +8616,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8635,10 +8639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128150949</v>
+        <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>92660</v>
+        <v>90850</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8646,37 +8650,33 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4368</v>
+        <v>5734</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483503</v>
+        <v>483615</v>
       </c>
       <c r="R72" t="n">
-        <v>6991606</v>
+        <v>6991623</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B29" t="n">
-        <v>92674</v>
+        <v>90897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,37 +4134,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4202,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4229,10 +4225,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148843</v>
+        <v>128151907</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>92634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,21 +4236,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4263,14 +4259,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483370</v>
+        <v>483759</v>
       </c>
       <c r="R30" t="n">
-        <v>6991758</v>
+        <v>6991515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128148629</v>
       </c>
       <c r="B31" t="n">
-        <v>90897</v>
+        <v>92674</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4342,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>1968</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483486</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4413,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R32" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4972,49 +4972,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B37" t="n">
-        <v>97496</v>
+        <v>90889</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,48 +5078,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B38" t="n">
-        <v>90889</v>
+        <v>97496</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>91352</v>
+        <v>92634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,34 +5196,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>90897</v>
+        <v>100559</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5369,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B41" t="n">
-        <v>92634</v>
+        <v>91352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,37 +5404,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R41" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5472,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,45 +5495,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B42" t="n">
-        <v>100559</v>
+        <v>90897</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6441,45 +6441,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B51" t="n">
-        <v>92676</v>
+        <v>90889</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,6 +6523,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6543,48 +6547,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B52" t="n">
-        <v>90889</v>
+        <v>92676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6625,7 +6626,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>90889</v>
+        <v>92634</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R53" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>92634</v>
+        <v>90889</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R54" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7383,45 +7383,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128145365</v>
+        <v>128148620</v>
       </c>
       <c r="B60" t="n">
-        <v>92674</v>
+        <v>90889</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483955</v>
+        <v>483486</v>
       </c>
       <c r="R60" t="n">
-        <v>6991637</v>
+        <v>6991836</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7462,6 +7465,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7485,48 +7489,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128145365</v>
       </c>
       <c r="B61" t="n">
-        <v>90889</v>
+        <v>92674</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483955</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7567,7 +7568,6 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B62" t="n">
         <v>90889</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R62" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -5601,48 +5601,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128147461</v>
       </c>
       <c r="B43" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483735</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991823</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5683,7 +5680,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5707,7 +5703,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128147461</v>
+        <v>128151646</v>
       </c>
       <c r="B44" t="n">
         <v>88624</v>
@@ -5736,16 +5732,19 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483735</v>
+        <v>483638</v>
       </c>
       <c r="R44" t="n">
-        <v>6991823</v>
+        <v>6991579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5786,6 +5785,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5809,32 +5809,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128151646</v>
+        <v>128152204</v>
       </c>
       <c r="B45" t="n">
-        <v>88624</v>
+        <v>88623</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5843,14 +5843,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483638</v>
+        <v>483808</v>
       </c>
       <c r="R45" t="n">
-        <v>6991579</v>
+        <v>6991708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128145822</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>90897</v>
+        <v>92674</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,34 +4134,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5754</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483907</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991607</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4202,6 +4205,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B30" t="n">
-        <v>92634</v>
+        <v>91370</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,21 +4240,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4259,14 +4263,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R30" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B31" t="n">
-        <v>92674</v>
+        <v>90897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,37 +4346,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R31" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4413,7 +4414,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148843</v>
+        <v>128151907</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>92634</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483370</v>
+        <v>483759</v>
       </c>
       <c r="R32" t="n">
-        <v>6991758</v>
+        <v>6991515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>90882</v>
+        <v>88623</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,32 +4861,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>88623</v>
+        <v>90882</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4900,14 +4895,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4940,6 +4935,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,48 +4972,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>90889</v>
+        <v>97496</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,49 +5079,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>97496</v>
+        <v>90889</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R38" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>92634</v>
+        <v>91352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,45 +5287,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>100559</v>
+        <v>90897</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B41" t="n">
-        <v>91352</v>
+        <v>92634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,34 +5404,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R41" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,48 +5499,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>90897</v>
+        <v>100559</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B47" t="n">
-        <v>90815</v>
+        <v>92660</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,34 +6032,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B48" t="n">
-        <v>92660</v>
+        <v>90815</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,37 +6138,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,7 +6206,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6441,48 +6441,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>90889</v>
+        <v>92676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R51" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6547,45 +6543,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B52" t="n">
-        <v>92676</v>
+        <v>90889</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R52" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6626,6 +6625,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6967,10 +6967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128152853</v>
+        <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>91370</v>
+        <v>90815</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,37 +6978,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483774</v>
+        <v>483855</v>
       </c>
       <c r="R56" t="n">
-        <v>6991911</v>
+        <v>6991698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7049,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7179,45 +7175,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B58" t="n">
-        <v>90889</v>
+        <v>91370</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R58" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7258,6 +7257,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7281,32 +7281,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146291</v>
+        <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>90815</v>
+        <v>90889</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483855</v>
+        <v>483825</v>
       </c>
       <c r="R59" t="n">
-        <v>6991698</v>
+        <v>6991736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7383,48 +7383,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128148620</v>
+        <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>90889</v>
+        <v>92674</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483486</v>
+        <v>483955</v>
       </c>
       <c r="R60" t="n">
-        <v>6991836</v>
+        <v>6991637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7465,7 +7462,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7489,45 +7485,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128145365</v>
+        <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>92674</v>
+        <v>90889</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483955</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991637</v>
+        <v>6991763</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7568,6 +7567,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B62" t="n">
         <v>90889</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R62" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B29" t="n">
-        <v>92674</v>
+        <v>90897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,37 +4134,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4202,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4229,10 +4225,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148843</v>
+        <v>128151907</v>
       </c>
       <c r="B30" t="n">
-        <v>91370</v>
+        <v>92634</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,21 +4236,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4263,14 +4259,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483370</v>
+        <v>483759</v>
       </c>
       <c r="R30" t="n">
-        <v>6991758</v>
+        <v>6991515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128148629</v>
       </c>
       <c r="B31" t="n">
-        <v>90897</v>
+        <v>92674</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4342,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>1968</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483486</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4413,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B32" t="n">
-        <v>92634</v>
+        <v>91370</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R32" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88623</v>
+        <v>90882</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90882</v>
+        <v>88623</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5601,45 +5601,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128147461</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88624</v>
+        <v>88623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483735</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991823</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5680,6 +5683,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5703,7 +5707,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128151646</v>
+        <v>128147461</v>
       </c>
       <c r="B44" t="n">
         <v>88624</v>
@@ -5732,19 +5736,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483638</v>
+        <v>483735</v>
       </c>
       <c r="R44" t="n">
-        <v>6991579</v>
+        <v>6991823</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5785,7 +5786,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5809,32 +5809,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128152204</v>
+        <v>128151646</v>
       </c>
       <c r="B45" t="n">
-        <v>88623</v>
+        <v>88624</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5843,14 +5843,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483808</v>
+        <v>483638</v>
       </c>
       <c r="R45" t="n">
-        <v>6991708</v>
+        <v>6991579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>92660</v>
+        <v>90815</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,37 +6032,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6127,10 +6123,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90815</v>
+        <v>92660</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6138,34 +6134,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6205,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6441,45 +6441,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B51" t="n">
-        <v>92676</v>
+        <v>90889</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,6 +6523,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6543,48 +6547,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B52" t="n">
-        <v>90889</v>
+        <v>92676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6625,7 +6626,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>92660</v>
+        <v>92304</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R63" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128145274</v>
+        <v>128148640</v>
       </c>
       <c r="B64" t="n">
-        <v>92304</v>
+        <v>91370</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484038</v>
+        <v>483483</v>
       </c>
       <c r="R64" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148640</v>
+        <v>128148761</v>
       </c>
       <c r="B65" t="n">
-        <v>91370</v>
+        <v>92660</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483483</v>
+        <v>483384</v>
       </c>
       <c r="R65" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,45 +3597,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146899</v>
+        <v>128151830</v>
       </c>
       <c r="B24" t="n">
-        <v>91472</v>
+        <v>90895</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483803</v>
+        <v>483768</v>
       </c>
       <c r="R24" t="n">
-        <v>6991652</v>
+        <v>6991562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3676,6 +3679,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3699,32 +3703,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128145243</v>
+        <v>128148746</v>
       </c>
       <c r="B25" t="n">
-        <v>92287</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3733,14 +3737,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484061</v>
+        <v>483384</v>
       </c>
       <c r="R25" t="n">
-        <v>6991711</v>
+        <v>6991763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3805,10 +3809,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B26" t="n">
-        <v>92634</v>
+        <v>91480</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3816,37 +3820,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R26" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3887,7 +3888,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B27" t="n">
-        <v>92660</v>
+        <v>92295</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3945,14 +3945,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R27" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151830</v>
+        <v>128151674</v>
       </c>
       <c r="B28" t="n">
-        <v>90889</v>
+        <v>92668</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483768</v>
+        <v>483639</v>
       </c>
       <c r="R28" t="n">
-        <v>6991562</v>
+        <v>6991536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128145822</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>90897</v>
+        <v>92682</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,34 +4134,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5754</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483907</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991607</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4202,6 +4205,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B30" t="n">
-        <v>92634</v>
+        <v>91378</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,21 +4240,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4259,14 +4263,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R30" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148629</v>
+        <v>128151907</v>
       </c>
       <c r="B31" t="n">
-        <v>92674</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,21 +4346,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4365,14 +4369,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483486</v>
+        <v>483759</v>
       </c>
       <c r="R31" t="n">
-        <v>6991836</v>
+        <v>6991515</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148843</v>
+        <v>128145822</v>
       </c>
       <c r="B32" t="n">
-        <v>91370</v>
+        <v>90903</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,37 +4452,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483370</v>
+        <v>483907</v>
       </c>
       <c r="R32" t="n">
-        <v>6991758</v>
+        <v>6991607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4519,7 +4520,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4543,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128148801</v>
+        <v>128148749</v>
       </c>
       <c r="B33" t="n">
-        <v>92641</v>
+        <v>92644</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1435</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483378</v>
+        <v>483384</v>
       </c>
       <c r="R33" t="n">
         <v>6991763</v>
@@ -4649,32 +4649,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128148749</v>
+        <v>128148801</v>
       </c>
       <c r="B34" t="n">
-        <v>92636</v>
+        <v>92649</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483384</v>
+        <v>483378</v>
       </c>
       <c r="R34" t="n">
         <v>6991763</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>90882</v>
+        <v>88629</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,32 +4861,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>88623</v>
+        <v>90888</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4900,14 +4895,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4940,6 +4935,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4975,7 +4975,7 @@
         <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>97496</v>
+        <v>97504</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>91352</v>
+        <v>92642</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,34 +5196,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>90897</v>
+        <v>100567</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5369,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B41" t="n">
-        <v>92634</v>
+        <v>91360</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,37 +5404,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R41" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5472,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,45 +5495,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B42" t="n">
-        <v>100559</v>
+        <v>90903</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,48 +5601,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128147461</v>
       </c>
       <c r="B43" t="n">
-        <v>88623</v>
+        <v>88630</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483735</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991823</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5683,7 +5680,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5707,10 +5703,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128147461</v>
+        <v>128148255</v>
       </c>
       <c r="B44" t="n">
-        <v>88624</v>
+        <v>92644</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5718,34 +5714,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483735</v>
+        <v>483625</v>
       </c>
       <c r="R44" t="n">
-        <v>6991823</v>
+        <v>6991850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5786,6 +5785,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5809,32 +5809,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128151646</v>
+        <v>128152204</v>
       </c>
       <c r="B45" t="n">
-        <v>88624</v>
+        <v>88629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5843,14 +5843,14 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483638</v>
+        <v>483808</v>
       </c>
       <c r="R45" t="n">
-        <v>6991579</v>
+        <v>6991708</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B46" t="n">
-        <v>92636</v>
+        <v>88630</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R46" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6024,7 +6024,7 @@
         <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>90815</v>
+        <v>90821</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6232,7 +6232,7 @@
         <v>128151718</v>
       </c>
       <c r="B49" t="n">
-        <v>90874</v>
+        <v>90880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>128149405</v>
       </c>
       <c r="B50" t="n">
-        <v>91472</v>
+        <v>91480</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6441,48 +6441,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>90889</v>
+        <v>92684</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R51" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6547,45 +6543,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B52" t="n">
-        <v>92676</v>
+        <v>90895</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R52" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6626,6 +6625,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>92634</v>
+        <v>90895</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>90889</v>
+        <v>92642</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R54" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6861,32 +6861,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128151387</v>
+        <v>128148839</v>
       </c>
       <c r="B55" t="n">
-        <v>88623</v>
+        <v>92668</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>824</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,14 +6895,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483598</v>
+        <v>483370</v>
       </c>
       <c r="R55" t="n">
-        <v>6991632</v>
+        <v>6991758</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6970,7 +6970,7 @@
         <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>90815</v>
+        <v>90821</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7069,48 +7069,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128148839</v>
+        <v>128146254</v>
       </c>
       <c r="B57" t="n">
-        <v>92660</v>
+        <v>90895</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483370</v>
+        <v>483825</v>
       </c>
       <c r="R57" t="n">
-        <v>6991758</v>
+        <v>6991736</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7151,7 +7148,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7175,32 +7171,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128152853</v>
+        <v>128151387</v>
       </c>
       <c r="B58" t="n">
-        <v>91370</v>
+        <v>88629</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>824</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7209,14 +7205,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483774</v>
+        <v>483598</v>
       </c>
       <c r="R58" t="n">
-        <v>6991911</v>
+        <v>6991632</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7281,45 +7277,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B59" t="n">
-        <v>90889</v>
+        <v>91378</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7360,6 +7359,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>92674</v>
+        <v>92682</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B61" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B62" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R62" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7700,7 +7700,7 @@
         <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>92304</v>
+        <v>92312</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>128148640</v>
       </c>
       <c r="B64" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>128148761</v>
       </c>
       <c r="B65" t="n">
-        <v>92660</v>
+        <v>92668</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>128152970</v>
       </c>
       <c r="B66" t="n">
-        <v>90897</v>
+        <v>90903</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8121,48 +8121,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128152208</v>
+        <v>128146630</v>
       </c>
       <c r="B67" t="n">
-        <v>91472</v>
+        <v>90895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483808</v>
+        <v>483783</v>
       </c>
       <c r="R67" t="n">
-        <v>6991708</v>
+        <v>6991660</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8203,7 +8200,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8227,41 +8223,44 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128146568</v>
+        <v>128151479</v>
       </c>
       <c r="B68" t="n">
-        <v>86884</v>
+        <v>90856</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3624</v>
+        <v>5734</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
+          <t>Ramaria botrytis s.lat.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483803</v>
+        <v>483615</v>
       </c>
       <c r="R68" t="n">
-        <v>6991669</v>
+        <v>6991623</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8302,6 +8301,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8328,7 +8328,7 @@
         <v>128150924</v>
       </c>
       <c r="B69" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8431,10 +8431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150949</v>
+        <v>128152208</v>
       </c>
       <c r="B70" t="n">
-        <v>92660</v>
+        <v>91480</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8442,21 +8442,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8465,14 +8465,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R70" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8537,45 +8537,48 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128146630</v>
+        <v>128150949</v>
       </c>
       <c r="B71" t="n">
-        <v>90889</v>
+        <v>92668</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483783</v>
+        <v>483503</v>
       </c>
       <c r="R71" t="n">
-        <v>6991660</v>
+        <v>6991606</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8616,6 +8619,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8639,44 +8643,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128151479</v>
+        <v>128146568</v>
       </c>
       <c r="B72" t="n">
-        <v>90850</v>
+        <v>86888</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5734</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
+          <t>Cortinarius glaucopus s.lat.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R72" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8717,7 +8718,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90156</v>
+        <v>90895</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,37 +8854,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R74" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8922,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8949,10 +8945,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>90889</v>
+        <v>90162</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8960,34 +8956,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R75" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,6 +9027,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9051,48 +9051,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B76" t="n">
-        <v>89404</v>
+        <v>88630</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R76" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9133,7 +9130,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9160,7 +9156,7 @@
         <v>128145310</v>
       </c>
       <c r="B77" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9259,45 +9255,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128147310</v>
+        <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>88624</v>
+        <v>89410</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4412</v>
+        <v>275</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483747</v>
+        <v>483589</v>
       </c>
       <c r="R78" t="n">
-        <v>6991783</v>
+        <v>6991633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9338,6 +9337,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>91472</v>
+        <v>91480</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>89333</v>
+        <v>89339</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>88624</v>
+        <v>88630</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91472</v>
+        <v>91480</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>90889</v>
+        <v>90895</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90156</v>
+        <v>90162</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>90890</v>
+        <v>90893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90877</v>
+        <v>90880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4543,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128148749</v>
+        <v>128148801</v>
       </c>
       <c r="B33" t="n">
-        <v>92644</v>
+        <v>92649</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483384</v>
+        <v>483378</v>
       </c>
       <c r="R33" t="n">
         <v>6991763</v>
@@ -4649,32 +4649,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128148801</v>
+        <v>128148749</v>
       </c>
       <c r="B34" t="n">
-        <v>92649</v>
+        <v>92644</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1435</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483378</v>
+        <v>483384</v>
       </c>
       <c r="R34" t="n">
         <v>6991763</v>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>92642</v>
+        <v>91360</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,45 +5287,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B40" t="n">
-        <v>100567</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146450</v>
+        <v>128151475</v>
       </c>
       <c r="B41" t="n">
-        <v>91360</v>
+        <v>90903</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,34 +5404,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483803</v>
+        <v>483615</v>
       </c>
       <c r="R41" t="n">
-        <v>6991669</v>
+        <v>6991623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,48 +5499,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>90903</v>
+        <v>100567</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,45 +5601,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128147461</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88630</v>
+        <v>88629</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483735</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991823</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5680,6 +5683,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5703,10 +5707,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B44" t="n">
-        <v>92644</v>
+        <v>88630</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5714,21 +5718,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5737,14 +5741,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R44" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5809,48 +5813,45 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128152204</v>
+        <v>128147461</v>
       </c>
       <c r="B45" t="n">
-        <v>88629</v>
+        <v>88630</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483808</v>
+        <v>483735</v>
       </c>
       <c r="R45" t="n">
-        <v>6991708</v>
+        <v>6991823</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5891,7 +5892,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128151646</v>
+        <v>128148255</v>
       </c>
       <c r="B46" t="n">
-        <v>88630</v>
+        <v>92644</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483638</v>
+        <v>483625</v>
       </c>
       <c r="R46" t="n">
-        <v>6991579</v>
+        <v>6991850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,45 +6021,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B47" t="n">
-        <v>90821</v>
+        <v>90880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B48" t="n">
-        <v>92668</v>
+        <v>90821</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,37 +6138,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,7 +6206,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6229,32 +6229,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151718</v>
+        <v>128151897</v>
       </c>
       <c r="B49" t="n">
-        <v>90880</v>
+        <v>92668</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>256335</v>
+        <v>4368</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483661</v>
+        <v>483761</v>
       </c>
       <c r="R49" t="n">
-        <v>6991539</v>
+        <v>6991506</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>90895</v>
+        <v>92642</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R53" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>92642</v>
+        <v>90895</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R54" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128151830</v>
+        <v>128148746</v>
       </c>
       <c r="B24" t="n">
-        <v>90895</v>
+        <v>92734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483768</v>
+        <v>483384</v>
       </c>
       <c r="R24" t="n">
-        <v>6991562</v>
+        <v>6991763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>91572</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3714,37 +3714,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R25" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3785,7 +3782,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3809,45 +3805,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146899</v>
+        <v>128145243</v>
       </c>
       <c r="B26" t="n">
-        <v>91480</v>
+        <v>92387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3277</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483803</v>
+        <v>484061</v>
       </c>
       <c r="R26" t="n">
-        <v>6991652</v>
+        <v>6991711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3888,6 +3887,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128145243</v>
+        <v>128151830</v>
       </c>
       <c r="B27" t="n">
-        <v>92295</v>
+        <v>90987</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3945,14 +3945,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484061</v>
+        <v>483768</v>
       </c>
       <c r="R27" t="n">
-        <v>6991711</v>
+        <v>6991562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
         <v>128151674</v>
       </c>
       <c r="B28" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>92682</v>
+        <v>92774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148843</v>
+        <v>128145822</v>
       </c>
       <c r="B30" t="n">
-        <v>91378</v>
+        <v>90995</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,37 +4240,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483370</v>
+        <v>483907</v>
       </c>
       <c r="R30" t="n">
-        <v>6991758</v>
+        <v>6991607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,7 +4308,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4335,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128151907</v>
+        <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>91470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,21 +4342,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4369,14 +4365,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483759</v>
+        <v>483370</v>
       </c>
       <c r="R31" t="n">
-        <v>6991515</v>
+        <v>6991758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4441,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128145822</v>
+        <v>128151907</v>
       </c>
       <c r="B32" t="n">
-        <v>90903</v>
+        <v>92734</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4452,34 +4448,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483907</v>
+        <v>483759</v>
       </c>
       <c r="R32" t="n">
-        <v>6991607</v>
+        <v>6991515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4520,6 +4519,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>128148801</v>
       </c>
       <c r="B33" t="n">
-        <v>92649</v>
+        <v>92741</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148749</v>
       </c>
       <c r="B34" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88629</v>
+        <v>90980</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90888</v>
+        <v>88721</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,49 +4972,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B37" t="n">
-        <v>97504</v>
+        <v>90987</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,48 +5078,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B38" t="n">
-        <v>90895</v>
+        <v>97597</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>91360</v>
+        <v>92734</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,34 +5196,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128147638</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>92642</v>
+        <v>100660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483719</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991835</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5369,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5396,7 +5396,7 @@
         <v>128151475</v>
       </c>
       <c r="B41" t="n">
-        <v>90903</v>
+        <v>90995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128146450</v>
       </c>
       <c r="B42" t="n">
-        <v>100567</v>
+        <v>91452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483803</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,48 +5601,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128147461</v>
       </c>
       <c r="B43" t="n">
-        <v>88629</v>
+        <v>88722</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483735</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991823</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5683,7 +5680,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5707,10 +5703,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128151646</v>
+        <v>128148255</v>
       </c>
       <c r="B44" t="n">
-        <v>88630</v>
+        <v>92736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5718,21 +5714,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5741,14 +5737,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483638</v>
+        <v>483625</v>
       </c>
       <c r="R44" t="n">
-        <v>6991579</v>
+        <v>6991850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5813,10 +5809,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128147461</v>
+        <v>128151646</v>
       </c>
       <c r="B45" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5842,16 +5838,19 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483735</v>
+        <v>483638</v>
       </c>
       <c r="R45" t="n">
-        <v>6991823</v>
+        <v>6991579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5892,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5915,32 +5915,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128148255</v>
+        <v>128152204</v>
       </c>
       <c r="B46" t="n">
-        <v>92644</v>
+        <v>88721</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>824</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483625</v>
+        <v>483808</v>
       </c>
       <c r="R46" t="n">
-        <v>6991850</v>
+        <v>6991708</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,48 +6021,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>90880</v>
+        <v>90913</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6127,45 +6123,48 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B48" t="n">
-        <v>90821</v>
+        <v>90972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6205,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>128151897</v>
       </c>
       <c r="B49" t="n">
-        <v>92668</v>
+        <v>92760</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6335,48 +6335,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B50" t="n">
-        <v>91480</v>
+        <v>92776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R50" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6417,7 +6414,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6441,45 +6437,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B51" t="n">
-        <v>92684</v>
+        <v>90987</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,6 +6519,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128149405</v>
       </c>
       <c r="B52" t="n">
-        <v>90895</v>
+        <v>91572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6577,14 +6577,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483367</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991677</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,48 +6861,45 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128148839</v>
+        <v>128146254</v>
       </c>
       <c r="B55" t="n">
-        <v>92668</v>
+        <v>90987</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483370</v>
+        <v>483825</v>
       </c>
       <c r="R55" t="n">
-        <v>6991758</v>
+        <v>6991736</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6943,7 +6940,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6967,45 +6963,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B56" t="n">
-        <v>90821</v>
+        <v>88721</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R56" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7045,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,45 +7069,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128146254</v>
+        <v>128148839</v>
       </c>
       <c r="B57" t="n">
-        <v>90895</v>
+        <v>92760</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483825</v>
+        <v>483370</v>
       </c>
       <c r="R57" t="n">
-        <v>6991736</v>
+        <v>6991758</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7148,6 +7151,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7171,48 +7175,45 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128151387</v>
+        <v>128146291</v>
       </c>
       <c r="B58" t="n">
-        <v>88629</v>
+        <v>90913</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>824</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483598</v>
+        <v>483855</v>
       </c>
       <c r="R58" t="n">
-        <v>6991632</v>
+        <v>6991698</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7253,7 +7254,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>128152853</v>
       </c>
       <c r="B59" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7383,45 +7383,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128145365</v>
+        <v>128148620</v>
       </c>
       <c r="B60" t="n">
-        <v>92682</v>
+        <v>90987</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483955</v>
+        <v>483486</v>
       </c>
       <c r="R60" t="n">
-        <v>6991637</v>
+        <v>6991836</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7462,6 +7465,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7485,10 +7489,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7523,10 +7527,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,48 +7595,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148828</v>
+        <v>128145365</v>
       </c>
       <c r="B62" t="n">
-        <v>90895</v>
+        <v>92774</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483378</v>
+        <v>483955</v>
       </c>
       <c r="R62" t="n">
-        <v>6991763</v>
+        <v>6991637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7673,7 +7674,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128145274</v>
+        <v>128152970</v>
       </c>
       <c r="B63" t="n">
-        <v>92312</v>
+        <v>90995</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4787</v>
+        <v>5754</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484038</v>
+        <v>483774</v>
       </c>
       <c r="R63" t="n">
-        <v>6991684</v>
+        <v>6991911</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148640</v>
+        <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>91378</v>
+        <v>92404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>4787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483483</v>
+        <v>484038</v>
       </c>
       <c r="R64" t="n">
-        <v>6991836</v>
+        <v>6991684</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148761</v>
+        <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>92668</v>
+        <v>91470</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483384</v>
+        <v>483483</v>
       </c>
       <c r="R65" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128152970</v>
+        <v>128148761</v>
       </c>
       <c r="B66" t="n">
-        <v>90903</v>
+        <v>92760</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483774</v>
+        <v>483384</v>
       </c>
       <c r="R66" t="n">
-        <v>6991911</v>
+        <v>6991763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8124,7 +8124,7 @@
         <v>128146630</v>
       </c>
       <c r="B67" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         <v>128151479</v>
       </c>
       <c r="B68" t="n">
-        <v>90856</v>
+        <v>90948</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8328,7 +8328,7 @@
         <v>128150924</v>
       </c>
       <c r="B69" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8431,10 +8431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128152208</v>
+        <v>128150949</v>
       </c>
       <c r="B70" t="n">
-        <v>91480</v>
+        <v>92760</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8442,21 +8442,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3277</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8465,14 +8465,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483808</v>
+        <v>483503</v>
       </c>
       <c r="R70" t="n">
-        <v>6991708</v>
+        <v>6991606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8537,10 +8537,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128150949</v>
+        <v>128152208</v>
       </c>
       <c r="B71" t="n">
-        <v>92668</v>
+        <v>91572</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8548,21 +8548,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8571,14 +8571,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R71" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8646,7 +8646,7 @@
         <v>128146568</v>
       </c>
       <c r="B72" t="n">
-        <v>86888</v>
+        <v>86980</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>90162</v>
+        <v>90254</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,32 +9051,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128147310</v>
+        <v>128145310</v>
       </c>
       <c r="B76" t="n">
-        <v>88630</v>
+        <v>90987</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483747</v>
+        <v>484048</v>
       </c>
       <c r="R76" t="n">
-        <v>6991783</v>
+        <v>6991644</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9153,32 +9153,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128145310</v>
+        <v>128147310</v>
       </c>
       <c r="B77" t="n">
-        <v>90895</v>
+        <v>88722</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>4412</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9188,10 +9188,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>484048</v>
+        <v>483747</v>
       </c>
       <c r="R77" t="n">
-        <v>6991644</v>
+        <v>6991783</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9258,7 +9258,7 @@
         <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>89410</v>
+        <v>89502</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>91480</v>
+        <v>91572</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>89339</v>
+        <v>89431</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>88630</v>
+        <v>88722</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91480</v>
+        <v>91572</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>90895</v>
+        <v>90987</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90162</v>
+        <v>90254</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>90893</v>
+        <v>90985</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90880</v>
+        <v>90972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128148746</v>
+        <v>128151830</v>
       </c>
       <c r="B24" t="n">
-        <v>92734</v>
+        <v>90987</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483384</v>
+        <v>483768</v>
       </c>
       <c r="R24" t="n">
-        <v>6991763</v>
+        <v>6991562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146899</v>
+        <v>128151674</v>
       </c>
       <c r="B25" t="n">
-        <v>91572</v>
+        <v>92760</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3714,34 +3714,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3277</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483803</v>
+        <v>483639</v>
       </c>
       <c r="R25" t="n">
-        <v>6991652</v>
+        <v>6991536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3782,6 +3785,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3805,32 +3809,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128145243</v>
+        <v>128148746</v>
       </c>
       <c r="B26" t="n">
-        <v>92387</v>
+        <v>92734</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3839,14 +3843,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484061</v>
+        <v>483384</v>
       </c>
       <c r="R26" t="n">
-        <v>6991711</v>
+        <v>6991763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3911,48 +3915,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151830</v>
+        <v>128146899</v>
       </c>
       <c r="B27" t="n">
-        <v>90987</v>
+        <v>91572</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483768</v>
+        <v>483803</v>
       </c>
       <c r="R27" t="n">
-        <v>6991562</v>
+        <v>6991652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3993,7 +3994,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B28" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4051,14 +4051,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R28" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128148843</v>
       </c>
       <c r="B29" t="n">
-        <v>92774</v>
+        <v>91470</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483370</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991758</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128145822</v>
+        <v>128151907</v>
       </c>
       <c r="B30" t="n">
-        <v>90995</v>
+        <v>92734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,34 +4240,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483907</v>
+        <v>483759</v>
       </c>
       <c r="R30" t="n">
-        <v>6991607</v>
+        <v>6991515</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4308,6 +4311,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B31" t="n">
-        <v>91470</v>
+        <v>92774</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,21 +4346,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4369,10 +4373,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R31" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128151907</v>
+        <v>128145822</v>
       </c>
       <c r="B32" t="n">
-        <v>92734</v>
+        <v>90995</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,37 +4452,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483759</v>
+        <v>483907</v>
       </c>
       <c r="R32" t="n">
-        <v>6991515</v>
+        <v>6991607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4519,7 +4520,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>92734</v>
+        <v>91452</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,45 +5287,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B40" t="n">
-        <v>100660</v>
+        <v>92734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,48 +5393,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128151475</v>
+        <v>128145519</v>
       </c>
       <c r="B41" t="n">
-        <v>90995</v>
+        <v>100660</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5754</v>
+        <v>222771</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483615</v>
+        <v>483943</v>
       </c>
       <c r="R41" t="n">
-        <v>6991623</v>
+        <v>6991638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5472,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,10 +5495,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128151475</v>
       </c>
       <c r="B42" t="n">
-        <v>91452</v>
+        <v>90995</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5510,34 +5506,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483615</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,45 +5601,48 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128147461</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88722</v>
+        <v>88721</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483735</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991823</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5680,6 +5683,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5703,10 +5707,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B44" t="n">
-        <v>92736</v>
+        <v>88722</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5714,21 +5718,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5737,14 +5741,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R44" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5809,7 +5813,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128151646</v>
+        <v>128147461</v>
       </c>
       <c r="B45" t="n">
         <v>88722</v>
@@ -5838,19 +5842,16 @@
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483638</v>
+        <v>483735</v>
       </c>
       <c r="R45" t="n">
-        <v>6991579</v>
+        <v>6991823</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5891,7 +5892,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5915,32 +5915,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128152204</v>
+        <v>128148255</v>
       </c>
       <c r="B46" t="n">
-        <v>88721</v>
+        <v>92736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>824</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483808</v>
+        <v>483625</v>
       </c>
       <c r="R46" t="n">
-        <v>6991708</v>
+        <v>6991850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,45 +6021,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B47" t="n">
-        <v>90913</v>
+        <v>90972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6123,48 +6127,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B48" t="n">
-        <v>90972</v>
+        <v>90913</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R48" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,7 +6206,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6335,45 +6335,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128145589</v>
+        <v>128149405</v>
       </c>
       <c r="B50" t="n">
-        <v>92776</v>
+        <v>91572</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>3277</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483946</v>
+        <v>483367</v>
       </c>
       <c r="R50" t="n">
-        <v>6991610</v>
+        <v>6991677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,6 +6417,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6543,48 +6547,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B52" t="n">
-        <v>91572</v>
+        <v>92776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R52" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6625,7 +6626,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6861,45 +6861,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B55" t="n">
-        <v>90987</v>
+        <v>91470</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R55" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6940,6 +6943,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6963,48 +6967,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128151387</v>
+        <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>88721</v>
+        <v>90913</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>824</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483598</v>
+        <v>483855</v>
       </c>
       <c r="R56" t="n">
-        <v>6991632</v>
+        <v>6991698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7045,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,32 +7069,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128148839</v>
+        <v>128151387</v>
       </c>
       <c r="B57" t="n">
-        <v>92760</v>
+        <v>88721</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>824</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7103,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483370</v>
+        <v>483598</v>
       </c>
       <c r="R57" t="n">
-        <v>6991758</v>
+        <v>6991632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7175,10 +7175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128146291</v>
+        <v>128148839</v>
       </c>
       <c r="B58" t="n">
-        <v>90913</v>
+        <v>92760</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7186,34 +7186,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483855</v>
+        <v>483370</v>
       </c>
       <c r="R58" t="n">
-        <v>6991698</v>
+        <v>6991758</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7254,6 +7257,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7277,48 +7281,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>91470</v>
+        <v>90987</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R59" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7359,7 +7360,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7383,48 +7383,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128148620</v>
+        <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>90987</v>
+        <v>92774</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483486</v>
+        <v>483955</v>
       </c>
       <c r="R60" t="n">
-        <v>6991836</v>
+        <v>6991637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7465,7 +7462,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7595,45 +7591,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128145365</v>
+        <v>128148620</v>
       </c>
       <c r="B62" t="n">
-        <v>92774</v>
+        <v>90987</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483955</v>
+        <v>483486</v>
       </c>
       <c r="R62" t="n">
-        <v>6991637</v>
+        <v>6991836</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7674,6 +7673,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128152970</v>
+        <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>90995</v>
+        <v>92404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5754</v>
+        <v>4787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483774</v>
+        <v>484038</v>
       </c>
       <c r="R63" t="n">
-        <v>6991911</v>
+        <v>6991684</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128145274</v>
+        <v>128148640</v>
       </c>
       <c r="B64" t="n">
-        <v>92404</v>
+        <v>91470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484038</v>
+        <v>483483</v>
       </c>
       <c r="R64" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,10 +7909,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148640</v>
+        <v>128148761</v>
       </c>
       <c r="B65" t="n">
-        <v>91470</v>
+        <v>92760</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7920,21 +7920,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7947,10 +7947,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483483</v>
+        <v>483384</v>
       </c>
       <c r="R65" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148761</v>
+        <v>128152970</v>
       </c>
       <c r="B66" t="n">
-        <v>92760</v>
+        <v>90995</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483384</v>
+        <v>483774</v>
       </c>
       <c r="R66" t="n">
-        <v>6991763</v>
+        <v>6991911</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,45 +8121,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128146630</v>
+        <v>128152208</v>
       </c>
       <c r="B67" t="n">
-        <v>90987</v>
+        <v>91572</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483783</v>
+        <v>483808</v>
       </c>
       <c r="R67" t="n">
-        <v>6991660</v>
+        <v>6991708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8200,6 +8203,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8537,48 +8541,41 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128152208</v>
+        <v>128146568</v>
       </c>
       <c r="B71" t="n">
-        <v>91572</v>
+        <v>86980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3277</v>
+        <v>3624</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483808</v>
+        <v>483803</v>
       </c>
       <c r="R71" t="n">
-        <v>6991708</v>
+        <v>6991669</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8619,7 +8616,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8643,30 +8639,34 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128146568</v>
+        <v>128146630</v>
       </c>
       <c r="B72" t="n">
-        <v>86980</v>
+        <v>90987</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5747</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -8674,10 +8674,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483803</v>
+        <v>483783</v>
       </c>
       <c r="R72" t="n">
-        <v>6991669</v>
+        <v>6991660</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B74" t="n">
-        <v>90987</v>
+        <v>90254</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,34 +8854,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R74" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8922,6 +8925,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8945,10 +8949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B75" t="n">
-        <v>90254</v>
+        <v>90987</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8956,37 +8960,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R75" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9027,7 +9028,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128151830</v>
+        <v>128148746</v>
       </c>
       <c r="B24" t="n">
-        <v>90987</v>
+        <v>92734</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483768</v>
+        <v>483384</v>
       </c>
       <c r="R24" t="n">
-        <v>6991562</v>
+        <v>6991763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B25" t="n">
-        <v>92760</v>
+        <v>92387</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3737,14 +3737,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R25" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,10 +3809,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B26" t="n">
-        <v>92734</v>
+        <v>91572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3820,37 +3820,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R26" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3891,7 +3888,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3915,10 +3911,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146899</v>
+        <v>128151674</v>
       </c>
       <c r="B27" t="n">
-        <v>91572</v>
+        <v>92760</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3926,34 +3922,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3277</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483803</v>
+        <v>483639</v>
       </c>
       <c r="R27" t="n">
-        <v>6991652</v>
+        <v>6991536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3994,6 +3993,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128145243</v>
+        <v>128151830</v>
       </c>
       <c r="B28" t="n">
-        <v>92387</v>
+        <v>90987</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>5747</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4051,14 +4051,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484061</v>
+        <v>483768</v>
       </c>
       <c r="R28" t="n">
-        <v>6991711</v>
+        <v>6991562</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>91470</v>
+        <v>92774</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4161,10 +4161,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B31" t="n">
-        <v>92774</v>
+        <v>90995</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,37 +4346,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R31" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4417,7 +4414,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4441,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B32" t="n">
-        <v>90995</v>
+        <v>91470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4452,34 +4448,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R32" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4520,6 +4519,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>90980</v>
+        <v>88721</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,32 +4861,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>88721</v>
+        <v>90980</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4900,14 +4895,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4940,6 +4935,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,48 +4972,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>90987</v>
+        <v>97597</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,49 +5079,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>97597</v>
+        <v>90987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R38" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>91452</v>
+        <v>92734</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,34 +5196,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,48 +5291,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128147638</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>92734</v>
+        <v>100660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483719</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991835</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5369,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,45 +5393,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B41" t="n">
-        <v>100660</v>
+        <v>90995</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R41" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128151475</v>
+        <v>128146450</v>
       </c>
       <c r="B42" t="n">
-        <v>90995</v>
+        <v>91452</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,37 +5510,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R42" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6021,48 +6021,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>90972</v>
+        <v>90913</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6127,10 +6123,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90913</v>
+        <v>92760</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6138,34 +6134,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6205,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6229,32 +6229,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151897</v>
+        <v>128151718</v>
       </c>
       <c r="B49" t="n">
-        <v>92760</v>
+        <v>90972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4368</v>
+        <v>256335</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483761</v>
+        <v>483661</v>
       </c>
       <c r="R49" t="n">
-        <v>6991506</v>
+        <v>6991539</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6335,48 +6335,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B50" t="n">
-        <v>91572</v>
+        <v>92776</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R50" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6417,7 +6414,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6547,45 +6543,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128145589</v>
+        <v>128149405</v>
       </c>
       <c r="B52" t="n">
-        <v>92776</v>
+        <v>91572</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>3277</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483946</v>
+        <v>483367</v>
       </c>
       <c r="R52" t="n">
-        <v>6991610</v>
+        <v>6991677</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6626,6 +6625,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>92734</v>
+        <v>90987</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>90987</v>
+        <v>92734</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R54" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128152853</v>
+        <v>128146291</v>
       </c>
       <c r="B55" t="n">
-        <v>91470</v>
+        <v>90913</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,37 +6872,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>3286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483774</v>
+        <v>483855</v>
       </c>
       <c r="R55" t="n">
-        <v>6991911</v>
+        <v>6991698</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6943,7 +6940,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6967,45 +6963,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B56" t="n">
-        <v>90913</v>
+        <v>88721</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R56" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7045,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,32 +7069,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128151387</v>
+        <v>128152853</v>
       </c>
       <c r="B57" t="n">
-        <v>88721</v>
+        <v>91470</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>824</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7103,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483598</v>
+        <v>483774</v>
       </c>
       <c r="R57" t="n">
-        <v>6991632</v>
+        <v>6991911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7485,7 +7485,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B61" t="n">
         <v>90987</v>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,7 +7591,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B62" t="n">
         <v>90987</v>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R62" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8121,48 +8121,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128152208</v>
+        <v>128146630</v>
       </c>
       <c r="B67" t="n">
-        <v>91572</v>
+        <v>90987</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483808</v>
+        <v>483783</v>
       </c>
       <c r="R67" t="n">
-        <v>6991708</v>
+        <v>6991660</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8203,7 +8200,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8227,44 +8223,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128151479</v>
+        <v>128146568</v>
       </c>
       <c r="B68" t="n">
-        <v>90948</v>
+        <v>86980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5734</v>
+        <v>3624</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
+          <t>Cortinarius glaucopus s.lat.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R68" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8305,7 +8298,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8329,10 +8321,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128150924</v>
+        <v>128150949</v>
       </c>
       <c r="B69" t="n">
-        <v>91470</v>
+        <v>92760</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,21 +8332,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8435,10 +8427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150949</v>
+        <v>128152208</v>
       </c>
       <c r="B70" t="n">
-        <v>92760</v>
+        <v>91572</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8446,21 +8438,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8469,14 +8461,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R70" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8541,41 +8533,44 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128146568</v>
+        <v>128151479</v>
       </c>
       <c r="B71" t="n">
-        <v>86980</v>
+        <v>90948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3624</v>
+        <v>5734</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
+          <t>Ramaria botrytis s.lat.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483803</v>
+        <v>483615</v>
       </c>
       <c r="R71" t="n">
-        <v>6991669</v>
+        <v>6991623</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8616,6 +8611,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8639,45 +8635,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128146630</v>
+        <v>128150924</v>
       </c>
       <c r="B72" t="n">
-        <v>90987</v>
+        <v>91470</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483783</v>
+        <v>483503</v>
       </c>
       <c r="R72" t="n">
-        <v>6991660</v>
+        <v>6991606</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8718,6 +8717,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90254</v>
+        <v>90987</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,37 +8854,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R74" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8922,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8949,10 +8945,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>90987</v>
+        <v>90254</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8960,34 +8956,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R75" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,6 +9027,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,10 +3597,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128148746</v>
+        <v>128146899</v>
       </c>
       <c r="B24" t="n">
-        <v>92734</v>
+        <v>91572</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,37 +3608,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>3277</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483384</v>
+        <v>483803</v>
       </c>
       <c r="R24" t="n">
-        <v>6991763</v>
+        <v>6991652</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3679,7 +3676,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3703,32 +3699,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128145243</v>
+        <v>128148746</v>
       </c>
       <c r="B25" t="n">
-        <v>92387</v>
+        <v>92734</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3737,14 +3733,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484061</v>
+        <v>483384</v>
       </c>
       <c r="R25" t="n">
-        <v>6991711</v>
+        <v>6991763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,45 +3805,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146899</v>
+        <v>128145243</v>
       </c>
       <c r="B26" t="n">
-        <v>91572</v>
+        <v>92387</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3277</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483803</v>
+        <v>484061</v>
       </c>
       <c r="R26" t="n">
-        <v>6991652</v>
+        <v>6991711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3888,6 +3887,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,45 +3597,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146899</v>
+        <v>128151830</v>
       </c>
       <c r="B24" t="n">
-        <v>91572</v>
+        <v>90999</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483803</v>
+        <v>483768</v>
       </c>
       <c r="R24" t="n">
-        <v>6991652</v>
+        <v>6991562</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3676,6 +3679,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3699,10 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128148746</v>
+        <v>128151674</v>
       </c>
       <c r="B25" t="n">
-        <v>92734</v>
+        <v>92772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3710,21 +3714,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3733,14 +3737,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483384</v>
+        <v>483639</v>
       </c>
       <c r="R25" t="n">
-        <v>6991763</v>
+        <v>6991536</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3805,32 +3809,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128145243</v>
+        <v>128148746</v>
       </c>
       <c r="B26" t="n">
-        <v>92387</v>
+        <v>92746</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3839,14 +3843,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484061</v>
+        <v>483384</v>
       </c>
       <c r="R26" t="n">
-        <v>6991711</v>
+        <v>6991763</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3911,10 +3915,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151674</v>
+        <v>128146899</v>
       </c>
       <c r="B27" t="n">
-        <v>92760</v>
+        <v>91584</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3922,37 +3926,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483639</v>
+        <v>483803</v>
       </c>
       <c r="R27" t="n">
-        <v>6991536</v>
+        <v>6991652</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3993,7 +3994,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151830</v>
+        <v>128145243</v>
       </c>
       <c r="B28" t="n">
-        <v>90987</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4051,14 +4051,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483768</v>
+        <v>484061</v>
       </c>
       <c r="R28" t="n">
-        <v>6991562</v>
+        <v>6991711</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128151907</v>
       </c>
       <c r="B29" t="n">
-        <v>92774</v>
+        <v>92746</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4157,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483759</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128151907</v>
+        <v>128148629</v>
       </c>
       <c r="B30" t="n">
-        <v>92734</v>
+        <v>92786</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,21 +4240,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4263,14 +4263,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483759</v>
+        <v>483486</v>
       </c>
       <c r="R30" t="n">
-        <v>6991515</v>
+        <v>6991836</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4335,10 +4335,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>90995</v>
+        <v>91482</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4346,34 +4346,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R31" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4414,6 +4417,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4437,10 +4441,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148843</v>
+        <v>128145822</v>
       </c>
       <c r="B32" t="n">
-        <v>91470</v>
+        <v>91007</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,37 +4452,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483370</v>
+        <v>483907</v>
       </c>
       <c r="R32" t="n">
-        <v>6991758</v>
+        <v>6991607</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4519,7 +4520,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>128148801</v>
       </c>
       <c r="B33" t="n">
-        <v>92741</v>
+        <v>92753</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148749</v>
       </c>
       <c r="B34" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>88721</v>
+        <v>88733</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4864,7 +4864,7 @@
         <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>90980</v>
+        <v>90992</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>97597</v>
+        <v>97609</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>92734</v>
+        <v>91464</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,45 +5287,48 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>100660</v>
+        <v>91007</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128151475</v>
+        <v>128147638</v>
       </c>
       <c r="B41" t="n">
-        <v>90995</v>
+        <v>92746</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5427,14 +5427,14 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483615</v>
+        <v>483719</v>
       </c>
       <c r="R41" t="n">
-        <v>6991623</v>
+        <v>6991835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>91452</v>
+        <v>100674</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,32 +5601,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128151646</v>
       </c>
       <c r="B43" t="n">
-        <v>88721</v>
+        <v>88734</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5635,14 +5635,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483638</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5707,32 +5707,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128151646</v>
+        <v>128152204</v>
       </c>
       <c r="B44" t="n">
-        <v>88722</v>
+        <v>88733</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5741,14 +5741,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483638</v>
+        <v>483808</v>
       </c>
       <c r="R44" t="n">
-        <v>6991579</v>
+        <v>6991708</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5816,7 +5816,7 @@
         <v>128147461</v>
       </c>
       <c r="B45" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5918,7 +5918,7 @@
         <v>128148255</v>
       </c>
       <c r="B46" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6021,45 +6021,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151718</v>
       </c>
       <c r="B47" t="n">
-        <v>90913</v>
+        <v>90984</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>256335</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483661</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6123,10 +6127,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B48" t="n">
-        <v>92760</v>
+        <v>90925</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6134,37 +6138,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6205,7 +6206,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6229,32 +6229,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151718</v>
+        <v>128151897</v>
       </c>
       <c r="B49" t="n">
-        <v>90972</v>
+        <v>92772</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>256335</v>
+        <v>4368</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483661</v>
+        <v>483761</v>
       </c>
       <c r="R49" t="n">
-        <v>6991539</v>
+        <v>6991506</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6335,45 +6335,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B50" t="n">
-        <v>92776</v>
+        <v>90999</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R50" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6414,6 +6417,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6437,48 +6441,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>90987</v>
+        <v>92788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R51" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6519,7 +6520,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6546,7 +6546,7 @@
         <v>128149405</v>
       </c>
       <c r="B52" t="n">
-        <v>91572</v>
+        <v>91584</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>90987</v>
+        <v>92746</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R53" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>92734</v>
+        <v>90999</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R54" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128146291</v>
+        <v>128148839</v>
       </c>
       <c r="B55" t="n">
-        <v>90913</v>
+        <v>92772</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,34 +6872,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483855</v>
+        <v>483370</v>
       </c>
       <c r="R55" t="n">
-        <v>6991698</v>
+        <v>6991758</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6940,6 +6943,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6963,48 +6967,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128151387</v>
+        <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>88721</v>
+        <v>90925</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>824</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483598</v>
+        <v>483855</v>
       </c>
       <c r="R56" t="n">
-        <v>6991632</v>
+        <v>6991698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7045,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,48 +7069,45 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B57" t="n">
-        <v>91470</v>
+        <v>90999</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R57" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7151,7 +7148,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7175,10 +7171,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128148839</v>
+        <v>128152853</v>
       </c>
       <c r="B58" t="n">
-        <v>92760</v>
+        <v>91482</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7186,21 +7182,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7209,14 +7205,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483370</v>
+        <v>483774</v>
       </c>
       <c r="R58" t="n">
-        <v>6991758</v>
+        <v>6991911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7281,10 +7277,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128151387</v>
       </c>
       <c r="B59" t="n">
-        <v>90987</v>
+        <v>88733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7292,34 +7288,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>824</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483598</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991632</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7360,6 +7359,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7386,7 +7386,7 @@
         <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>92774</v>
+        <v>92786</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B61" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B62" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R62" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128145274</v>
+        <v>128148761</v>
       </c>
       <c r="B63" t="n">
-        <v>92404</v>
+        <v>92772</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4787</v>
+        <v>4368</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484038</v>
+        <v>483384</v>
       </c>
       <c r="R63" t="n">
-        <v>6991684</v>
+        <v>6991763</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148640</v>
+        <v>128152970</v>
       </c>
       <c r="B64" t="n">
-        <v>91470</v>
+        <v>91007</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483483</v>
+        <v>483774</v>
       </c>
       <c r="R64" t="n">
-        <v>6991836</v>
+        <v>6991911</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,32 +7909,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B65" t="n">
-        <v>92760</v>
+        <v>92416</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7943,14 +7943,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R65" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128152970</v>
+        <v>128148640</v>
       </c>
       <c r="B66" t="n">
-        <v>90995</v>
+        <v>91482</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483774</v>
+        <v>483483</v>
       </c>
       <c r="R66" t="n">
-        <v>6991911</v>
+        <v>6991836</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,45 +8121,48 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128146630</v>
+        <v>128152208</v>
       </c>
       <c r="B67" t="n">
-        <v>90987</v>
+        <v>91584</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483783</v>
+        <v>483808</v>
       </c>
       <c r="R67" t="n">
-        <v>6991660</v>
+        <v>6991708</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8200,6 +8203,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8226,7 +8230,7 @@
         <v>128146568</v>
       </c>
       <c r="B68" t="n">
-        <v>86980</v>
+        <v>86991</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8321,48 +8325,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128150949</v>
+        <v>128146630</v>
       </c>
       <c r="B69" t="n">
-        <v>92760</v>
+        <v>90999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483503</v>
+        <v>483783</v>
       </c>
       <c r="R69" t="n">
-        <v>6991606</v>
+        <v>6991660</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8403,7 +8404,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8427,10 +8427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128152208</v>
+        <v>128151479</v>
       </c>
       <c r="B70" t="n">
-        <v>91572</v>
+        <v>90960</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8438,37 +8438,33 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3277</v>
+        <v>5734</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483808</v>
+        <v>483615</v>
       </c>
       <c r="R70" t="n">
-        <v>6991708</v>
+        <v>6991623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8533,10 +8529,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128151479</v>
+        <v>128150924</v>
       </c>
       <c r="B71" t="n">
-        <v>90948</v>
+        <v>91482</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8544,33 +8540,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5734</v>
+        <v>5432</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483615</v>
+        <v>483503</v>
       </c>
       <c r="R71" t="n">
-        <v>6991623</v>
+        <v>6991606</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8635,10 +8635,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128150924</v>
+        <v>128150949</v>
       </c>
       <c r="B72" t="n">
-        <v>91470</v>
+        <v>92772</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8646,21 +8646,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8744,7 +8744,7 @@
         <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B74" t="n">
-        <v>90987</v>
+        <v>90266</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,34 +8854,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R74" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8922,6 +8925,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8945,10 +8949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B75" t="n">
-        <v>90254</v>
+        <v>90999</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8956,37 +8960,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R75" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9027,7 +9028,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9051,10 +9051,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128145310</v>
+        <v>128151367</v>
       </c>
       <c r="B76" t="n">
-        <v>90987</v>
+        <v>89514</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9062,34 +9062,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5747</v>
+        <v>275</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>484048</v>
+        <v>483589</v>
       </c>
       <c r="R76" t="n">
-        <v>6991644</v>
+        <v>6991633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9130,6 +9133,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9156,7 +9160,7 @@
         <v>128147310</v>
       </c>
       <c r="B77" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9255,10 +9259,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128151367</v>
+        <v>128145310</v>
       </c>
       <c r="B78" t="n">
-        <v>89502</v>
+        <v>90999</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9266,37 +9270,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>275</v>
+        <v>5747</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483589</v>
+        <v>484048</v>
       </c>
       <c r="R78" t="n">
-        <v>6991633</v>
+        <v>6991644</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9337,7 +9338,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>91572</v>
+        <v>91584</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>89431</v>
+        <v>89443</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>88722</v>
+        <v>88734</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91572</v>
+        <v>91584</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>90987</v>
+        <v>90999</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90254</v>
+        <v>90266</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>90985</v>
+        <v>90997</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90972</v>
+        <v>90984</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>91464</v>
+        <v>92746</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,34 +5196,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,10 +5291,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128146450</v>
       </c>
       <c r="B40" t="n">
-        <v>91007</v>
+        <v>91464</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,37 +5302,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5369,7 +5370,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,48 +5393,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128147638</v>
+        <v>128145519</v>
       </c>
       <c r="B41" t="n">
-        <v>92746</v>
+        <v>100674</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>222771</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483719</v>
+        <v>483943</v>
       </c>
       <c r="R41" t="n">
-        <v>6991835</v>
+        <v>6991638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5472,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,45 +5495,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B42" t="n">
-        <v>100674</v>
+        <v>91007</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128148839</v>
+        <v>128152853</v>
       </c>
       <c r="B55" t="n">
-        <v>92772</v>
+        <v>91482</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,21 +6872,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,14 +6895,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483370</v>
+        <v>483774</v>
       </c>
       <c r="R55" t="n">
-        <v>6991758</v>
+        <v>6991911</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6967,45 +6967,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B56" t="n">
-        <v>90925</v>
+        <v>88733</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R56" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7049,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,45 +7073,48 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128146254</v>
+        <v>128148839</v>
       </c>
       <c r="B57" t="n">
-        <v>90999</v>
+        <v>92772</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483825</v>
+        <v>483370</v>
       </c>
       <c r="R57" t="n">
-        <v>6991736</v>
+        <v>6991758</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7148,6 +7155,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7171,10 +7179,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128152853</v>
+        <v>128146291</v>
       </c>
       <c r="B58" t="n">
-        <v>91482</v>
+        <v>90925</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7182,37 +7190,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>3286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483774</v>
+        <v>483855</v>
       </c>
       <c r="R58" t="n">
-        <v>6991911</v>
+        <v>6991698</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7253,7 +7258,6 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7277,10 +7281,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128151387</v>
+        <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>88733</v>
+        <v>90999</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7288,37 +7292,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>824</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483598</v>
+        <v>483825</v>
       </c>
       <c r="R59" t="n">
-        <v>6991632</v>
+        <v>6991736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7359,7 +7360,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90266</v>
+        <v>90999</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,37 +8854,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R74" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8922,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8949,10 +8945,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>90999</v>
+        <v>90266</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8960,34 +8956,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R75" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,6 +9027,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -9051,48 +9051,45 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B76" t="n">
-        <v>89514</v>
+        <v>88734</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R76" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9133,7 +9130,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9157,32 +9153,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128147310</v>
+        <v>128145310</v>
       </c>
       <c r="B77" t="n">
-        <v>88734</v>
+        <v>90999</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9192,10 +9188,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483747</v>
+        <v>484048</v>
       </c>
       <c r="R77" t="n">
-        <v>6991783</v>
+        <v>6991644</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9259,10 +9255,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128145310</v>
+        <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>90999</v>
+        <v>89514</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9270,34 +9266,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5747</v>
+        <v>275</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>484048</v>
+        <v>483589</v>
       </c>
       <c r="R78" t="n">
-        <v>6991644</v>
+        <v>6991633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9338,6 +9337,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,32 +3597,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128151830</v>
+        <v>128148746</v>
       </c>
       <c r="B24" t="n">
-        <v>90999</v>
+        <v>92748</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483768</v>
+        <v>483384</v>
       </c>
       <c r="R24" t="n">
-        <v>6991562</v>
+        <v>6991763</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128151674</v>
+        <v>128146899</v>
       </c>
       <c r="B25" t="n">
-        <v>92772</v>
+        <v>91586</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3714,37 +3714,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483639</v>
+        <v>483803</v>
       </c>
       <c r="R25" t="n">
-        <v>6991536</v>
+        <v>6991652</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3785,7 +3782,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3809,32 +3805,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128148746</v>
+        <v>128145243</v>
       </c>
       <c r="B26" t="n">
-        <v>92746</v>
+        <v>92401</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>4769</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3843,14 +3839,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483384</v>
+        <v>484061</v>
       </c>
       <c r="R26" t="n">
-        <v>6991763</v>
+        <v>6991711</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3915,45 +3911,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146899</v>
+        <v>128151830</v>
       </c>
       <c r="B27" t="n">
-        <v>91584</v>
+        <v>91001</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483803</v>
+        <v>483768</v>
       </c>
       <c r="R27" t="n">
-        <v>6991652</v>
+        <v>6991562</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3994,6 +3993,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128145243</v>
+        <v>128151674</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>92774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4051,14 +4051,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484061</v>
+        <v>483639</v>
       </c>
       <c r="R28" t="n">
-        <v>6991711</v>
+        <v>6991536</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128151907</v>
+        <v>128148629</v>
       </c>
       <c r="B29" t="n">
-        <v>92746</v>
+        <v>92788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4157,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483759</v>
+        <v>483486</v>
       </c>
       <c r="R29" t="n">
-        <v>6991515</v>
+        <v>6991836</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4229,10 +4229,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148629</v>
+        <v>128145822</v>
       </c>
       <c r="B30" t="n">
-        <v>92786</v>
+        <v>91009</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,37 +4240,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1968</v>
+        <v>5754</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483486</v>
+        <v>483907</v>
       </c>
       <c r="R30" t="n">
-        <v>6991836</v>
+        <v>6991607</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4311,7 +4308,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4338,7 +4334,7 @@
         <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4441,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128145822</v>
+        <v>128151907</v>
       </c>
       <c r="B32" t="n">
-        <v>91007</v>
+        <v>92748</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4452,34 +4448,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483907</v>
+        <v>483759</v>
       </c>
       <c r="R32" t="n">
-        <v>6991607</v>
+        <v>6991515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4520,6 +4519,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4546,7 +4546,7 @@
         <v>128148801</v>
       </c>
       <c r="B33" t="n">
-        <v>92753</v>
+        <v>92755</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148749</v>
       </c>
       <c r="B34" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88733</v>
+        <v>90994</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90992</v>
+        <v>88735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,49 +4972,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B37" t="n">
-        <v>97609</v>
+        <v>91001</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,48 +5078,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B38" t="n">
-        <v>90999</v>
+        <v>97611</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128151475</v>
       </c>
       <c r="B39" t="n">
-        <v>92746</v>
+        <v>91009</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,21 +5196,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5219,14 +5219,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>483615</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991623</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,32 +5291,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B40" t="n">
-        <v>91464</v>
+        <v>100679</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R40" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5393,45 +5393,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B41" t="n">
-        <v>100674</v>
+        <v>92748</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R41" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128151475</v>
+        <v>128146450</v>
       </c>
       <c r="B42" t="n">
-        <v>91007</v>
+        <v>91466</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,37 +5510,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R42" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128151646</v>
+        <v>128148255</v>
       </c>
       <c r="B43" t="n">
-        <v>88734</v>
+        <v>92750</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5635,14 +5635,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483638</v>
+        <v>483625</v>
       </c>
       <c r="R43" t="n">
-        <v>6991579</v>
+        <v>6991850</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5710,7 +5710,7 @@
         <v>128152204</v>
       </c>
       <c r="B44" t="n">
-        <v>88733</v>
+        <v>88735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>128147461</v>
       </c>
       <c r="B45" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B46" t="n">
-        <v>92748</v>
+        <v>88736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R46" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,48 +6021,45 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151718</v>
+        <v>128146959</v>
       </c>
       <c r="B47" t="n">
-        <v>90984</v>
+        <v>90927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256335</v>
+        <v>3286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483661</v>
+        <v>483814</v>
       </c>
       <c r="R47" t="n">
-        <v>6991539</v>
+        <v>6991692</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6103,7 +6100,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6127,10 +6123,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90925</v>
+        <v>92774</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6138,34 +6134,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6206,6 +6205,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6229,32 +6229,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151897</v>
+        <v>128151718</v>
       </c>
       <c r="B49" t="n">
-        <v>92772</v>
+        <v>90986</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4368</v>
+        <v>256335</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483761</v>
+        <v>483661</v>
       </c>
       <c r="R49" t="n">
-        <v>6991506</v>
+        <v>6991539</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6335,32 +6335,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128147670</v>
+        <v>128149405</v>
       </c>
       <c r="B50" t="n">
-        <v>90999</v>
+        <v>91586</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6369,14 +6369,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483723</v>
+        <v>483367</v>
       </c>
       <c r="R50" t="n">
-        <v>6991850</v>
+        <v>6991677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6444,7 +6444,7 @@
         <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6543,32 +6543,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128149405</v>
+        <v>128147670</v>
       </c>
       <c r="B52" t="n">
-        <v>91584</v>
+        <v>91001</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6577,14 +6577,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483367</v>
+        <v>483723</v>
       </c>
       <c r="R52" t="n">
-        <v>6991677</v>
+        <v>6991850</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6652,7 +6652,7 @@
         <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128152853</v>
+        <v>128148839</v>
       </c>
       <c r="B55" t="n">
-        <v>91482</v>
+        <v>92774</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,21 +6872,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6895,14 +6895,14 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483774</v>
+        <v>483370</v>
       </c>
       <c r="R55" t="n">
-        <v>6991911</v>
+        <v>6991758</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6967,48 +6967,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128151387</v>
+        <v>128146291</v>
       </c>
       <c r="B56" t="n">
-        <v>88733</v>
+        <v>90927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>824</v>
+        <v>3286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483598</v>
+        <v>483855</v>
       </c>
       <c r="R56" t="n">
-        <v>6991632</v>
+        <v>6991698</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7049,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7073,32 +7069,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128148839</v>
+        <v>128151387</v>
       </c>
       <c r="B57" t="n">
-        <v>92772</v>
+        <v>88735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4368</v>
+        <v>824</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7107,14 +7103,14 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483370</v>
+        <v>483598</v>
       </c>
       <c r="R57" t="n">
-        <v>6991758</v>
+        <v>6991632</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7179,10 +7175,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128146291</v>
+        <v>128152853</v>
       </c>
       <c r="B58" t="n">
-        <v>90925</v>
+        <v>91484</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7190,34 +7186,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483855</v>
+        <v>483774</v>
       </c>
       <c r="R58" t="n">
-        <v>6991698</v>
+        <v>6991911</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7258,6 +7257,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>128145365</v>
       </c>
       <c r="B60" t="n">
-        <v>92786</v>
+        <v>92788</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7485,10 +7485,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B61" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7523,10 +7523,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B62" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7629,10 +7629,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R62" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B63" t="n">
-        <v>92772</v>
+        <v>92418</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R63" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,10 +7803,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128152970</v>
+        <v>128148761</v>
       </c>
       <c r="B64" t="n">
-        <v>91007</v>
+        <v>92774</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7814,21 +7814,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483774</v>
+        <v>483384</v>
       </c>
       <c r="R64" t="n">
-        <v>6991911</v>
+        <v>6991763</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7909,32 +7909,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128145274</v>
+        <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>92416</v>
+        <v>91484</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4787</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7943,14 +7943,14 @@
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484038</v>
+        <v>483483</v>
       </c>
       <c r="R65" t="n">
-        <v>6991684</v>
+        <v>6991836</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148640</v>
+        <v>128152970</v>
       </c>
       <c r="B66" t="n">
-        <v>91482</v>
+        <v>91009</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>5754</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483483</v>
+        <v>483774</v>
       </c>
       <c r="R66" t="n">
-        <v>6991836</v>
+        <v>6991911</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,48 +8121,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128152208</v>
+        <v>128146630</v>
       </c>
       <c r="B67" t="n">
-        <v>91584</v>
+        <v>91001</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483808</v>
+        <v>483783</v>
       </c>
       <c r="R67" t="n">
-        <v>6991708</v>
+        <v>6991660</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8203,7 +8200,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8227,41 +8223,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128146568</v>
+        <v>128152208</v>
       </c>
       <c r="B68" t="n">
-        <v>86991</v>
+        <v>91586</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3624</v>
+        <v>3277</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483803</v>
+        <v>483808</v>
       </c>
       <c r="R68" t="n">
-        <v>6991669</v>
+        <v>6991708</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8302,6 +8305,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8325,45 +8329,44 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128146630</v>
+        <v>128151479</v>
       </c>
       <c r="B69" t="n">
-        <v>90999</v>
+        <v>90962</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5747</v>
+        <v>5734</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483783</v>
+        <v>483615</v>
       </c>
       <c r="R69" t="n">
-        <v>6991660</v>
+        <v>6991623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8404,6 +8407,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -8427,10 +8431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128151479</v>
+        <v>128150924</v>
       </c>
       <c r="B70" t="n">
-        <v>90960</v>
+        <v>91484</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8438,33 +8442,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5734</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483615</v>
+        <v>483503</v>
       </c>
       <c r="R70" t="n">
-        <v>6991623</v>
+        <v>6991606</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8529,10 +8537,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128150924</v>
+        <v>128150949</v>
       </c>
       <c r="B71" t="n">
-        <v>91482</v>
+        <v>92774</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8540,21 +8548,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8635,48 +8643,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128150949</v>
+        <v>128146568</v>
       </c>
       <c r="B72" t="n">
-        <v>92772</v>
+        <v>86993</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4368</v>
+        <v>3624</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483503</v>
+        <v>483803</v>
       </c>
       <c r="R72" t="n">
-        <v>6991606</v>
+        <v>6991669</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8717,7 +8718,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8744,7 +8744,7 @@
         <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8846,7 +8846,7 @@
         <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>90266</v>
+        <v>90268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,32 +9051,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128147310</v>
+        <v>128145310</v>
       </c>
       <c r="B76" t="n">
-        <v>88734</v>
+        <v>91001</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9086,10 +9086,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483747</v>
+        <v>484048</v>
       </c>
       <c r="R76" t="n">
-        <v>6991783</v>
+        <v>6991644</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9153,10 +9153,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128145310</v>
+        <v>128151367</v>
       </c>
       <c r="B77" t="n">
-        <v>90999</v>
+        <v>89516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9164,34 +9164,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>275</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>484048</v>
+        <v>483589</v>
       </c>
       <c r="R77" t="n">
-        <v>6991644</v>
+        <v>6991633</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9232,6 +9235,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9255,48 +9259,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B78" t="n">
-        <v>89514</v>
+        <v>88736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R78" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9337,7 +9338,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>91584</v>
+        <v>91586</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>89443</v>
+        <v>89445</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>88734</v>
+        <v>88736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91584</v>
+        <v>91586</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>90999</v>
+        <v>91001</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90266</v>
+        <v>90268</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>90997</v>
+        <v>90999</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90984</v>
+        <v>90986</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3703,45 +3703,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146899</v>
+        <v>128145243</v>
       </c>
       <c r="B25" t="n">
-        <v>91586</v>
+        <v>92401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3277</v>
+        <v>4769</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483803</v>
+        <v>484061</v>
       </c>
       <c r="R25" t="n">
-        <v>6991652</v>
+        <v>6991711</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3782,6 +3785,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3805,48 +3809,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128145243</v>
+        <v>128146899</v>
       </c>
       <c r="B26" t="n">
-        <v>92401</v>
+        <v>91586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4769</v>
+        <v>3277</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484061</v>
+        <v>483803</v>
       </c>
       <c r="R26" t="n">
-        <v>6991711</v>
+        <v>6991652</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3887,7 +3888,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151830</v>
+        <v>128151674</v>
       </c>
       <c r="B27" t="n">
-        <v>91001</v>
+        <v>92774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5747</v>
+        <v>4368</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3949,10 +3949,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483768</v>
+        <v>483639</v>
       </c>
       <c r="R27" t="n">
-        <v>6991562</v>
+        <v>6991536</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,32 +4017,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151674</v>
+        <v>128151830</v>
       </c>
       <c r="B28" t="n">
-        <v>92774</v>
+        <v>91001</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483639</v>
+        <v>483768</v>
       </c>
       <c r="R28" t="n">
-        <v>6991536</v>
+        <v>6991562</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128148629</v>
+        <v>128151907</v>
       </c>
       <c r="B29" t="n">
-        <v>92788</v>
+        <v>92748</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,21 +4134,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4157,14 +4157,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483486</v>
+        <v>483759</v>
       </c>
       <c r="R29" t="n">
-        <v>6991836</v>
+        <v>6991515</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128151907</v>
+        <v>128148629</v>
       </c>
       <c r="B32" t="n">
-        <v>92748</v>
+        <v>92788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>1968</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483759</v>
+        <v>483486</v>
       </c>
       <c r="R32" t="n">
-        <v>6991515</v>
+        <v>6991836</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,32 +4543,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128148801</v>
+        <v>128148749</v>
       </c>
       <c r="B33" t="n">
-        <v>92755</v>
+        <v>92750</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1435</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483378</v>
+        <v>483384</v>
       </c>
       <c r="R33" t="n">
         <v>6991763</v>
@@ -4649,32 +4649,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128148749</v>
+        <v>128148801</v>
       </c>
       <c r="B34" t="n">
-        <v>92750</v>
+        <v>92755</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>1435</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483384</v>
+        <v>483378</v>
       </c>
       <c r="R34" t="n">
         <v>6991763</v>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B35" t="n">
-        <v>90994</v>
+        <v>88735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,11 +4829,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4866,32 +4861,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B36" t="n">
-        <v>88735</v>
+        <v>90994</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4900,14 +4895,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4940,6 +4935,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5291,32 +5291,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128145519</v>
+        <v>128146450</v>
       </c>
       <c r="B40" t="n">
-        <v>100679</v>
+        <v>91466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222771</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483943</v>
+        <v>483803</v>
       </c>
       <c r="R40" t="n">
-        <v>6991638</v>
+        <v>6991669</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>91466</v>
+        <v>100685</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,10 +5601,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B43" t="n">
-        <v>92750</v>
+        <v>88736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5612,21 +5612,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5635,14 +5635,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R43" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128151646</v>
+        <v>128148255</v>
       </c>
       <c r="B46" t="n">
-        <v>88736</v>
+        <v>92750</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483638</v>
+        <v>483625</v>
       </c>
       <c r="R46" t="n">
-        <v>6991579</v>
+        <v>6991850</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6123,32 +6123,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128151718</v>
       </c>
       <c r="B48" t="n">
-        <v>92774</v>
+        <v>90986</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>256335</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6161,10 +6161,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483661</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991539</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6229,32 +6229,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151718</v>
+        <v>128151897</v>
       </c>
       <c r="B49" t="n">
-        <v>90986</v>
+        <v>92774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>256335</v>
+        <v>4368</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6267,10 +6267,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483661</v>
+        <v>483761</v>
       </c>
       <c r="R49" t="n">
-        <v>6991539</v>
+        <v>6991506</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6335,32 +6335,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128149405</v>
+        <v>128147670</v>
       </c>
       <c r="B50" t="n">
-        <v>91586</v>
+        <v>91001</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6369,14 +6369,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483367</v>
+        <v>483723</v>
       </c>
       <c r="R50" t="n">
-        <v>6991677</v>
+        <v>6991850</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6441,45 +6441,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128149405</v>
       </c>
       <c r="B51" t="n">
-        <v>92790</v>
+        <v>91586</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>3277</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483367</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6520,6 +6523,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6543,48 +6547,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128145589</v>
       </c>
       <c r="B52" t="n">
-        <v>91001</v>
+        <v>92790</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483946</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991610</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6625,7 +6626,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6861,10 +6861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128148839</v>
+        <v>128146291</v>
       </c>
       <c r="B55" t="n">
-        <v>92774</v>
+        <v>90927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,37 +6872,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483370</v>
+        <v>483855</v>
       </c>
       <c r="R55" t="n">
-        <v>6991758</v>
+        <v>6991698</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6943,7 +6940,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6967,10 +6963,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146291</v>
+        <v>128148839</v>
       </c>
       <c r="B56" t="n">
-        <v>90927</v>
+        <v>92774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,34 +6974,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483855</v>
+        <v>483370</v>
       </c>
       <c r="R56" t="n">
-        <v>6991698</v>
+        <v>6991758</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7046,6 +7045,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7069,10 +7069,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128151387</v>
+        <v>128146254</v>
       </c>
       <c r="B57" t="n">
-        <v>88735</v>
+        <v>91001</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7080,37 +7080,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>824</v>
+        <v>5747</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483598</v>
+        <v>483825</v>
       </c>
       <c r="R57" t="n">
-        <v>6991632</v>
+        <v>6991736</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7151,7 +7148,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7175,32 +7171,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128152853</v>
+        <v>128151387</v>
       </c>
       <c r="B58" t="n">
-        <v>91484</v>
+        <v>88735</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>824</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7209,14 +7205,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483774</v>
+        <v>483598</v>
       </c>
       <c r="R58" t="n">
-        <v>6991911</v>
+        <v>6991632</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7281,45 +7277,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128152853</v>
       </c>
       <c r="B59" t="n">
-        <v>91001</v>
+        <v>91484</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483774</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991911</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7360,6 +7359,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7383,45 +7383,48 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128145365</v>
+        <v>128148620</v>
       </c>
       <c r="B60" t="n">
-        <v>92788</v>
+        <v>91001</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1968</v>
+        <v>5747</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483955</v>
+        <v>483486</v>
       </c>
       <c r="R60" t="n">
-        <v>6991637</v>
+        <v>6991836</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7462,6 +7465,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7485,7 +7489,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B61" t="n">
         <v>91001</v>
@@ -7523,10 +7527,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7591,48 +7595,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128148828</v>
+        <v>128145365</v>
       </c>
       <c r="B62" t="n">
-        <v>91001</v>
+        <v>92788</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5747</v>
+        <v>1968</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483378</v>
+        <v>483955</v>
       </c>
       <c r="R62" t="n">
-        <v>6991763</v>
+        <v>6991637</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7673,7 +7674,6 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7697,32 +7697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128145274</v>
+        <v>128152970</v>
       </c>
       <c r="B63" t="n">
-        <v>92418</v>
+        <v>91009</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4787</v>
+        <v>5754</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7735,10 +7735,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484038</v>
+        <v>483774</v>
       </c>
       <c r="R63" t="n">
-        <v>6991684</v>
+        <v>6991911</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7803,32 +7803,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128148761</v>
+        <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>92774</v>
+        <v>92418</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4368</v>
+        <v>4787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7837,14 +7837,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>483384</v>
+        <v>484038</v>
       </c>
       <c r="R64" t="n">
-        <v>6991763</v>
+        <v>6991684</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128152970</v>
+        <v>128148761</v>
       </c>
       <c r="B66" t="n">
-        <v>91009</v>
+        <v>92774</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483774</v>
+        <v>483384</v>
       </c>
       <c r="R66" t="n">
-        <v>6991911</v>
+        <v>6991763</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8223,48 +8223,41 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128152208</v>
+        <v>128146568</v>
       </c>
       <c r="B68" t="n">
-        <v>91586</v>
+        <v>86993</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3277</v>
+        <v>3624</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483808</v>
+        <v>483803</v>
       </c>
       <c r="R68" t="n">
-        <v>6991708</v>
+        <v>6991669</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8305,7 +8298,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8329,10 +8321,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128151479</v>
+        <v>128152208</v>
       </c>
       <c r="B69" t="n">
-        <v>90962</v>
+        <v>91586</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8340,33 +8332,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5734</v>
+        <v>3277</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Alloclavaria purpurea</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483615</v>
+        <v>483808</v>
       </c>
       <c r="R69" t="n">
-        <v>6991623</v>
+        <v>6991708</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8431,10 +8427,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150924</v>
+        <v>128150949</v>
       </c>
       <c r="B70" t="n">
-        <v>91484</v>
+        <v>92774</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8442,21 +8438,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8537,10 +8533,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128150949</v>
+        <v>128151479</v>
       </c>
       <c r="B71" t="n">
-        <v>92774</v>
+        <v>90962</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8548,37 +8544,33 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4368</v>
+        <v>5734</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483503</v>
+        <v>483615</v>
       </c>
       <c r="R71" t="n">
-        <v>6991606</v>
+        <v>6991623</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8643,41 +8635,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128146568</v>
+        <v>128150924</v>
       </c>
       <c r="B72" t="n">
-        <v>86993</v>
+        <v>91484</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3624</v>
+        <v>5432</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483803</v>
+        <v>483503</v>
       </c>
       <c r="R72" t="n">
-        <v>6991669</v>
+        <v>6991606</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8718,6 +8717,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9153,48 +9153,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B77" t="n">
-        <v>89516</v>
+        <v>88736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R77" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9235,7 +9232,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -9259,45 +9255,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128147310</v>
+        <v>128151367</v>
       </c>
       <c r="B78" t="n">
-        <v>88736</v>
+        <v>89516</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4412</v>
+        <v>275</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483747</v>
+        <v>483589</v>
       </c>
       <c r="R78" t="n">
-        <v>6991783</v>
+        <v>6991633</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9338,6 +9337,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4972,48 +4972,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>91001</v>
+        <v>97611</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,49 +5079,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>97611</v>
+        <v>91001</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R38" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,10 +5185,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128151475</v>
+        <v>128146450</v>
       </c>
       <c r="B39" t="n">
-        <v>91009</v>
+        <v>91466</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5196,37 +5196,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R39" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5267,7 +5264,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5291,10 +5287,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128146450</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>91466</v>
+        <v>91009</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5302,34 +5298,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483803</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991669</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5370,6 +5369,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5393,48 +5393,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128147638</v>
+        <v>128145519</v>
       </c>
       <c r="B41" t="n">
-        <v>92748</v>
+        <v>100685</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4361</v>
+        <v>222771</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483719</v>
+        <v>483943</v>
       </c>
       <c r="R41" t="n">
-        <v>6991835</v>
+        <v>6991638</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5472,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,45 +5495,48 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B42" t="n">
-        <v>100685</v>
+        <v>92748</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5578,6 +5577,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5601,32 +5601,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128151646</v>
+        <v>128152204</v>
       </c>
       <c r="B43" t="n">
-        <v>88736</v>
+        <v>88735</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4412</v>
+        <v>824</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5635,14 +5635,14 @@
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483638</v>
+        <v>483808</v>
       </c>
       <c r="R43" t="n">
-        <v>6991579</v>
+        <v>6991708</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5707,32 +5707,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128152204</v>
+        <v>128151646</v>
       </c>
       <c r="B44" t="n">
-        <v>88735</v>
+        <v>88736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5741,14 +5741,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483808</v>
+        <v>483638</v>
       </c>
       <c r="R44" t="n">
-        <v>6991708</v>
+        <v>6991579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128146959</v>
+        <v>128151897</v>
       </c>
       <c r="B47" t="n">
-        <v>90927</v>
+        <v>92774</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,34 +6032,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3286</v>
+        <v>4368</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483814</v>
+        <v>483761</v>
       </c>
       <c r="R47" t="n">
-        <v>6991692</v>
+        <v>6991506</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6100,6 +6103,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6229,10 +6233,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128151897</v>
+        <v>128146959</v>
       </c>
       <c r="B49" t="n">
-        <v>92774</v>
+        <v>90927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6240,37 +6244,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4368</v>
+        <v>3286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483761</v>
+        <v>483814</v>
       </c>
       <c r="R49" t="n">
-        <v>6991506</v>
+        <v>6991692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6311,7 +6312,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6861,45 +6861,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128146291</v>
+        <v>128151387</v>
       </c>
       <c r="B55" t="n">
-        <v>90927</v>
+        <v>88735</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3286</v>
+        <v>824</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483855</v>
+        <v>483598</v>
       </c>
       <c r="R55" t="n">
-        <v>6991698</v>
+        <v>6991632</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6940,6 +6943,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6963,10 +6967,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128148839</v>
+        <v>128152853</v>
       </c>
       <c r="B56" t="n">
-        <v>92774</v>
+        <v>91484</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6974,21 +6978,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4368</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6997,14 +7001,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483370</v>
+        <v>483774</v>
       </c>
       <c r="R56" t="n">
-        <v>6991758</v>
+        <v>6991911</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7069,32 +7073,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128146254</v>
+        <v>128146291</v>
       </c>
       <c r="B57" t="n">
-        <v>91001</v>
+        <v>90927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7104,10 +7108,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483825</v>
+        <v>483855</v>
       </c>
       <c r="R57" t="n">
-        <v>6991736</v>
+        <v>6991698</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7171,32 +7175,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128151387</v>
+        <v>128148839</v>
       </c>
       <c r="B58" t="n">
-        <v>88735</v>
+        <v>92774</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>824</v>
+        <v>4368</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7205,14 +7209,14 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483598</v>
+        <v>483370</v>
       </c>
       <c r="R58" t="n">
-        <v>6991632</v>
+        <v>6991758</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7277,48 +7281,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B59" t="n">
-        <v>91484</v>
+        <v>91001</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R59" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7359,7 +7360,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B74" t="n">
-        <v>91001</v>
+        <v>90268</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,34 +8854,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R74" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8922,6 +8925,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8945,10 +8949,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B75" t="n">
-        <v>90268</v>
+        <v>91001</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8956,37 +8960,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R75" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9027,7 +9028,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -3597,10 +3597,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128148746</v>
+        <v>128151674</v>
       </c>
       <c r="B24" t="n">
-        <v>92748</v>
+        <v>92775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,21 +3608,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3631,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483384</v>
+        <v>483639</v>
       </c>
       <c r="R24" t="n">
-        <v>6991763</v>
+        <v>6991536</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3703,32 +3703,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128145243</v>
+        <v>128148746</v>
       </c>
       <c r="B25" t="n">
-        <v>92401</v>
+        <v>92749</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4769</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3737,14 +3737,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484061</v>
+        <v>483384</v>
       </c>
       <c r="R25" t="n">
-        <v>6991711</v>
+        <v>6991763</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3812,7 +3812,7 @@
         <v>128146899</v>
       </c>
       <c r="B26" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128151674</v>
+        <v>128145243</v>
       </c>
       <c r="B27" t="n">
-        <v>92774</v>
+        <v>92402</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4368</v>
+        <v>4769</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3945,14 +3945,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>483639</v>
+        <v>484061</v>
       </c>
       <c r="R27" t="n">
-        <v>6991536</v>
+        <v>6991711</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4020,7 +4020,7 @@
         <v>128151830</v>
       </c>
       <c r="B28" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>128151907</v>
       </c>
       <c r="B29" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4232,7 +4232,7 @@
         <v>128145822</v>
       </c>
       <c r="B30" t="n">
-        <v>91009</v>
+        <v>91010</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>128148843</v>
       </c>
       <c r="B31" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>128148629</v>
       </c>
       <c r="B32" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>128148749</v>
       </c>
       <c r="B33" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>128148801</v>
       </c>
       <c r="B34" t="n">
-        <v>92755</v>
+        <v>92756</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4755,32 +4755,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128151242</v>
+        <v>128146454</v>
       </c>
       <c r="B35" t="n">
-        <v>88735</v>
+        <v>90995</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>824</v>
+        <v>256756</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4789,14 +4789,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483560</v>
+        <v>483803</v>
       </c>
       <c r="R35" t="n">
-        <v>6991627</v>
+        <v>6991669</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4829,6 +4829,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4861,32 +4866,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146454</v>
+        <v>128151242</v>
       </c>
       <c r="B36" t="n">
-        <v>90994</v>
+        <v>88735</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>256756</v>
+        <v>824</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4895,14 +4900,14 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483803</v>
+        <v>483560</v>
       </c>
       <c r="R36" t="n">
-        <v>6991669</v>
+        <v>6991627</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4935,11 +4940,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4972,49 +4972,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B37" t="n">
-        <v>97611</v>
+        <v>91002</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +5060,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,48 +5078,49 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B38" t="n">
-        <v>91001</v>
+        <v>97612</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,32 +5185,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B39" t="n">
-        <v>91466</v>
+        <v>100686</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R39" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5287,10 +5287,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128147638</v>
       </c>
       <c r="B40" t="n">
-        <v>91009</v>
+        <v>92749</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,21 +5298,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5321,14 +5321,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>483719</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991835</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5393,45 +5393,48 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128145519</v>
+        <v>128151475</v>
       </c>
       <c r="B41" t="n">
-        <v>100685</v>
+        <v>91010</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>222771</v>
+        <v>5754</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483943</v>
+        <v>483615</v>
       </c>
       <c r="R41" t="n">
-        <v>6991638</v>
+        <v>6991623</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5472,6 +5475,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5495,10 +5499,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128147638</v>
+        <v>128146450</v>
       </c>
       <c r="B42" t="n">
-        <v>92748</v>
+        <v>91467</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5506,37 +5510,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4361</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483719</v>
+        <v>483803</v>
       </c>
       <c r="R42" t="n">
-        <v>6991835</v>
+        <v>6991669</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5577,7 +5578,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5707,7 +5707,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128151646</v>
+        <v>128147461</v>
       </c>
       <c r="B44" t="n">
         <v>88736</v>
@@ -5736,19 +5736,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483638</v>
+        <v>483735</v>
       </c>
       <c r="R44" t="n">
-        <v>6991579</v>
+        <v>6991823</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5789,7 +5786,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5813,10 +5809,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128147461</v>
+        <v>128148255</v>
       </c>
       <c r="B45" t="n">
-        <v>88736</v>
+        <v>92751</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5824,34 +5820,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4412</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483735</v>
+        <v>483625</v>
       </c>
       <c r="R45" t="n">
-        <v>6991823</v>
+        <v>6991850</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5892,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5915,10 +5915,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128148255</v>
+        <v>128151646</v>
       </c>
       <c r="B46" t="n">
-        <v>92750</v>
+        <v>88736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,21 +5926,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>4412</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5949,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483625</v>
+        <v>483638</v>
       </c>
       <c r="R46" t="n">
-        <v>6991850</v>
+        <v>6991579</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,32 +6021,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151897</v>
+        <v>128151718</v>
       </c>
       <c r="B47" t="n">
-        <v>92774</v>
+        <v>90987</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4368</v>
+        <v>256335</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6059,10 +6059,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483761</v>
+        <v>483661</v>
       </c>
       <c r="R47" t="n">
-        <v>6991506</v>
+        <v>6991539</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6127,32 +6127,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151718</v>
+        <v>128151897</v>
       </c>
       <c r="B48" t="n">
-        <v>90986</v>
+        <v>92775</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>256335</v>
+        <v>4368</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6165,10 +6165,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483661</v>
+        <v>483761</v>
       </c>
       <c r="R48" t="n">
-        <v>6991539</v>
+        <v>6991506</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6236,7 +6236,7 @@
         <v>128146959</v>
       </c>
       <c r="B49" t="n">
-        <v>90927</v>
+        <v>90928</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6335,32 +6335,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128147670</v>
+        <v>128149405</v>
       </c>
       <c r="B50" t="n">
-        <v>91001</v>
+        <v>91587</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5747</v>
+        <v>3277</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6369,14 +6369,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483723</v>
+        <v>483367</v>
       </c>
       <c r="R50" t="n">
-        <v>6991850</v>
+        <v>6991677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6441,48 +6441,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128149405</v>
+        <v>128145589</v>
       </c>
       <c r="B51" t="n">
-        <v>91586</v>
+        <v>92791</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3277</v>
+        <v>5964</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483367</v>
+        <v>483946</v>
       </c>
       <c r="R51" t="n">
-        <v>6991677</v>
+        <v>6991610</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6523,7 +6520,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -6547,45 +6543,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128145589</v>
+        <v>128147670</v>
       </c>
       <c r="B52" t="n">
-        <v>92790</v>
+        <v>91002</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483946</v>
+        <v>483723</v>
       </c>
       <c r="R52" t="n">
-        <v>6991610</v>
+        <v>6991850</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6626,6 +6625,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B53" t="n">
-        <v>92748</v>
+        <v>91002</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B54" t="n">
-        <v>91001</v>
+        <v>92749</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R54" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6967,48 +6967,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128152853</v>
+        <v>128146254</v>
       </c>
       <c r="B56" t="n">
-        <v>91484</v>
+        <v>91002</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>5747</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483774</v>
+        <v>483825</v>
       </c>
       <c r="R56" t="n">
-        <v>6991911</v>
+        <v>6991736</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7049,7 +7046,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -7073,10 +7069,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128146291</v>
+        <v>128152853</v>
       </c>
       <c r="B57" t="n">
-        <v>90927</v>
+        <v>91485</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7084,34 +7080,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3286</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483855</v>
+        <v>483774</v>
       </c>
       <c r="R57" t="n">
-        <v>6991698</v>
+        <v>6991911</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7152,6 +7151,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7178,7 +7178,7 @@
         <v>128148839</v>
       </c>
       <c r="B58" t="n">
-        <v>92774</v>
+        <v>92775</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7281,32 +7281,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146254</v>
+        <v>128146291</v>
       </c>
       <c r="B59" t="n">
-        <v>91001</v>
+        <v>90928</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5747</v>
+        <v>3286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7316,10 +7316,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483825</v>
+        <v>483855</v>
       </c>
       <c r="R59" t="n">
-        <v>6991736</v>
+        <v>6991698</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7383,10 +7383,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128148620</v>
+        <v>128148828</v>
       </c>
       <c r="B60" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R60" t="n">
-        <v>6991836</v>
+        <v>6991763</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7489,10 +7489,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148828</v>
+        <v>128148620</v>
       </c>
       <c r="B61" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7527,10 +7527,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483378</v>
+        <v>483486</v>
       </c>
       <c r="R61" t="n">
-        <v>6991763</v>
+        <v>6991836</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7598,7 +7598,7 @@
         <v>128145365</v>
       </c>
       <c r="B62" t="n">
-        <v>92788</v>
+        <v>92789</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7697,10 +7697,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128152970</v>
+        <v>128148761</v>
       </c>
       <c r="B63" t="n">
-        <v>91009</v>
+        <v>92775</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7708,21 +7708,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7731,14 +7731,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483774</v>
+        <v>483384</v>
       </c>
       <c r="R63" t="n">
-        <v>6991911</v>
+        <v>6991763</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7806,7 +7806,7 @@
         <v>128145274</v>
       </c>
       <c r="B64" t="n">
-        <v>92418</v>
+        <v>92419</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>128148640</v>
       </c>
       <c r="B65" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128148761</v>
+        <v>128152970</v>
       </c>
       <c r="B66" t="n">
-        <v>92774</v>
+        <v>91010</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8026,21 +8026,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4368</v>
+        <v>5754</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8049,14 +8049,14 @@
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483384</v>
+        <v>483774</v>
       </c>
       <c r="R66" t="n">
-        <v>6991763</v>
+        <v>6991911</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8121,34 +8121,30 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128146630</v>
+        <v>128146568</v>
       </c>
       <c r="B67" t="n">
-        <v>91001</v>
+        <v>86993</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5747</v>
+        <v>3624</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>Christan</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8156,10 +8152,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483783</v>
+        <v>483803</v>
       </c>
       <c r="R67" t="n">
-        <v>6991660</v>
+        <v>6991669</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8223,41 +8219,48 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128146568</v>
+        <v>128150924</v>
       </c>
       <c r="B68" t="n">
-        <v>86993</v>
+        <v>91485</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3624</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483803</v>
+        <v>483503</v>
       </c>
       <c r="R68" t="n">
-        <v>6991669</v>
+        <v>6991606</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8298,6 +8301,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -8321,10 +8325,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128152208</v>
+        <v>128150949</v>
       </c>
       <c r="B69" t="n">
-        <v>91586</v>
+        <v>92775</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8332,21 +8336,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3277</v>
+        <v>4368</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8355,14 +8359,14 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483808</v>
+        <v>483503</v>
       </c>
       <c r="R69" t="n">
-        <v>6991708</v>
+        <v>6991606</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8427,10 +8431,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128150949</v>
+        <v>128152208</v>
       </c>
       <c r="B70" t="n">
-        <v>92774</v>
+        <v>91587</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8438,21 +8442,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4368</v>
+        <v>3277</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8461,14 +8465,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483503</v>
+        <v>483808</v>
       </c>
       <c r="R70" t="n">
-        <v>6991606</v>
+        <v>6991708</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8533,44 +8537,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128151479</v>
+        <v>128146630</v>
       </c>
       <c r="B71" t="n">
-        <v>90962</v>
+        <v>91002</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5734</v>
+        <v>5747</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Druvfingersvampar</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria botrytis s.lat.</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>Ramaria safraniolens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Christan</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483615</v>
+        <v>483783</v>
       </c>
       <c r="R71" t="n">
-        <v>6991623</v>
+        <v>6991660</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8611,7 +8616,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -8635,10 +8639,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128150924</v>
+        <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>91484</v>
+        <v>90963</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8646,37 +8650,33 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5432</v>
+        <v>5734</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Druvfingersvampar</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Ramaria botrytis s.lat.</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483503</v>
+        <v>483615</v>
       </c>
       <c r="R72" t="n">
-        <v>6991606</v>
+        <v>6991623</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8744,7 +8744,7 @@
         <v>128145502</v>
       </c>
       <c r="B73" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>128146085</v>
       </c>
       <c r="B75" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9051,10 +9051,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128145310</v>
+        <v>128151367</v>
       </c>
       <c r="B76" t="n">
-        <v>91001</v>
+        <v>89516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9062,34 +9062,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5747</v>
+        <v>275</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>484048</v>
+        <v>483589</v>
       </c>
       <c r="R76" t="n">
-        <v>6991644</v>
+        <v>6991633</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9130,6 +9133,7 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -9153,32 +9157,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128147310</v>
+        <v>128145310</v>
       </c>
       <c r="B77" t="n">
-        <v>88736</v>
+        <v>91002</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9188,10 +9192,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>483747</v>
+        <v>484048</v>
       </c>
       <c r="R77" t="n">
-        <v>6991783</v>
+        <v>6991644</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9255,48 +9259,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128151367</v>
+        <v>128147310</v>
       </c>
       <c r="B78" t="n">
-        <v>89516</v>
+        <v>88736</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>275</v>
+        <v>4412</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483589</v>
+        <v>483747</v>
       </c>
       <c r="R78" t="n">
-        <v>6991633</v>
+        <v>6991783</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9337,7 +9338,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -9364,7 +9364,7 @@
         <v>128145240</v>
       </c>
       <c r="B79" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91586</v>
+        <v>91587</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>91001</v>
+        <v>91002</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>90999</v>
+        <v>91000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90986</v>
+        <v>90987</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128151907</v>
+        <v>128145822</v>
       </c>
       <c r="B29" t="n">
-        <v>92749</v>
+        <v>91010</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,37 +4134,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483759</v>
+        <v>483907</v>
       </c>
       <c r="R29" t="n">
-        <v>6991515</v>
+        <v>6991607</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4205,7 +4202,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4229,10 +4225,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128145822</v>
+        <v>128148843</v>
       </c>
       <c r="B30" t="n">
-        <v>91010</v>
+        <v>91485</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4240,34 +4236,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5754</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>483907</v>
+        <v>483370</v>
       </c>
       <c r="R30" t="n">
-        <v>6991607</v>
+        <v>6991758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4308,6 +4307,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4331,10 +4331,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148843</v>
+        <v>128148629</v>
       </c>
       <c r="B31" t="n">
-        <v>91485</v>
+        <v>92789</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,21 +4342,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483370</v>
+        <v>483486</v>
       </c>
       <c r="R31" t="n">
-        <v>6991758</v>
+        <v>6991836</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,10 +4437,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128148629</v>
+        <v>128151907</v>
       </c>
       <c r="B32" t="n">
-        <v>92789</v>
+        <v>92749</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +4448,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1968</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4471,14 +4471,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483486</v>
+        <v>483759</v>
       </c>
       <c r="R32" t="n">
-        <v>6991836</v>
+        <v>6991515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4972,48 +4972,49 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128149062</v>
+        <v>128153456</v>
       </c>
       <c r="B37" t="n">
-        <v>91002</v>
+        <v>97612</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483381</v>
+        <v>483832</v>
       </c>
       <c r="R37" t="n">
-        <v>6991732</v>
+        <v>6991926</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5060,7 +5061,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5078,49 +5079,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128153456</v>
+        <v>128149062</v>
       </c>
       <c r="B38" t="n">
-        <v>97612</v>
+        <v>91002</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222741</v>
+        <v>5747</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483832</v>
+        <v>483381</v>
       </c>
       <c r="R38" t="n">
-        <v>6991926</v>
+        <v>6991732</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5185,45 +5185,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128145519</v>
+        <v>128147638</v>
       </c>
       <c r="B39" t="n">
-        <v>100686</v>
+        <v>92749</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222771</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483943</v>
+        <v>483719</v>
       </c>
       <c r="R39" t="n">
-        <v>6991638</v>
+        <v>6991835</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5264,6 +5267,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5287,10 +5291,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128147638</v>
+        <v>128151475</v>
       </c>
       <c r="B40" t="n">
-        <v>92749</v>
+        <v>91010</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5298,21 +5302,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5321,14 +5325,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483719</v>
+        <v>483615</v>
       </c>
       <c r="R40" t="n">
-        <v>6991835</v>
+        <v>6991623</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5393,10 +5397,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128151475</v>
+        <v>128146450</v>
       </c>
       <c r="B41" t="n">
-        <v>91010</v>
+        <v>91467</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5404,37 +5408,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5754</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483615</v>
+        <v>483803</v>
       </c>
       <c r="R41" t="n">
-        <v>6991623</v>
+        <v>6991669</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5475,7 +5476,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5499,32 +5499,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146450</v>
+        <v>128145519</v>
       </c>
       <c r="B42" t="n">
-        <v>91467</v>
+        <v>100686</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>222771</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +5534,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483803</v>
+        <v>483943</v>
       </c>
       <c r="R42" t="n">
-        <v>6991669</v>
+        <v>6991638</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -6649,32 +6649,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151407</v>
+        <v>128151643</v>
       </c>
       <c r="B53" t="n">
-        <v>91002</v>
+        <v>92749</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5747</v>
+        <v>4361</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483602</v>
+        <v>483638</v>
       </c>
       <c r="R53" t="n">
-        <v>6991610</v>
+        <v>6991579</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,32 +6755,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151643</v>
+        <v>128151407</v>
       </c>
       <c r="B54" t="n">
-        <v>92749</v>
+        <v>91002</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4361</v>
+        <v>5747</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6793,10 +6793,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483638</v>
+        <v>483602</v>
       </c>
       <c r="R54" t="n">
-        <v>6991579</v>
+        <v>6991610</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -8843,10 +8843,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128151611</v>
+        <v>128146085</v>
       </c>
       <c r="B74" t="n">
-        <v>90268</v>
+        <v>91002</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8854,37 +8854,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1599</v>
+        <v>5747</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483633</v>
+        <v>483847</v>
       </c>
       <c r="R74" t="n">
-        <v>6991596</v>
+        <v>6991688</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8925,7 +8922,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8949,10 +8945,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128146085</v>
+        <v>128151611</v>
       </c>
       <c r="B75" t="n">
-        <v>91002</v>
+        <v>90268</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8960,34 +8956,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5747</v>
+        <v>1599</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483847</v>
+        <v>483633</v>
       </c>
       <c r="R75" t="n">
-        <v>6991688</v>
+        <v>6991596</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9028,6 +9027,7 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -9470,7 +9470,7 @@
         <v>128149279</v>
       </c>
       <c r="B80" t="n">
-        <v>89445</v>
+        <v>89472</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>128149429</v>
       </c>
       <c r="B81" t="n">
-        <v>88736</v>
+        <v>88763</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9682,7 +9682,7 @@
         <v>128149640</v>
       </c>
       <c r="B82" t="n">
-        <v>91587</v>
+        <v>91614</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9788,7 +9788,7 @@
         <v>128149500</v>
       </c>
       <c r="B83" t="n">
-        <v>91002</v>
+        <v>91029</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>128149450</v>
       </c>
       <c r="B84" t="n">
-        <v>92749</v>
+        <v>92776</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>128149268</v>
       </c>
       <c r="B85" t="n">
-        <v>90268</v>
+        <v>90295</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>91000</v>
+        <v>91027</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>90987</v>
+        <v>91014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>91027</v>
+        <v>91037</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>91014</v>
+        <v>91024</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -10106,7 +10106,7 @@
         <v>128148616</v>
       </c>
       <c r="B86" t="n">
-        <v>91037</v>
+        <v>91041</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
         <v>128151166</v>
       </c>
       <c r="B87" t="n">
-        <v>91024</v>
+        <v>91028</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -8642,7 +8642,7 @@
         <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>91128</v>
+        <v>91130</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -8642,7 +8642,7 @@
         <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>91130</v>
+        <v>91217</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -8642,7 +8642,7 @@
         <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>91217</v>
+        <v>91220</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -8642,7 +8642,7 @@
         <v>128151479</v>
       </c>
       <c r="B72" t="n">
-        <v>91220</v>
+        <v>91246</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY89"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,58 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122708958</v>
+        <v>128151367</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>275</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kejsarskivling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Catathelasma imperiale</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483506</v>
+        <v>483589</v>
       </c>
       <c r="R2" t="n">
-        <v>6991681</v>
+        <v>6991633</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fertila bålar.</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,96 +757,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122708546</v>
+        <v>128151242</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89155</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>824</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483452</v>
+        <v>483560</v>
       </c>
       <c r="R3" t="n">
-        <v>6991602</v>
+        <v>6991627</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,93 +863,72 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122709111</v>
+        <v>128151387</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89155</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>824</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>A.H.Sm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483508</v>
+        <v>483598</v>
       </c>
       <c r="R4" t="n">
-        <v>6991741</v>
+        <v>6991632</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,107 +969,72 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122709081</v>
+        <v>128152204</v>
       </c>
       <c r="B5" t="n">
-        <v>90970</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89155</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>824</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skäggvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hygrophorus inocybiformis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>A.H.Sm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>483515</v>
+        <v>483808</v>
       </c>
       <c r="R5" t="n">
-        <v>6991731</v>
+        <v>6991708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,12 +1061,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,58 +1075,34 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122708596</v>
+        <v>128146450</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,37 +1110,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>483520</v>
+        <v>483803</v>
       </c>
       <c r="R6" t="n">
-        <v>6991663</v>
+        <v>6991669</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1277,12 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,55 +1181,30 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122709756</v>
+        <v>123180336</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,42 +1212,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1352</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Småflikig brosklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina sinensis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>Jatta</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>483522</v>
+        <v>483833</v>
       </c>
       <c r="R7" t="n">
         <v>6991771</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1409,17 +1275,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-02-22</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
+          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1431,99 +1307,78 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123177015</v>
+        <v>128148801</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1435</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bitter taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum fennicum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>483436</v>
+        <v>483378</v>
       </c>
       <c r="R8" t="n">
-        <v>6991677</v>
+        <v>6991763</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1550,27 +1405,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:01</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,92 +1419,72 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123177397</v>
+        <v>128149268</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1599</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>483605</v>
+        <v>483328</v>
       </c>
       <c r="R9" t="n">
-        <v>6991834</v>
+        <v>6991694</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1691,27 +1511,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:13</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,83 +1525,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123176924</v>
+        <v>128151611</v>
       </c>
       <c r="B10" t="n">
-        <v>74879</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>1599</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Fjällfotad musseron</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tricholoma olivaceotinctum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>483383</v>
+        <v>483633</v>
       </c>
       <c r="R10" t="n">
-        <v>6991656</v>
+        <v>6991596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1823,27 +1617,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>09:53</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>09:53</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1852,48 +1631,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123179132</v>
+        <v>128145365</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1901,39 +1666,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1968</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>483553</v>
+        <v>483955</v>
       </c>
       <c r="R11" t="n">
-        <v>6991669</v>
+        <v>6991637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1960,27 +1720,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>10:34</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På grov granhögstubbe (44 cm dbh) i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1992,45 +1737,30 @@
       <c r="AG11" t="b">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123182989</v>
+        <v>128148629</v>
       </c>
       <c r="B12" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2038,34 +1768,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1968</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>483820</v>
+        <v>483486</v>
       </c>
       <c r="R12" t="n">
-        <v>6991546</v>
+        <v>6991836</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2092,27 +1825,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:54</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:54</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2121,33 +1839,34 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123176616</v>
+        <v>128145240</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2155,43 +1874,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>483371</v>
+        <v>484061</v>
       </c>
       <c r="R13" t="n">
-        <v>6991602</v>
+        <v>6991711</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2218,27 +1931,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>09:45</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På grenar på gammal levande gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2247,55 +1945,56 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123180297</v>
+        <v>128146899</v>
       </c>
       <c r="B14" t="n">
-        <v>79898</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>3277</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2305,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>483829</v>
+        <v>483803</v>
       </c>
       <c r="R14" t="n">
-        <v>6991767</v>
+        <v>6991652</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2335,27 +2034,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På grenar på gran stående under gamla aspar</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2367,45 +2051,30 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123176943</v>
+        <v>128149405</v>
       </c>
       <c r="B15" t="n">
-        <v>77721</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2413,34 +2082,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228579</v>
+        <v>3277</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>483380</v>
+        <v>483367</v>
       </c>
       <c r="R15" t="n">
-        <v>6991656</v>
+        <v>6991677</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2467,27 +2139,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>09:54</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>09:54</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2496,48 +2153,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123184445</v>
+        <v>128149640</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2545,34 +2188,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>3277</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Lillhägnen, Lillhägnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>483565</v>
+        <v>483366</v>
       </c>
       <c r="R16" t="n">
-        <v>6991603</v>
+        <v>6991587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2599,27 +2245,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:07</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2628,33 +2259,34 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123177862</v>
+        <v>128152208</v>
       </c>
       <c r="B17" t="n">
-        <v>74879</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2662,42 +2294,40 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>3277</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>483615</v>
+        <v>483808</v>
       </c>
       <c r="R17" t="n">
-        <v>6991838</v>
+        <v>6991708</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2721,27 +2351,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>10:16</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>10:16</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2750,48 +2365,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123182534</v>
+        <v>128146291</v>
       </c>
       <c r="B18" t="n">
-        <v>79869</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2799,21 +2400,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>3286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2823,10 +2424,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484029</v>
+        <v>483855</v>
       </c>
       <c r="R18" t="n">
-        <v>6991692</v>
+        <v>6991698</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2853,27 +2454,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:18</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,45 +2471,30 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123181366</v>
+        <v>128146959</v>
       </c>
       <c r="B19" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2931,21 +2502,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>3286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Quél.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2955,10 +2526,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>483899</v>
+        <v>483814</v>
       </c>
       <c r="R19" t="n">
-        <v>6991685</v>
+        <v>6991692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2985,22 +2556,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3012,89 +2573,61 @@
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123176917</v>
+        <v>128146568</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87412</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>3624</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Strimspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Cortinarius glaucopus s.lat.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>483378</v>
+        <v>483803</v>
       </c>
       <c r="R20" t="n">
-        <v>6991654</v>
+        <v>6991669</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3121,27 +2654,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>09:52</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>09:52</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt på gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3153,45 +2671,30 @@
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123180336</v>
+        <v>128145502</v>
       </c>
       <c r="B21" t="n">
-        <v>79324</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3199,43 +2702,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1352</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Småflikig brosklav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramalina sinensis</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jatta</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>483833</v>
+        <v>483943</v>
       </c>
       <c r="R21" t="n">
-        <v>6991771</v>
+        <v>6991638</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3262,27 +2756,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:06</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande asp (23 cm dbh) i kanten mellan åker och gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3294,45 +2773,30 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123179071</v>
+        <v>128147638</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3340,43 +2804,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>483575</v>
+        <v>483719</v>
       </c>
       <c r="R22" t="n">
-        <v>6991710</v>
+        <v>6991835</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3403,27 +2861,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>10:31</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>10:31</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3432,83 +2875,72 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123182555</v>
+        <v>128148746</v>
       </c>
       <c r="B23" t="n">
-        <v>79773</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>484005</v>
+        <v>483384</v>
       </c>
       <c r="R23" t="n">
-        <v>6991716</v>
+        <v>6991763</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3535,27 +2967,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På asp (40 cm dbh)</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3564,43 +2981,34 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128151674</v>
+        <v>128149450</v>
       </c>
       <c r="B24" t="n">
-        <v>92775</v>
+        <v>93189</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3608,21 +3016,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4368</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3631,14 +3039,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>483639</v>
+        <v>483377</v>
       </c>
       <c r="R24" t="n">
-        <v>6991536</v>
+        <v>6991684</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3685,7 +3093,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3703,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128148746</v>
+        <v>128151643</v>
       </c>
       <c r="B25" t="n">
-        <v>92749</v>
+        <v>93189</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3737,14 +3145,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>483384</v>
+        <v>483638</v>
       </c>
       <c r="R25" t="n">
-        <v>6991763</v>
+        <v>6991579</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3809,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146899</v>
+        <v>128151907</v>
       </c>
       <c r="B26" t="n">
-        <v>91587</v>
+        <v>93189</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3820,34 +3228,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3277</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>483803</v>
+        <v>483759</v>
       </c>
       <c r="R26" t="n">
-        <v>6991652</v>
+        <v>6991515</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3888,6 +3299,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3911,32 +3323,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128145243</v>
+        <v>128148255</v>
       </c>
       <c r="B27" t="n">
-        <v>92402</v>
+        <v>93191</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4769</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3945,14 +3357,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484061</v>
+        <v>483625</v>
       </c>
       <c r="R27" t="n">
-        <v>6991711</v>
+        <v>6991850</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4017,32 +3429,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128151830</v>
+        <v>128148749</v>
       </c>
       <c r="B28" t="n">
-        <v>91002</v>
+        <v>93191</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5747</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -4051,14 +3463,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>483768</v>
+        <v>483384</v>
       </c>
       <c r="R28" t="n">
-        <v>6991562</v>
+        <v>6991763</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4123,10 +3535,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128145822</v>
+        <v>128148761</v>
       </c>
       <c r="B29" t="n">
-        <v>91010</v>
+        <v>93215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4134,34 +3546,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5754</v>
+        <v>4368</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>483907</v>
+        <v>483384</v>
       </c>
       <c r="R29" t="n">
-        <v>6991607</v>
+        <v>6991763</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4202,6 +3617,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4225,10 +3641,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128148843</v>
+        <v>128148839</v>
       </c>
       <c r="B30" t="n">
-        <v>91485</v>
+        <v>93215</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4236,21 +3652,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4331,10 +3747,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128148629</v>
+        <v>128150949</v>
       </c>
       <c r="B31" t="n">
-        <v>92789</v>
+        <v>93215</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4342,21 +3758,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1968</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4369,10 +3785,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>483486</v>
+        <v>483503</v>
       </c>
       <c r="R31" t="n">
-        <v>6991836</v>
+        <v>6991606</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4437,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128151907</v>
+        <v>128151674</v>
       </c>
       <c r="B32" t="n">
-        <v>92749</v>
+        <v>93215</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4448,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4361</v>
+        <v>4368</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4475,10 +3891,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>483759</v>
+        <v>483639</v>
       </c>
       <c r="R32" t="n">
-        <v>6991515</v>
+        <v>6991536</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4543,10 +3959,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128148749</v>
+        <v>128151897</v>
       </c>
       <c r="B33" t="n">
-        <v>92751</v>
+        <v>93215</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4554,21 +3970,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>4368</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4577,14 +3993,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>483384</v>
+        <v>483761</v>
       </c>
       <c r="R33" t="n">
-        <v>6991763</v>
+        <v>6991506</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4649,48 +4065,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128148801</v>
+        <v>128147310</v>
       </c>
       <c r="B34" t="n">
-        <v>92756</v>
+        <v>89156</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1435</v>
+        <v>4412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bitter taggsvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum fennicum</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>483378</v>
+        <v>483747</v>
       </c>
       <c r="R34" t="n">
-        <v>6991763</v>
+        <v>6991783</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4731,7 +4144,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4755,10 +4167,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146454</v>
+        <v>128147461</v>
       </c>
       <c r="B35" t="n">
-        <v>90995</v>
+        <v>89156</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4766,37 +4178,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>256756</v>
+        <v>4412</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>483803</v>
+        <v>483735</v>
       </c>
       <c r="R35" t="n">
-        <v>6991669</v>
+        <v>6991823</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4831,18 +4240,12 @@
           <t>2025-09-02</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4866,32 +4269,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128151242</v>
+        <v>128149429</v>
       </c>
       <c r="B36" t="n">
-        <v>88735</v>
+        <v>89156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>824</v>
+        <v>4412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4904,10 +4307,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>483560</v>
+        <v>483367</v>
       </c>
       <c r="R36" t="n">
-        <v>6991627</v>
+        <v>6991677</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4954,7 +4357,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4972,49 +4375,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128153456</v>
+        <v>128151646</v>
       </c>
       <c r="B37" t="n">
-        <v>97612</v>
+        <v>89156</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222741</v>
+        <v>4412</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>483832</v>
+        <v>483638</v>
       </c>
       <c r="R37" t="n">
-        <v>6991926</v>
+        <v>6991579</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5061,7 +4463,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkpåverkad, örtrik sumpskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -5079,32 +4481,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128149062</v>
+        <v>128145243</v>
       </c>
       <c r="B38" t="n">
-        <v>91002</v>
+        <v>92869</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5747</v>
+        <v>4769</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5113,14 +4515,14 @@
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>483381</v>
+        <v>484061</v>
       </c>
       <c r="R38" t="n">
-        <v>6991732</v>
+        <v>6991711</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5185,32 +4587,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128147638</v>
+        <v>128145274</v>
       </c>
       <c r="B39" t="n">
-        <v>92749</v>
+        <v>92886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>4787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Granriska</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius zonarioides</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Kühner &amp; Romagn.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5223,10 +4625,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>483719</v>
+        <v>484038</v>
       </c>
       <c r="R39" t="n">
-        <v>6991835</v>
+        <v>6991684</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5291,48 +4693,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128151475</v>
+        <v>128145310</v>
       </c>
       <c r="B40" t="n">
-        <v>91010</v>
+        <v>91435</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5754</v>
+        <v>5747</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>483615</v>
+        <v>484048</v>
       </c>
       <c r="R40" t="n">
-        <v>6991623</v>
+        <v>6991644</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5373,7 +4772,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5397,32 +4795,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146450</v>
+        <v>128146085</v>
       </c>
       <c r="B41" t="n">
-        <v>91467</v>
+        <v>91435</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>5747</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5432,10 +4830,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>483803</v>
+        <v>483847</v>
       </c>
       <c r="R41" t="n">
-        <v>6991669</v>
+        <v>6991688</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5499,32 +4897,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128145519</v>
+        <v>128146254</v>
       </c>
       <c r="B42" t="n">
-        <v>100686</v>
+        <v>91435</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>222771</v>
+        <v>5747</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5534,10 +4932,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>483943</v>
+        <v>483825</v>
       </c>
       <c r="R42" t="n">
-        <v>6991638</v>
+        <v>6991736</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5601,10 +4999,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128152204</v>
+        <v>128146630</v>
       </c>
       <c r="B43" t="n">
-        <v>88735</v>
+        <v>91435</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5612,37 +5010,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>824</v>
+        <v>5747</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>483808</v>
+        <v>483783</v>
       </c>
       <c r="R43" t="n">
-        <v>6991708</v>
+        <v>6991660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5683,7 +5078,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5707,45 +5101,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128147461</v>
+        <v>128147670</v>
       </c>
       <c r="B44" t="n">
-        <v>88736</v>
+        <v>91435</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>483735</v>
+        <v>483723</v>
       </c>
       <c r="R44" t="n">
-        <v>6991823</v>
+        <v>6991850</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5786,6 +5183,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5809,32 +5207,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128148255</v>
+        <v>128148620</v>
       </c>
       <c r="B45" t="n">
-        <v>92751</v>
+        <v>91435</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>5747</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5847,10 +5245,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>483625</v>
+        <v>483486</v>
       </c>
       <c r="R45" t="n">
-        <v>6991850</v>
+        <v>6991836</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5915,32 +5313,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128151646</v>
+        <v>128148828</v>
       </c>
       <c r="B46" t="n">
-        <v>88736</v>
+        <v>91435</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4412</v>
+        <v>5747</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5949,14 +5347,14 @@
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>483638</v>
+        <v>483378</v>
       </c>
       <c r="R46" t="n">
-        <v>6991579</v>
+        <v>6991763</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6021,10 +5419,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128151718</v>
+        <v>128149062</v>
       </c>
       <c r="B47" t="n">
-        <v>90987</v>
+        <v>91435</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6032,21 +5430,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>256335</v>
+        <v>5747</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Taggfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria karstenii</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6055,14 +5453,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>483661</v>
+        <v>483381</v>
       </c>
       <c r="R47" t="n">
-        <v>6991539</v>
+        <v>6991732</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6127,32 +5525,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128151897</v>
+        <v>128149500</v>
       </c>
       <c r="B48" t="n">
-        <v>92775</v>
+        <v>91435</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4368</v>
+        <v>5747</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6161,14 +5559,14 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>483761</v>
+        <v>483377</v>
       </c>
       <c r="R48" t="n">
-        <v>6991506</v>
+        <v>6991679</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6215,7 +5613,7 @@
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
@@ -6233,45 +5631,48 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128146959</v>
+        <v>128151407</v>
       </c>
       <c r="B49" t="n">
-        <v>90928</v>
+        <v>91435</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>3286</v>
+        <v>5747</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>483814</v>
+        <v>483602</v>
       </c>
       <c r="R49" t="n">
-        <v>6991692</v>
+        <v>6991610</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6312,6 +5713,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6335,32 +5737,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128149405</v>
+        <v>128151830</v>
       </c>
       <c r="B50" t="n">
-        <v>91587</v>
+        <v>91435</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3277</v>
+        <v>5747</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6369,14 +5771,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>483367</v>
+        <v>483768</v>
       </c>
       <c r="R50" t="n">
-        <v>6991677</v>
+        <v>6991562</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6441,32 +5843,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128145589</v>
+        <v>128145822</v>
       </c>
       <c r="B51" t="n">
-        <v>92791</v>
+        <v>91443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6476,10 +5878,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>483946</v>
+        <v>483907</v>
       </c>
       <c r="R51" t="n">
-        <v>6991610</v>
+        <v>6991607</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6543,32 +5945,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128147670</v>
+        <v>128151475</v>
       </c>
       <c r="B52" t="n">
-        <v>91002</v>
+        <v>91443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5747</v>
+        <v>5754</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6577,14 +5979,14 @@
       <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>483723</v>
+        <v>483615</v>
       </c>
       <c r="R52" t="n">
-        <v>6991850</v>
+        <v>6991623</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6649,10 +6051,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128151643</v>
+        <v>128152970</v>
       </c>
       <c r="B53" t="n">
-        <v>92749</v>
+        <v>91443</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6660,21 +6062,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4361</v>
+        <v>5754</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6683,14 +6085,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>483638</v>
+        <v>483774</v>
       </c>
       <c r="R53" t="n">
-        <v>6991579</v>
+        <v>6991911</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6755,45 +6157,42 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128151407</v>
+        <v>128145589</v>
       </c>
       <c r="B54" t="n">
-        <v>91002</v>
+        <v>93233</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5747</v>
+        <v>5964</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>483602</v>
+        <v>483946</v>
       </c>
       <c r="R54" t="n">
         <v>6991610</v>
@@ -6837,7 +6236,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6861,10 +6259,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128151387</v>
+        <v>122708546</v>
       </c>
       <c r="B55" t="n">
-        <v>88735</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6872,40 +6270,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>824</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skäggvaxskivling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hygrophorus inocybiformis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>A.H.Sm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>483598</v>
+        <v>483452</v>
       </c>
       <c r="R55" t="n">
-        <v>6991632</v>
+        <v>6991602</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6929,12 +6324,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6943,34 +6338,53 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128146254</v>
+        <v>122708596</v>
       </c>
       <c r="B56" t="n">
-        <v>91002</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6978,37 +6392,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5747</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>483825</v>
+        <v>483520</v>
       </c>
       <c r="R56" t="n">
-        <v>6991736</v>
+        <v>6991663</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7032,12 +6446,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7049,71 +6463,93 @@
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128152853</v>
+        <v>122708958</v>
       </c>
       <c r="B57" t="n">
-        <v>91485</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>483774</v>
+        <v>483506</v>
       </c>
       <c r="R57" t="n">
-        <v>6991911</v>
+        <v>6991681</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7137,12 +6573,17 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Fertila bålar.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7151,72 +6592,88 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128148839</v>
+        <v>122709111</v>
       </c>
       <c r="B58" t="n">
-        <v>92775</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>483370</v>
+        <v>483508</v>
       </c>
       <c r="R58" t="n">
-        <v>6991758</v>
+        <v>6991741</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7243,12 +6700,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7257,72 +6714,96 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128146291</v>
+        <v>122709756</v>
       </c>
       <c r="B59" t="n">
-        <v>90928</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3286</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>483855</v>
+        <v>483522</v>
       </c>
       <c r="R59" t="n">
-        <v>6991698</v>
+        <v>6991771</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7346,12 +6827,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Med ovanligt förekommande soral. Finns även fertil garnlav i området. I relativt hänglavsrik kontinuitetsskog.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7363,30 +6849,50 @@
       <c r="AG59" t="b">
         <v>0</v>
       </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128148828</v>
+        <v>123176616</v>
       </c>
       <c r="B60" t="n">
-        <v>91002</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7394,37 +6900,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5747</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>483378</v>
+        <v>483371</v>
       </c>
       <c r="R60" t="n">
-        <v>6991763</v>
+        <v>6991602</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7451,12 +6963,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På grenar på gammal levande gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7465,34 +6992,28 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128148620</v>
+        <v>123176917</v>
       </c>
       <c r="B61" t="n">
-        <v>91002</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7500,37 +7021,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5747</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Christan</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>483486</v>
+        <v>483378</v>
       </c>
       <c r="R61" t="n">
-        <v>6991836</v>
+        <v>6991654</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7557,12 +7084,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:52</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7571,69 +7113,87 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128145365</v>
+        <v>123177015</v>
       </c>
       <c r="B62" t="n">
-        <v>92789</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1968</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon violascens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>483955</v>
+        <v>483436</v>
       </c>
       <c r="R62" t="n">
-        <v>6991637</v>
+        <v>6991677</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7660,12 +7220,27 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7677,68 +7252,84 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128148761</v>
+        <v>123177397</v>
       </c>
       <c r="B63" t="n">
-        <v>92775</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4368</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>483384</v>
+        <v>483605</v>
       </c>
       <c r="R63" t="n">
-        <v>6991763</v>
+        <v>6991834</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7765,12 +7356,27 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7779,72 +7385,87 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128145274</v>
+        <v>123179071</v>
       </c>
       <c r="B64" t="n">
-        <v>92419</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4787</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lactarius zonarioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kühner &amp; Romagn.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484038</v>
+        <v>483575</v>
       </c>
       <c r="R64" t="n">
-        <v>6991684</v>
+        <v>6991710</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7871,12 +7492,27 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7885,72 +7521,78 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128148640</v>
+        <v>123181366</v>
       </c>
       <c r="B65" t="n">
-        <v>91485</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>483483</v>
+        <v>483899</v>
       </c>
       <c r="R65" t="n">
-        <v>6991836</v>
+        <v>6991685</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7977,12 +7619,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7991,72 +7643,78 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128152970</v>
+        <v>123182989</v>
       </c>
       <c r="B66" t="n">
-        <v>91010</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5754</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>483774</v>
+        <v>483820</v>
       </c>
       <c r="R66" t="n">
-        <v>6991911</v>
+        <v>6991546</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8083,12 +7741,27 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8097,65 +7770,63 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128146568</v>
+        <v>123184445</v>
       </c>
       <c r="B67" t="n">
-        <v>86993</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3624</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Strimspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius glaucopus s.lat.</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>483803</v>
+        <v>483565</v>
       </c>
       <c r="R67" t="n">
-        <v>6991669</v>
+        <v>6991603</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8182,12 +7853,27 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8198,72 +7884,64 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128150924</v>
+        <v>133059573</v>
       </c>
       <c r="B68" t="n">
-        <v>91485</v>
+        <v>79373</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>483503</v>
+        <v>483225</v>
       </c>
       <c r="R68" t="n">
-        <v>6991606</v>
+        <v>6991633</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8287,12 +7965,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8301,34 +7989,28 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128150949</v>
+        <v>123176924</v>
       </c>
       <c r="B69" t="n">
-        <v>92775</v>
+        <v>83307</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8336,37 +8018,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4368</v>
+        <v>6440</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>483503</v>
+        <v>483383</v>
       </c>
       <c r="R69" t="n">
-        <v>6991606</v>
+        <v>6991656</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8393,12 +8072,27 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>09:53</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8407,34 +8101,43 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128152208</v>
+        <v>123177862</v>
       </c>
       <c r="B70" t="n">
-        <v>91587</v>
+        <v>83307</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8442,40 +8145,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3277</v>
+        <v>6440</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>483808</v>
+        <v>483615</v>
       </c>
       <c r="R70" t="n">
-        <v>6991708</v>
+        <v>6991838</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8499,12 +8204,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:16</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8513,56 +8233,65 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128146630</v>
+        <v>123182555</v>
       </c>
       <c r="B71" t="n">
-        <v>91002</v>
+        <v>80336</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5747</v>
+        <v>6456</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8572,10 +8301,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>483783</v>
+        <v>484005</v>
       </c>
       <c r="R71" t="n">
-        <v>6991660</v>
+        <v>6991716</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8602,12 +8331,27 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På asp (40 cm dbh)</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8619,30 +8363,40 @@
       <c r="AG71" t="b">
         <v>0</v>
       </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128151479</v>
+        <v>123182534</v>
       </c>
       <c r="B72" t="n">
-        <v>91246</v>
+        <v>80432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8650,36 +8404,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6331699</v>
+        <v>6458</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramaria aff. rubrievanescens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>s.auct.scand.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>eDNA</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>483615</v>
+        <v>484029</v>
       </c>
       <c r="R72" t="n">
-        <v>6991623</v>
+        <v>6991692</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8706,12 +8458,27 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal asp med många bohål från hackspett, i gammal granskog</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8720,61 +8487,65 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128145502</v>
+        <v>123180297</v>
       </c>
       <c r="B73" t="n">
-        <v>92749</v>
+        <v>80461</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4361</v>
+        <v>6462</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8784,13 +8555,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>483943</v>
+        <v>483829</v>
       </c>
       <c r="R73" t="n">
-        <v>6991638</v>
+        <v>6991767</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8814,12 +8585,27 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På grenar på gran stående under gamla aspar</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8831,65 +8617,75 @@
       <c r="AG73" t="b">
         <v>0</v>
       </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128146085</v>
+        <v>133059574</v>
       </c>
       <c r="B74" t="n">
-        <v>91002</v>
+        <v>58349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5747</v>
+        <v>103015</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>483847</v>
+        <v>483226</v>
       </c>
       <c r="R74" t="n">
-        <v>6991688</v>
+        <v>6991635</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8916,12 +8712,22 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8932,72 +8738,64 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128151611</v>
+        <v>133059569</v>
       </c>
       <c r="B75" t="n">
-        <v>90268</v>
+        <v>104707</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1599</v>
+        <v>222412</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>483633</v>
+        <v>483225</v>
       </c>
       <c r="R75" t="n">
-        <v>6991596</v>
+        <v>6991627</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9021,12 +8819,22 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9035,75 +8843,66 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128151367</v>
+        <v>133059570</v>
       </c>
       <c r="B76" t="n">
-        <v>89516</v>
+        <v>101403</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>275</v>
+        <v>222498</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kejsarskivling</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Catathelasma imperiale</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(P.Karst.) Singer</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Löfsåsen, Löfsåsen, Jmt</t>
+          <t>Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>483589</v>
+        <v>483224</v>
       </c>
       <c r="R76" t="n">
-        <v>6991633</v>
+        <v>6991630</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9127,12 +8926,22 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9141,69 +8950,67 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128145310</v>
+        <v>128153456</v>
       </c>
       <c r="B77" t="n">
-        <v>91002</v>
+        <v>98137</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5747</v>
+        <v>222741</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>484048</v>
+        <v>483832</v>
       </c>
       <c r="R77" t="n">
-        <v>6991644</v>
+        <v>6991926</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9244,12 +9051,13 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+          <t>Kalkpåverkad, örtrik sumpskog</t>
         </is>
       </c>
       <c r="AT77" t="inlineStr"/>
@@ -9267,32 +9075,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128147310</v>
+        <v>128145519</v>
       </c>
       <c r="B78" t="n">
-        <v>88736</v>
+        <v>101228</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4412</v>
+        <v>222771</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9302,10 +9110,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>483747</v>
+        <v>483943</v>
       </c>
       <c r="R78" t="n">
-        <v>6991783</v>
+        <v>6991638</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9369,10 +9177,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128145240</v>
+        <v>123176943</v>
       </c>
       <c r="B79" t="n">
-        <v>91587</v>
+        <v>78339</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9380,37 +9188,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3277</v>
+        <v>228579</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kvarnsved, Kvarnsved, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>484061</v>
+        <v>483380</v>
       </c>
       <c r="R79" t="n">
-        <v>6991711</v>
+        <v>6991656</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9437,12 +9242,27 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-03-14</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9451,56 +9271,65 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128149279</v>
+        <v>128148616</v>
       </c>
       <c r="B80" t="n">
-        <v>89472</v>
+        <v>91433</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>236437</v>
+        <v>233196</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Fjällfotad fingersvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Ramaria rufescens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Schaeff.) Corner</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9513,10 +9342,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>483326</v>
+        <v>483486</v>
       </c>
       <c r="R80" t="n">
-        <v>6991694</v>
+        <v>6991836</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9563,7 +9392,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9581,32 +9410,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128149429</v>
+        <v>128149279</v>
       </c>
       <c r="B81" t="n">
-        <v>88763</v>
+        <v>89870</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4412</v>
+        <v>236437</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Brun klibbskivling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Limacella glioderma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
+          <t>(Fr.) Maire</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9619,10 +9448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>483367</v>
+        <v>483326</v>
       </c>
       <c r="R81" t="n">
-        <v>6991677</v>
+        <v>6991694</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9687,32 +9516,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128149640</v>
+        <v>128151166</v>
       </c>
       <c r="B82" t="n">
-        <v>91614</v>
+        <v>91420</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3277</v>
+        <v>256335</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9721,14 +9550,14 @@
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Lillhägnen, Lillhägnen, Jmt</t>
+          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>483366</v>
+        <v>483551</v>
       </c>
       <c r="R82" t="n">
-        <v>6991587</v>
+        <v>6991637</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9775,7 +9604,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9793,10 +9622,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128149500</v>
+        <v>128151718</v>
       </c>
       <c r="B83" t="n">
-        <v>91029</v>
+        <v>91420</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9804,21 +9633,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5747</v>
+        <v>256335</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Taggfingersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Ramaria karstenii</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Sacc. &amp; P.Syd.) Corner</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9827,14 +9656,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>483377</v>
+        <v>483661</v>
       </c>
       <c r="R83" t="n">
-        <v>6991679</v>
+        <v>6991539</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9881,7 +9710,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9899,10 +9728,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128149450</v>
+        <v>128146454</v>
       </c>
       <c r="B84" t="n">
-        <v>92776</v>
+        <v>91428</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9910,21 +9739,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4361</v>
+        <v>256756</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9933,14 +9762,14 @@
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Kvarnsved, Kvarnsved, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>483377</v>
+        <v>483803</v>
       </c>
       <c r="R84" t="n">
-        <v>6991684</v>
+        <v>6991669</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9975,6 +9804,11 @@
           <t>2025-09-02</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Förekommer i en cirka 6-8 meter bred häxring.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9987,7 +9821,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -10005,32 +9839,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128149268</v>
+        <v>128149015</v>
       </c>
       <c r="B85" t="n">
-        <v>90295</v>
+        <v>87213</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1599</v>
+        <v>6038616</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Fjällfotad musseron</t>
+          <t>Blyspindling</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tricholoma olivaceotinctum</t>
+          <t>Cortinarius caesiocinctus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Mort.Chr. &amp; Heilm.-Claus.</t>
+          <t>Kühner</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10043,10 +9877,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>483328</v>
+        <v>483385</v>
       </c>
       <c r="R85" t="n">
-        <v>6991694</v>
+        <v>6991744</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10093,7 +9927,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Tidigare avverkad men naturligt föryngrad barrblandskog/kalkbarrskog</t>
+          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10111,10 +9945,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128148616</v>
+        <v>128151479</v>
       </c>
       <c r="B86" t="n">
-        <v>91041</v>
+        <v>91389</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10122,37 +9956,36 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>233196</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Fjällfotad fingersvamp</t>
-        </is>
+        <v>6331699</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria rufescens</t>
+          <t>Ramaria aff. rubrievanescens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) Corner</t>
+          <t>s.auct.scand.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="J86" t="inlineStr"/>
       <c r="K86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>eDNA</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
+          <t>Löfsåsen, Löfsåsen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>483486</v>
+        <v>483615</v>
       </c>
       <c r="R86" t="n">
-        <v>6991836</v>
+        <v>6991623</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10202,6 +10035,11 @@
           <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
         </is>
       </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
@@ -10214,326 +10052,6 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>128151166</v>
-      </c>
-      <c r="B87" t="n">
-        <v>91028</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>256335</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Taggfingersvamp</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ramaria karstenii</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>(Sacc. &amp; P.Syd.) Corner</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Kvarnsvedbäcken, Kvarnsvedbäcken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>483551</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6991637</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>Gammal och örtrik kalkgranskog med inslag av tall</t>
-        </is>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>133059574</v>
-      </c>
-      <c r="B88" t="n">
-        <v>58332</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q88" t="n">
-        <v>483226</v>
-      </c>
-      <c r="R88" t="n">
-        <v>6991635</v>
-      </c>
-      <c r="S88" t="n">
-        <v>10</v>
-      </c>
-      <c r="T88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>11:24</t>
-        </is>
-      </c>
-      <c r="AD88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG88" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT88" t="inlineStr"/>
-      <c r="AW88" t="inlineStr">
-        <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>133059573</v>
-      </c>
-      <c r="B89" t="n">
-        <v>79334</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q89" t="n">
-        <v>483225</v>
-      </c>
-      <c r="R89" t="n">
-        <v>6991633</v>
-      </c>
-      <c r="S89" t="n">
-        <v>6</v>
-      </c>
-      <c r="T89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AA89" t="inlineStr">
-        <is>
-          <t>2026-05-03</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AD89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG89" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT89" t="inlineStr"/>
-      <c r="AW89" t="inlineStr">
-        <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>Anne Siivola</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151387</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128152204</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146450</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123180336</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1440,6 +1475,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148801</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1546,6 +1586,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149268</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1652,6 +1697,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151611</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1754,6 +1804,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145365</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1860,6 +1915,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148629</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145240</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146899</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2174,6 +2244,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149405</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2280,6 +2355,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149640</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2386,6 +2466,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128152208</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2488,6 +2573,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146291</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2590,6 +2680,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146959</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2688,6 +2783,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146568</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2790,6 +2890,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145502</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2896,6 +3001,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128147638</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3002,6 +3112,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148746</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3108,6 +3223,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149450</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3214,6 +3334,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151643</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3320,6 +3445,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151907</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3426,6 +3556,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148255</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3532,6 +3667,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148749</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3638,6 +3778,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148761</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3744,6 +3889,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148839</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3850,6 +4000,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128150949</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3956,6 +4111,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151674</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4062,6 +4222,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151897</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4164,6 +4329,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128147310</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4266,6 +4436,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128147461</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4372,6 +4547,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149429</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4478,6 +4658,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151646</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4584,6 +4769,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145243</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4690,6 +4880,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145274</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4792,6 +4987,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145310</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4894,6 +5094,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146085</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4996,6 +5201,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146254</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5098,6 +5308,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146630</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5204,6 +5419,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128147670</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5310,6 +5530,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148620</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5416,6 +5641,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148828</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5522,6 +5752,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149062</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5628,6 +5863,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149500</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5734,6 +5974,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151407</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5840,6 +6085,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151830</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5942,6 +6192,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145822</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6048,6 +6303,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151475</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6154,6 +6414,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128152970</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6256,6 +6521,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145589</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6378,6 +6648,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122708546</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6500,6 +6775,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122708596</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6632,6 +6912,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122708958</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6754,6 +7039,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122709111</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6886,6 +7176,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122709756</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7007,6 +7302,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123176616</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7143,6 +7443,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123176917</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7279,6 +7584,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123177015</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7415,6 +7725,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123177397</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7551,6 +7866,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123179071</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7673,6 +7993,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123181366</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7785,6 +8110,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123182989</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7897,6 +8227,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123184445</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8004,6 +8339,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059573</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8131,6 +8471,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123176924</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8263,6 +8608,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123177862</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8390,6 +8740,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123182555</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8517,6 +8872,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123182534</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8644,6 +9004,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123180297</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8751,6 +9116,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059574</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8858,6 +9228,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059569</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8965,6 +9340,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133059570</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9072,6 +9452,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128153456</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9174,6 +9559,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128145519</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9301,6 +9691,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123176943</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9407,6 +9802,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128148616</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9513,6 +9913,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149279</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9619,6 +10024,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151166</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9725,6 +10135,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151718</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9836,6 +10251,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128146454</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9942,6 +10362,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128149015</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10052,8 +10477,100 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,116 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135993731</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91530</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6331699</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramaria aff. rubrievanescens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>s.auct.scand.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10570,6 +10680,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -10488,7 +10488,7 @@
         <v>135993731</v>
       </c>
       <c r="B87" t="n">
-        <v>91530</v>
+        <v>91531</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,116 +10480,6 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135993731</v>
-      </c>
-      <c r="B87" t="n">
-        <v>91531</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>6331699</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ramaria aff. rubrievanescens</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>s.auct.scand.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>483615</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6991624</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10570,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,116 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135993731</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91533</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6331699</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramaria aff. rubrievanescens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>s.auct.scand.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10570,6 +10680,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,116 +10480,6 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135993731</v>
-      </c>
-      <c r="B87" t="n">
-        <v>91533</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>6331699</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ramaria aff. rubrievanescens</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>s.auct.scand.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>483615</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6991624</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10570,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,116 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135993731</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91546</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6331699</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramaria aff. rubrievanescens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>s.auct.scand.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10570,6 +10680,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,116 +10480,6 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135993731</v>
-      </c>
-      <c r="B87" t="n">
-        <v>91546</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>6331699</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ramaria aff. rubrievanescens</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>s.auct.scand.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>483615</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6991624</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10570,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ86"/>
+  <dimension ref="A1:AZ87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,6 +10480,116 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>135993731</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91554</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6331699</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramaria aff. rubrievanescens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>s.auct.scand.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Löfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>483615</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6991624</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lockne</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10570,6 +10680,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -10488,7 +10488,7 @@
         <v>135993731</v>
       </c>
       <c r="B87" t="n">
-        <v>91554</v>
+        <v>91567</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>

--- a/artfynd/A 4967-2025 artfynd.xlsx
+++ b/artfynd/A 4967-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ87"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10480,116 +10480,6 @@
       <c r="AZ86" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128151479</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>135993731</v>
-      </c>
-      <c r="B87" t="n">
-        <v>91567</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>6331699</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Ramaria aff. rubrievanescens</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>s.auct.scand.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>Löfsåsen, Jmt</t>
-        </is>
-      </c>
-      <c r="Q87" t="n">
-        <v>483615</v>
-      </c>
-      <c r="R87" t="n">
-        <v>6991624</v>
-      </c>
-      <c r="S87" t="n">
-        <v>10</v>
-      </c>
-      <c r="T87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U87" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V87" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W87" t="inlineStr">
-        <is>
-          <t>Lockne</t>
-        </is>
-      </c>
-      <c r="Y87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AA87" t="inlineStr">
-        <is>
-          <t>2025-09-02</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>DNA-sekvens av Rashid Kadhims rapport https://artportalen.se/Sighting/128151479.</t>
-        </is>
-      </c>
-      <c r="AD87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF87" t="inlineStr"/>
-      <c r="AG87" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT87" t="inlineStr"/>
-      <c r="AW87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY87" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135993731</t>
         </is>
       </c>
     </row>
@@ -10680,7 +10570,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
